--- a/drone_data.xlsx
+++ b/drone_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ronak\Desktop\Drone Dashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ronak\Desktop\Drone Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D202CD-85D9-4CDA-9723-6157A22C5947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C18B614-9039-421D-82D9-8D3AD034C80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6042,7 +6042,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6069,6 +6069,7 @@
     <xf numFmtId="21" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="46" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8295,7 +8296,7 @@
       <c r="N1" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="14" t="s">
         <v>1951</v>
       </c>
       <c r="P1" s="10" t="s">
@@ -8345,7 +8346,7 @@
       <c r="N2" s="10">
         <v>91</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P2" s="13">
@@ -8395,7 +8396,7 @@
       <c r="N3" s="10">
         <v>142</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P3" s="13">
@@ -8443,7 +8444,7 @@
       <c r="N4" s="10">
         <v>440</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P4" s="10"/>
@@ -8481,7 +8482,7 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P5" s="13">
@@ -8531,7 +8532,7 @@
       <c r="N6" s="10">
         <v>239</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P6" s="13">
@@ -8581,7 +8582,7 @@
       <c r="N7" s="10">
         <v>603</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P7" s="13">
@@ -8631,7 +8632,7 @@
       <c r="N8" s="10">
         <v>589</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P8" s="13">
@@ -8681,7 +8682,7 @@
       <c r="N9" s="10">
         <v>434</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P9" s="13">
@@ -8729,7 +8730,7 @@
       <c r="N10" s="10">
         <v>349</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P10" s="10"/>
@@ -8777,7 +8778,7 @@
       <c r="N11" s="10">
         <v>351</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P11" s="13">
@@ -8827,7 +8828,7 @@
       <c r="N12" s="10">
         <v>441</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P12" s="13">
@@ -8875,7 +8876,7 @@
       <c r="N13" s="10">
         <v>349</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P13" s="10"/>
@@ -8923,7 +8924,7 @@
       <c r="N14" s="10">
         <v>531</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P14" s="13">
@@ -8971,7 +8972,7 @@
       <c r="N15" s="10">
         <v>573</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P15" s="10"/>
@@ -9017,7 +9018,7 @@
       <c r="N16" s="10">
         <v>574</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P16" s="10"/>
@@ -9065,7 +9066,7 @@
       <c r="N17" s="10">
         <v>390</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P17" s="13">
@@ -9113,7 +9114,7 @@
       <c r="N18" s="10">
         <v>227</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P18" s="10"/>
@@ -9159,7 +9160,7 @@
       <c r="N19" s="10">
         <v>372</v>
       </c>
-      <c r="O19" s="10" t="s">
+      <c r="O19" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P19" s="10"/>
@@ -9207,7 +9208,7 @@
       <c r="N20" s="10">
         <v>479</v>
       </c>
-      <c r="O20" s="10" t="s">
+      <c r="O20" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P20" s="13">
@@ -9255,7 +9256,7 @@
       <c r="N21" s="10">
         <v>530</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="O21" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P21" s="10"/>
@@ -9303,7 +9304,7 @@
       <c r="N22" s="10">
         <v>246</v>
       </c>
-      <c r="O22" s="10" t="s">
+      <c r="O22" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P22" s="13">
@@ -9353,7 +9354,7 @@
       <c r="N23" s="10">
         <v>401</v>
       </c>
-      <c r="O23" s="10" t="s">
+      <c r="O23" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P23" s="13">
@@ -9403,7 +9404,7 @@
       <c r="N24" s="10">
         <v>483</v>
       </c>
-      <c r="O24" s="10" t="s">
+      <c r="O24" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P24" s="13">
@@ -9451,7 +9452,7 @@
       <c r="N25" s="10">
         <v>427</v>
       </c>
-      <c r="O25" s="10" t="s">
+      <c r="O25" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P25" s="10"/>
@@ -9497,7 +9498,7 @@
       <c r="N26" s="10">
         <v>376</v>
       </c>
-      <c r="O26" s="10" t="s">
+      <c r="O26" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P26" s="10"/>
@@ -9545,7 +9546,7 @@
       <c r="N27" s="10">
         <v>361</v>
       </c>
-      <c r="O27" s="10" t="s">
+      <c r="O27" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P27" s="13">
@@ -9593,7 +9594,7 @@
       <c r="N28" s="10">
         <v>339</v>
       </c>
-      <c r="O28" s="10" t="s">
+      <c r="O28" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P28" s="10"/>
@@ -9639,7 +9640,7 @@
       <c r="N29" s="10">
         <v>584</v>
       </c>
-      <c r="O29" s="10" t="s">
+      <c r="O29" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P29" s="10"/>
@@ -9685,7 +9686,7 @@
       <c r="N30" s="10">
         <v>-22</v>
       </c>
-      <c r="O30" s="10" t="s">
+      <c r="O30" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P30" s="10"/>
@@ -9733,7 +9734,7 @@
       <c r="N31" s="10">
         <v>7</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P31" s="13">
@@ -9783,7 +9784,7 @@
       <c r="N32" s="10">
         <v>69</v>
       </c>
-      <c r="O32" s="10" t="s">
+      <c r="O32" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P32" s="13">
@@ -9833,7 +9834,7 @@
       <c r="N33" s="10">
         <v>144</v>
       </c>
-      <c r="O33" s="10" t="s">
+      <c r="O33" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P33" s="13">
@@ -9883,7 +9884,7 @@
       <c r="N34" s="10">
         <v>162</v>
       </c>
-      <c r="O34" s="10" t="s">
+      <c r="O34" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P34" s="13">
@@ -9933,7 +9934,7 @@
       <c r="N35" s="10">
         <v>144</v>
       </c>
-      <c r="O35" s="10" t="s">
+      <c r="O35" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P35" s="13">
@@ -9983,7 +9984,7 @@
       <c r="N36" s="10">
         <v>15</v>
       </c>
-      <c r="O36" s="10" t="s">
+      <c r="O36" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P36" s="13">
@@ -10033,7 +10034,7 @@
       <c r="N37" s="10">
         <v>133</v>
       </c>
-      <c r="O37" s="10" t="s">
+      <c r="O37" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P37" s="13">
@@ -10083,7 +10084,7 @@
       <c r="N38" s="10">
         <v>155</v>
       </c>
-      <c r="O38" s="10" t="s">
+      <c r="O38" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P38" s="13">
@@ -10133,7 +10134,7 @@
       <c r="N39" s="10">
         <v>69</v>
       </c>
-      <c r="O39" s="10" t="s">
+      <c r="O39" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P39" s="13">
@@ -10183,7 +10184,7 @@
       <c r="N40" s="10">
         <v>126</v>
       </c>
-      <c r="O40" s="10" t="s">
+      <c r="O40" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P40" s="13">
@@ -10233,7 +10234,7 @@
       <c r="N41" s="10">
         <v>136</v>
       </c>
-      <c r="O41" s="10" t="s">
+      <c r="O41" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P41" s="13">
@@ -10283,7 +10284,7 @@
       <c r="N42" s="10">
         <v>147</v>
       </c>
-      <c r="O42" s="10" t="s">
+      <c r="O42" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P42" s="13">
@@ -10333,7 +10334,7 @@
       <c r="N43" s="10">
         <v>165</v>
       </c>
-      <c r="O43" s="10" t="s">
+      <c r="O43" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P43" s="13">
@@ -10383,7 +10384,7 @@
       <c r="N44" s="10">
         <v>158</v>
       </c>
-      <c r="O44" s="10" t="s">
+      <c r="O44" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P44" s="13">
@@ -10433,7 +10434,7 @@
       <c r="N45" s="10">
         <v>155</v>
       </c>
-      <c r="O45" s="10" t="s">
+      <c r="O45" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P45" s="13">
@@ -10483,7 +10484,7 @@
       <c r="N46" s="10">
         <v>151</v>
       </c>
-      <c r="O46" s="10" t="s">
+      <c r="O46" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P46" s="13">
@@ -10533,7 +10534,7 @@
       <c r="N47" s="10">
         <v>153</v>
       </c>
-      <c r="O47" s="10" t="s">
+      <c r="O47" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P47" s="13">
@@ -10583,7 +10584,7 @@
       <c r="N48" s="10">
         <v>148</v>
       </c>
-      <c r="O48" s="10" t="s">
+      <c r="O48" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P48" s="13">
@@ -10633,7 +10634,7 @@
       <c r="N49" s="10">
         <v>157</v>
       </c>
-      <c r="O49" s="10" t="s">
+      <c r="O49" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P49" s="13">
@@ -10683,7 +10684,7 @@
       <c r="N50" s="10">
         <v>416</v>
       </c>
-      <c r="O50" s="10" t="s">
+      <c r="O50" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P50" s="13">
@@ -10733,7 +10734,7 @@
       <c r="N51" s="10">
         <v>103</v>
       </c>
-      <c r="O51" s="10" t="s">
+      <c r="O51" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P51" s="13">
@@ -10783,7 +10784,7 @@
       <c r="N52" s="10">
         <v>50</v>
       </c>
-      <c r="O52" s="10" t="s">
+      <c r="O52" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P52" s="13">
@@ -10831,7 +10832,7 @@
       <c r="N53" s="10">
         <v>32</v>
       </c>
-      <c r="O53" s="10" t="s">
+      <c r="O53" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P53" s="10"/>
@@ -10879,7 +10880,7 @@
       <c r="N54" s="10">
         <v>33</v>
       </c>
-      <c r="O54" s="10" t="s">
+      <c r="O54" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P54" s="13">
@@ -10929,7 +10930,7 @@
       <c r="N55" s="10">
         <v>41</v>
       </c>
-      <c r="O55" s="10" t="s">
+      <c r="O55" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P55" s="13">
@@ -10979,7 +10980,7 @@
       <c r="N56" s="10">
         <v>41</v>
       </c>
-      <c r="O56" s="10" t="s">
+      <c r="O56" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P56" s="13">
@@ -11029,7 +11030,7 @@
       <c r="N57" s="10">
         <v>176</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="O57" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P57" s="13">
@@ -11079,7 +11080,7 @@
       <c r="N58" s="10">
         <v>208</v>
       </c>
-      <c r="O58" s="10" t="s">
+      <c r="O58" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P58" s="13">
@@ -11129,7 +11130,7 @@
       <c r="N59" s="10">
         <v>206</v>
       </c>
-      <c r="O59" s="10" t="s">
+      <c r="O59" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P59" s="13">
@@ -11179,7 +11180,7 @@
       <c r="N60" s="10">
         <v>165</v>
       </c>
-      <c r="O60" s="10" t="s">
+      <c r="O60" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P60" s="13">
@@ -11229,7 +11230,7 @@
       <c r="N61" s="10">
         <v>164</v>
       </c>
-      <c r="O61" s="10" t="s">
+      <c r="O61" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P61" s="13">
@@ -11279,7 +11280,7 @@
       <c r="N62" s="10">
         <v>133</v>
       </c>
-      <c r="O62" s="10" t="s">
+      <c r="O62" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P62" s="13">
@@ -11329,7 +11330,7 @@
       <c r="N63" s="10">
         <v>121</v>
       </c>
-      <c r="O63" s="10" t="s">
+      <c r="O63" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P63" s="13">
@@ -11379,7 +11380,7 @@
       <c r="N64" s="10">
         <v>210</v>
       </c>
-      <c r="O64" s="10" t="s">
+      <c r="O64" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P64" s="13">
@@ -11429,7 +11430,7 @@
       <c r="N65" s="10">
         <v>-85</v>
       </c>
-      <c r="O65" s="10" t="s">
+      <c r="O65" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P65" s="13">
@@ -11479,7 +11480,7 @@
       <c r="N66" s="10">
         <v>176</v>
       </c>
-      <c r="O66" s="10" t="s">
+      <c r="O66" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P66" s="13">
@@ -11529,7 +11530,7 @@
       <c r="N67" s="10">
         <v>-85</v>
       </c>
-      <c r="O67" s="10" t="s">
+      <c r="O67" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P67" s="13">
@@ -11579,7 +11580,7 @@
       <c r="N68" s="10">
         <v>175</v>
       </c>
-      <c r="O68" s="10" t="s">
+      <c r="O68" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P68" s="13">
@@ -11629,7 +11630,7 @@
       <c r="N69" s="10">
         <v>195</v>
       </c>
-      <c r="O69" s="10" t="s">
+      <c r="O69" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P69" s="13">
@@ -11679,7 +11680,7 @@
       <c r="N70" s="10">
         <v>-85</v>
       </c>
-      <c r="O70" s="10" t="s">
+      <c r="O70" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P70" s="13">
@@ -11729,7 +11730,7 @@
       <c r="N71" s="10">
         <v>-85</v>
       </c>
-      <c r="O71" s="10" t="s">
+      <c r="O71" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P71" s="13">
@@ -11779,7 +11780,7 @@
       <c r="N72" s="10">
         <v>-85</v>
       </c>
-      <c r="O72" s="10" t="s">
+      <c r="O72" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P72" s="13">
@@ -11829,7 +11830,7 @@
       <c r="N73" s="10">
         <v>-98</v>
       </c>
-      <c r="O73" s="10" t="s">
+      <c r="O73" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P73" s="13">
@@ -11879,7 +11880,7 @@
       <c r="N74" s="10">
         <v>-98</v>
       </c>
-      <c r="O74" s="10" t="s">
+      <c r="O74" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P74" s="13">
@@ -11929,7 +11930,7 @@
       <c r="N75" s="10">
         <v>284</v>
       </c>
-      <c r="O75" s="10" t="s">
+      <c r="O75" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P75" s="13">
@@ -11979,7 +11980,7 @@
       <c r="N76" s="10">
         <v>160</v>
       </c>
-      <c r="O76" s="10" t="s">
+      <c r="O76" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P76" s="13">
@@ -12029,7 +12030,7 @@
       <c r="N77" s="10">
         <v>229</v>
       </c>
-      <c r="O77" s="10" t="s">
+      <c r="O77" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P77" s="13">
@@ -12079,7 +12080,7 @@
       <c r="N78" s="10">
         <v>-98</v>
       </c>
-      <c r="O78" s="10" t="s">
+      <c r="O78" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P78" s="13">
@@ -12129,7 +12130,7 @@
       <c r="N79" s="10">
         <v>157</v>
       </c>
-      <c r="O79" s="10" t="s">
+      <c r="O79" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P79" s="13">
@@ -12179,7 +12180,7 @@
       <c r="N80" s="10">
         <v>168</v>
       </c>
-      <c r="O80" s="10" t="s">
+      <c r="O80" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P80" s="13">
@@ -12229,7 +12230,7 @@
       <c r="N81" s="10">
         <v>148</v>
       </c>
-      <c r="O81" s="10" t="s">
+      <c r="O81" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P81" s="13">
@@ -12279,7 +12280,7 @@
       <c r="N82" s="10">
         <v>130</v>
       </c>
-      <c r="O82" s="10" t="s">
+      <c r="O82" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P82" s="13">
@@ -12329,7 +12330,7 @@
       <c r="N83" s="10">
         <v>-98</v>
       </c>
-      <c r="O83" s="10" t="s">
+      <c r="O83" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P83" s="13">
@@ -12377,7 +12378,7 @@
       <c r="N84" s="10">
         <v>-98</v>
       </c>
-      <c r="O84" s="10" t="s">
+      <c r="O84" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P84" s="10"/>
@@ -12425,7 +12426,7 @@
       <c r="N85" s="10">
         <v>221</v>
       </c>
-      <c r="O85" s="10" t="s">
+      <c r="O85" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P85" s="13">
@@ -12475,7 +12476,7 @@
       <c r="N86" s="10">
         <v>183</v>
       </c>
-      <c r="O86" s="10" t="s">
+      <c r="O86" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P86" s="13">
@@ -12525,7 +12526,7 @@
       <c r="N87" s="10">
         <v>169</v>
       </c>
-      <c r="O87" s="10" t="s">
+      <c r="O87" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P87" s="13">
@@ -12575,7 +12576,7 @@
       <c r="N88" s="10">
         <v>220</v>
       </c>
-      <c r="O88" s="10" t="s">
+      <c r="O88" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P88" s="13">
@@ -12625,7 +12626,7 @@
       <c r="N89" s="10">
         <v>210</v>
       </c>
-      <c r="O89" s="10" t="s">
+      <c r="O89" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P89" s="13">
@@ -12675,7 +12676,7 @@
       <c r="N90" s="10">
         <v>95</v>
       </c>
-      <c r="O90" s="10" t="s">
+      <c r="O90" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P90" s="13">
@@ -12725,7 +12726,7 @@
       <c r="N91" s="10">
         <v>178</v>
       </c>
-      <c r="O91" s="10" t="s">
+      <c r="O91" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P91" s="13">
@@ -12775,7 +12776,7 @@
       <c r="N92" s="10">
         <v>187</v>
       </c>
-      <c r="O92" s="10" t="s">
+      <c r="O92" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P92" s="13">
@@ -12825,7 +12826,7 @@
       <c r="N93" s="10">
         <v>69</v>
       </c>
-      <c r="O93" s="10" t="s">
+      <c r="O93" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P93" s="13">
@@ -12875,7 +12876,7 @@
       <c r="N94" s="10">
         <v>150</v>
       </c>
-      <c r="O94" s="10" t="s">
+      <c r="O94" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P94" s="13">
@@ -12925,7 +12926,7 @@
       <c r="N95" s="10">
         <v>179</v>
       </c>
-      <c r="O95" s="10" t="s">
+      <c r="O95" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P95" s="13">
@@ -12975,7 +12976,7 @@
       <c r="N96" s="10">
         <v>170</v>
       </c>
-      <c r="O96" s="10" t="s">
+      <c r="O96" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P96" s="13">
@@ -13025,7 +13026,7 @@
       <c r="N97" s="10">
         <v>560</v>
       </c>
-      <c r="O97" s="10" t="s">
+      <c r="O97" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P97" s="13">
@@ -13075,7 +13076,7 @@
       <c r="N98" s="10">
         <v>144</v>
       </c>
-      <c r="O98" s="10" t="s">
+      <c r="O98" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P98" s="13">
@@ -13125,7 +13126,7 @@
       <c r="N99" s="10">
         <v>136</v>
       </c>
-      <c r="O99" s="10" t="s">
+      <c r="O99" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P99" s="13">
@@ -13175,7 +13176,7 @@
       <c r="N100" s="10">
         <v>174</v>
       </c>
-      <c r="O100" s="10" t="s">
+      <c r="O100" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P100" s="13">
@@ -13225,7 +13226,7 @@
       <c r="N101" s="10">
         <v>170</v>
       </c>
-      <c r="O101" s="10" t="s">
+      <c r="O101" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P101" s="13">
@@ -13275,7 +13276,7 @@
       <c r="N102" s="10">
         <v>146</v>
       </c>
-      <c r="O102" s="10" t="s">
+      <c r="O102" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P102" s="13">
@@ -13325,7 +13326,7 @@
       <c r="N103" s="10">
         <v>193</v>
       </c>
-      <c r="O103" s="10" t="s">
+      <c r="O103" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P103" s="13">
@@ -13375,7 +13376,7 @@
       <c r="N104" s="10">
         <v>204</v>
       </c>
-      <c r="O104" s="10" t="s">
+      <c r="O104" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P104" s="13">
@@ -13425,7 +13426,7 @@
       <c r="N105" s="10">
         <v>173</v>
       </c>
-      <c r="O105" s="10" t="s">
+      <c r="O105" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P105" s="13">
@@ -13475,7 +13476,7 @@
       <c r="N106" s="10">
         <v>233</v>
       </c>
-      <c r="O106" s="10" t="s">
+      <c r="O106" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P106" s="13">
@@ -13525,7 +13526,7 @@
       <c r="N107" s="10">
         <v>153</v>
       </c>
-      <c r="O107" s="10" t="s">
+      <c r="O107" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P107" s="13">
@@ -13575,7 +13576,7 @@
       <c r="N108" s="10">
         <v>162</v>
       </c>
-      <c r="O108" s="10" t="s">
+      <c r="O108" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P108" s="13">
@@ -13625,7 +13626,7 @@
       <c r="N109" s="10">
         <v>172</v>
       </c>
-      <c r="O109" s="10" t="s">
+      <c r="O109" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P109" s="13">
@@ -13675,7 +13676,7 @@
       <c r="N110" s="10">
         <v>149</v>
       </c>
-      <c r="O110" s="10" t="s">
+      <c r="O110" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P110" s="13">
@@ -13725,7 +13726,7 @@
       <c r="N111" s="10">
         <v>152</v>
       </c>
-      <c r="O111" s="10" t="s">
+      <c r="O111" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P111" s="13">
@@ -13775,7 +13776,7 @@
       <c r="N112" s="10">
         <v>177</v>
       </c>
-      <c r="O112" s="10" t="s">
+      <c r="O112" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P112" s="13">
@@ -13825,7 +13826,7 @@
       <c r="N113" s="10">
         <v>175</v>
       </c>
-      <c r="O113" s="10" t="s">
+      <c r="O113" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P113" s="13">
@@ -13875,7 +13876,7 @@
       <c r="N114" s="10">
         <v>103</v>
       </c>
-      <c r="O114" s="10" t="s">
+      <c r="O114" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P114" s="13">
@@ -13925,7 +13926,7 @@
       <c r="N115" s="10">
         <v>149</v>
       </c>
-      <c r="O115" s="10" t="s">
+      <c r="O115" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P115" s="13">
@@ -13975,7 +13976,7 @@
       <c r="N116" s="10">
         <v>168</v>
       </c>
-      <c r="O116" s="10" t="s">
+      <c r="O116" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P116" s="13">
@@ -14025,7 +14026,7 @@
       <c r="N117" s="10">
         <v>-40</v>
       </c>
-      <c r="O117" s="10" t="s">
+      <c r="O117" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P117" s="13">
@@ -14075,7 +14076,7 @@
       <c r="N118" s="10">
         <v>173</v>
       </c>
-      <c r="O118" s="10" t="s">
+      <c r="O118" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P118" s="13">
@@ -14125,7 +14126,7 @@
       <c r="N119" s="10">
         <v>207</v>
       </c>
-      <c r="O119" s="10" t="s">
+      <c r="O119" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P119" s="13">
@@ -14175,7 +14176,7 @@
       <c r="N120" s="10">
         <v>-40</v>
       </c>
-      <c r="O120" s="10" t="s">
+      <c r="O120" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P120" s="13">
@@ -14225,7 +14226,7 @@
       <c r="N121" s="10">
         <v>138</v>
       </c>
-      <c r="O121" s="10" t="s">
+      <c r="O121" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P121" s="13">
@@ -14275,7 +14276,7 @@
       <c r="N122" s="10">
         <v>172</v>
       </c>
-      <c r="O122" s="10" t="s">
+      <c r="O122" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P122" s="13">
@@ -14325,7 +14326,7 @@
       <c r="N123" s="10">
         <v>197</v>
       </c>
-      <c r="O123" s="10" t="s">
+      <c r="O123" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P123" s="13">
@@ -14375,7 +14376,7 @@
       <c r="N124" s="10">
         <v>216</v>
       </c>
-      <c r="O124" s="10" t="s">
+      <c r="O124" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P124" s="13">
@@ -14425,7 +14426,7 @@
       <c r="N125" s="10">
         <v>159</v>
       </c>
-      <c r="O125" s="10" t="s">
+      <c r="O125" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P125" s="13">
@@ -14475,7 +14476,7 @@
       <c r="N126" s="10">
         <v>166</v>
       </c>
-      <c r="O126" s="10" t="s">
+      <c r="O126" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P126" s="13">
@@ -14525,7 +14526,7 @@
       <c r="N127" s="10">
         <v>216</v>
       </c>
-      <c r="O127" s="10" t="s">
+      <c r="O127" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P127" s="13">
@@ -14575,7 +14576,7 @@
       <c r="N128" s="10">
         <v>165</v>
       </c>
-      <c r="O128" s="10" t="s">
+      <c r="O128" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P128" s="13">
@@ -14625,7 +14626,7 @@
       <c r="N129" s="10">
         <v>200</v>
       </c>
-      <c r="O129" s="10" t="s">
+      <c r="O129" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P129" s="13">
@@ -14675,7 +14676,7 @@
       <c r="N130" s="10">
         <v>204</v>
       </c>
-      <c r="O130" s="10" t="s">
+      <c r="O130" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P130" s="13">
@@ -14725,7 +14726,7 @@
       <c r="N131" s="10">
         <v>206</v>
       </c>
-      <c r="O131" s="10" t="s">
+      <c r="O131" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P131" s="13">
@@ -14775,7 +14776,7 @@
       <c r="N132" s="10">
         <v>170</v>
       </c>
-      <c r="O132" s="10" t="s">
+      <c r="O132" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P132" s="13">
@@ -14825,7 +14826,7 @@
       <c r="N133" s="10">
         <v>212</v>
       </c>
-      <c r="O133" s="10" t="s">
+      <c r="O133" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P133" s="13">
@@ -14875,7 +14876,7 @@
       <c r="N134" s="10">
         <v>-45</v>
       </c>
-      <c r="O134" s="10" t="s">
+      <c r="O134" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P134" s="13">
@@ -14925,7 +14926,7 @@
       <c r="N135" s="10">
         <v>162</v>
       </c>
-      <c r="O135" s="10" t="s">
+      <c r="O135" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P135" s="13">
@@ -14975,7 +14976,7 @@
       <c r="N136" s="10">
         <v>206</v>
       </c>
-      <c r="O136" s="10" t="s">
+      <c r="O136" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P136" s="13">
@@ -15025,7 +15026,7 @@
       <c r="N137" s="10">
         <v>218</v>
       </c>
-      <c r="O137" s="10" t="s">
+      <c r="O137" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P137" s="13">
@@ -15075,7 +15076,7 @@
       <c r="N138" s="10">
         <v>192</v>
       </c>
-      <c r="O138" s="10" t="s">
+      <c r="O138" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P138" s="13">
@@ -15125,7 +15126,7 @@
       <c r="N139" s="10">
         <v>203</v>
       </c>
-      <c r="O139" s="10" t="s">
+      <c r="O139" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P139" s="13">
@@ -15175,7 +15176,7 @@
       <c r="N140" s="10">
         <v>191</v>
       </c>
-      <c r="O140" s="10" t="s">
+      <c r="O140" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P140" s="13">
@@ -15225,7 +15226,7 @@
       <c r="N141" s="10">
         <v>205</v>
       </c>
-      <c r="O141" s="10" t="s">
+      <c r="O141" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P141" s="13">
@@ -15275,7 +15276,7 @@
       <c r="N142" s="10">
         <v>181</v>
       </c>
-      <c r="O142" s="10" t="s">
+      <c r="O142" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P142" s="13">
@@ -15325,7 +15326,7 @@
       <c r="N143" s="10">
         <v>149</v>
       </c>
-      <c r="O143" s="10" t="s">
+      <c r="O143" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P143" s="13">
@@ -15375,7 +15376,7 @@
       <c r="N144" s="10">
         <v>273</v>
       </c>
-      <c r="O144" s="10" t="s">
+      <c r="O144" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P144" s="13">
@@ -15425,7 +15426,7 @@
       <c r="N145" s="10">
         <v>168</v>
       </c>
-      <c r="O145" s="10" t="s">
+      <c r="O145" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P145" s="13">
@@ -15475,7 +15476,7 @@
       <c r="N146" s="10">
         <v>206</v>
       </c>
-      <c r="O146" s="10" t="s">
+      <c r="O146" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P146" s="13">
@@ -15525,7 +15526,7 @@
       <c r="N147" s="10">
         <v>169</v>
       </c>
-      <c r="O147" s="10" t="s">
+      <c r="O147" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P147" s="13">
@@ -15575,7 +15576,7 @@
       <c r="N148" s="10">
         <v>206</v>
       </c>
-      <c r="O148" s="10" t="s">
+      <c r="O148" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P148" s="13">
@@ -15625,7 +15626,7 @@
       <c r="N149" s="10">
         <v>160</v>
       </c>
-      <c r="O149" s="10" t="s">
+      <c r="O149" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P149" s="13">
@@ -15675,7 +15676,7 @@
       <c r="N150" s="10">
         <v>173</v>
       </c>
-      <c r="O150" s="10" t="s">
+      <c r="O150" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P150" s="13">
@@ -15725,7 +15726,7 @@
       <c r="N151" s="10">
         <v>198</v>
       </c>
-      <c r="O151" s="10" t="s">
+      <c r="O151" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P151" s="13">
@@ -15775,7 +15776,7 @@
       <c r="N152" s="10">
         <v>-45</v>
       </c>
-      <c r="O152" s="10" t="s">
+      <c r="O152" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P152" s="13">
@@ -15825,7 +15826,7 @@
       <c r="N153" s="10">
         <v>198</v>
       </c>
-      <c r="O153" s="10" t="s">
+      <c r="O153" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P153" s="13">
@@ -15875,7 +15876,7 @@
       <c r="N154" s="10">
         <v>145</v>
       </c>
-      <c r="O154" s="10" t="s">
+      <c r="O154" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P154" s="13">
@@ -15925,7 +15926,7 @@
       <c r="N155" s="10">
         <v>179</v>
       </c>
-      <c r="O155" s="10" t="s">
+      <c r="O155" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P155" s="13">
@@ -15975,7 +15976,7 @@
       <c r="N156" s="10">
         <v>182</v>
       </c>
-      <c r="O156" s="10" t="s">
+      <c r="O156" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P156" s="13">
@@ -16025,7 +16026,7 @@
       <c r="N157" s="10">
         <v>154</v>
       </c>
-      <c r="O157" s="10" t="s">
+      <c r="O157" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P157" s="13">
@@ -16075,7 +16076,7 @@
       <c r="N158" s="10">
         <v>178</v>
       </c>
-      <c r="O158" s="10" t="s">
+      <c r="O158" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P158" s="13">
@@ -16125,7 +16126,7 @@
       <c r="N159" s="10">
         <v>446</v>
       </c>
-      <c r="O159" s="10" t="s">
+      <c r="O159" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P159" s="13">
@@ -16175,7 +16176,7 @@
       <c r="N160" s="10">
         <v>195</v>
       </c>
-      <c r="O160" s="10" t="s">
+      <c r="O160" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P160" s="13">
@@ -16225,7 +16226,7 @@
       <c r="N161" s="10">
         <v>204</v>
       </c>
-      <c r="O161" s="10" t="s">
+      <c r="O161" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P161" s="13">
@@ -16275,7 +16276,7 @@
       <c r="N162" s="10">
         <v>176</v>
       </c>
-      <c r="O162" s="10" t="s">
+      <c r="O162" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P162" s="13">
@@ -16325,7 +16326,7 @@
       <c r="N163" s="10">
         <v>156</v>
       </c>
-      <c r="O163" s="10" t="s">
+      <c r="O163" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P163" s="13">
@@ -16375,7 +16376,7 @@
       <c r="N164" s="10">
         <v>181</v>
       </c>
-      <c r="O164" s="10" t="s">
+      <c r="O164" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P164" s="13">
@@ -16425,7 +16426,7 @@
       <c r="N165" s="10">
         <v>182</v>
       </c>
-      <c r="O165" s="10" t="s">
+      <c r="O165" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P165" s="13">
@@ -16475,7 +16476,7 @@
       <c r="N166" s="10">
         <v>180</v>
       </c>
-      <c r="O166" s="10" t="s">
+      <c r="O166" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P166" s="13">
@@ -16525,7 +16526,7 @@
       <c r="N167" s="10">
         <v>247</v>
       </c>
-      <c r="O167" s="10" t="s">
+      <c r="O167" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P167" s="13">
@@ -16575,7 +16576,7 @@
       <c r="N168" s="10">
         <v>180</v>
       </c>
-      <c r="O168" s="10" t="s">
+      <c r="O168" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P168" s="13">
@@ -16625,7 +16626,7 @@
       <c r="N169" s="10">
         <v>183</v>
       </c>
-      <c r="O169" s="10" t="s">
+      <c r="O169" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P169" s="13">
@@ -16675,7 +16676,7 @@
       <c r="N170" s="10">
         <v>242</v>
       </c>
-      <c r="O170" s="10" t="s">
+      <c r="O170" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P170" s="13">
@@ -16725,7 +16726,7 @@
       <c r="N171" s="10">
         <v>176</v>
       </c>
-      <c r="O171" s="10" t="s">
+      <c r="O171" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P171" s="13">
@@ -16775,7 +16776,7 @@
       <c r="N172" s="10">
         <v>246</v>
       </c>
-      <c r="O172" s="10" t="s">
+      <c r="O172" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P172" s="13">
@@ -16825,7 +16826,7 @@
       <c r="N173" s="10">
         <v>258</v>
       </c>
-      <c r="O173" s="10" t="s">
+      <c r="O173" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P173" s="13">
@@ -16875,7 +16876,7 @@
       <c r="N174" s="10">
         <v>179</v>
       </c>
-      <c r="O174" s="10" t="s">
+      <c r="O174" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P174" s="13">
@@ -16925,7 +16926,7 @@
       <c r="N175" s="10">
         <v>247</v>
       </c>
-      <c r="O175" s="10" t="s">
+      <c r="O175" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P175" s="13">
@@ -16975,7 +16976,7 @@
       <c r="N176" s="10">
         <v>184</v>
       </c>
-      <c r="O176" s="10" t="s">
+      <c r="O176" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P176" s="13">
@@ -17025,7 +17026,7 @@
       <c r="N177" s="10">
         <v>173</v>
       </c>
-      <c r="O177" s="10" t="s">
+      <c r="O177" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P177" s="13">
@@ -17075,7 +17076,7 @@
       <c r="N178" s="10">
         <v>251</v>
       </c>
-      <c r="O178" s="10" t="s">
+      <c r="O178" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P178" s="13">
@@ -17125,7 +17126,7 @@
       <c r="N179" s="10">
         <v>198</v>
       </c>
-      <c r="O179" s="10" t="s">
+      <c r="O179" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P179" s="13">
@@ -17175,7 +17176,7 @@
       <c r="N180" s="10">
         <v>226</v>
       </c>
-      <c r="O180" s="10" t="s">
+      <c r="O180" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P180" s="13">
@@ -17223,7 +17224,7 @@
       <c r="N181" s="10">
         <v>-68</v>
       </c>
-      <c r="O181" s="10" t="s">
+      <c r="O181" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P181" s="10"/>
@@ -17271,7 +17272,7 @@
       <c r="N182" s="10">
         <v>158</v>
       </c>
-      <c r="O182" s="10" t="s">
+      <c r="O182" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P182" s="13">
@@ -17321,7 +17322,7 @@
       <c r="N183" s="10">
         <v>195</v>
       </c>
-      <c r="O183" s="10" t="s">
+      <c r="O183" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P183" s="13">
@@ -17371,7 +17372,7 @@
       <c r="N184" s="10">
         <v>165</v>
       </c>
-      <c r="O184" s="10" t="s">
+      <c r="O184" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P184" s="13">
@@ -17421,7 +17422,7 @@
       <c r="N185" s="10">
         <v>170</v>
       </c>
-      <c r="O185" s="10" t="s">
+      <c r="O185" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P185" s="13">
@@ -17469,7 +17470,7 @@
       <c r="N186" s="10">
         <v>154</v>
       </c>
-      <c r="O186" s="10" t="s">
+      <c r="O186" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P186" s="10"/>
@@ -17517,7 +17518,7 @@
       <c r="N187" s="10">
         <v>175</v>
       </c>
-      <c r="O187" s="10" t="s">
+      <c r="O187" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P187" s="13">
@@ -17567,7 +17568,7 @@
       <c r="N188" s="10">
         <v>185</v>
       </c>
-      <c r="O188" s="10" t="s">
+      <c r="O188" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P188" s="13">
@@ -17617,7 +17618,7 @@
       <c r="N189" s="10">
         <v>220</v>
       </c>
-      <c r="O189" s="10" t="s">
+      <c r="O189" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P189" s="13">
@@ -17667,7 +17668,7 @@
       <c r="N190" s="10">
         <v>196</v>
       </c>
-      <c r="O190" s="10" t="s">
+      <c r="O190" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P190" s="13">
@@ -17717,7 +17718,7 @@
       <c r="N191" s="10">
         <v>185</v>
       </c>
-      <c r="O191" s="10" t="s">
+      <c r="O191" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P191" s="13">
@@ -17767,7 +17768,7 @@
       <c r="N192" s="10">
         <v>205</v>
       </c>
-      <c r="O192" s="10" t="s">
+      <c r="O192" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P192" s="13">
@@ -17817,7 +17818,7 @@
       <c r="N193" s="10">
         <v>245</v>
       </c>
-      <c r="O193" s="10" t="s">
+      <c r="O193" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P193" s="13">
@@ -17867,7 +17868,7 @@
       <c r="N194" s="10">
         <v>230</v>
       </c>
-      <c r="O194" s="10" t="s">
+      <c r="O194" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P194" s="13">
@@ -17917,7 +17918,7 @@
       <c r="N195" s="10">
         <v>271</v>
       </c>
-      <c r="O195" s="10" t="s">
+      <c r="O195" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P195" s="13">
@@ -17967,7 +17968,7 @@
       <c r="N196" s="10">
         <v>215</v>
       </c>
-      <c r="O196" s="10" t="s">
+      <c r="O196" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P196" s="13">
@@ -18017,7 +18018,7 @@
       <c r="N197" s="10">
         <v>180</v>
       </c>
-      <c r="O197" s="10" t="s">
+      <c r="O197" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P197" s="13">
@@ -18067,7 +18068,7 @@
       <c r="N198" s="10">
         <v>275</v>
       </c>
-      <c r="O198" s="10" t="s">
+      <c r="O198" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P198" s="13">
@@ -18117,7 +18118,7 @@
       <c r="N199" s="10">
         <v>175</v>
       </c>
-      <c r="O199" s="10" t="s">
+      <c r="O199" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P199" s="13">
@@ -18167,7 +18168,7 @@
       <c r="N200" s="10">
         <v>230</v>
       </c>
-      <c r="O200" s="10" t="s">
+      <c r="O200" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P200" s="13">
@@ -18217,7 +18218,7 @@
       <c r="N201" s="10">
         <v>268</v>
       </c>
-      <c r="O201" s="10" t="s">
+      <c r="O201" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P201" s="13">
@@ -18267,7 +18268,7 @@
       <c r="N202" s="10">
         <v>179</v>
       </c>
-      <c r="O202" s="10" t="s">
+      <c r="O202" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P202" s="13">
@@ -18317,7 +18318,7 @@
       <c r="N203" s="10">
         <v>172</v>
       </c>
-      <c r="O203" s="10" t="s">
+      <c r="O203" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P203" s="13">
@@ -18367,7 +18368,7 @@
       <c r="N204" s="10">
         <v>152</v>
       </c>
-      <c r="O204" s="10" t="s">
+      <c r="O204" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P204" s="13">
@@ -18417,7 +18418,7 @@
       <c r="N205" s="10">
         <v>204</v>
       </c>
-      <c r="O205" s="10" t="s">
+      <c r="O205" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P205" s="13">
@@ -18467,7 +18468,7 @@
       <c r="N206" s="10">
         <v>315</v>
       </c>
-      <c r="O206" s="10" t="s">
+      <c r="O206" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P206" s="13">
@@ -18517,7 +18518,7 @@
       <c r="N207" s="10">
         <v>206</v>
       </c>
-      <c r="O207" s="10" t="s">
+      <c r="O207" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P207" s="13">
@@ -18567,7 +18568,7 @@
       <c r="N208" s="10">
         <v>219</v>
       </c>
-      <c r="O208" s="10" t="s">
+      <c r="O208" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P208" s="13">
@@ -18617,7 +18618,7 @@
       <c r="N209" s="10">
         <v>1022</v>
       </c>
-      <c r="O209" s="10" t="s">
+      <c r="O209" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P209" s="13">
@@ -18667,7 +18668,7 @@
       <c r="N210" s="10">
         <v>169</v>
       </c>
-      <c r="O210" s="10" t="s">
+      <c r="O210" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P210" s="13">
@@ -18717,7 +18718,7 @@
       <c r="N211" s="10">
         <v>171</v>
       </c>
-      <c r="O211" s="10" t="s">
+      <c r="O211" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P211" s="13">
@@ -18767,7 +18768,7 @@
       <c r="N212" s="10">
         <v>253</v>
       </c>
-      <c r="O212" s="10" t="s">
+      <c r="O212" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P212" s="13">
@@ -18817,7 +18818,7 @@
       <c r="N213" s="10">
         <v>145</v>
       </c>
-      <c r="O213" s="10" t="s">
+      <c r="O213" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P213" s="13">
@@ -18867,7 +18868,7 @@
       <c r="N214" s="10">
         <v>236</v>
       </c>
-      <c r="O214" s="10" t="s">
+      <c r="O214" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P214" s="13">
@@ -18917,7 +18918,7 @@
       <c r="N215" s="10">
         <v>176</v>
       </c>
-      <c r="O215" s="10" t="s">
+      <c r="O215" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P215" s="13">
@@ -18967,7 +18968,7 @@
       <c r="N216" s="10">
         <v>219</v>
       </c>
-      <c r="O216" s="10" t="s">
+      <c r="O216" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P216" s="13">
@@ -19017,7 +19018,7 @@
       <c r="N217" s="10">
         <v>219</v>
       </c>
-      <c r="O217" s="10" t="s">
+      <c r="O217" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P217" s="13">
@@ -19067,7 +19068,7 @@
       <c r="N218" s="10">
         <v>246</v>
       </c>
-      <c r="O218" s="10" t="s">
+      <c r="O218" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P218" s="13">
@@ -19117,7 +19118,7 @@
       <c r="N219" s="10">
         <v>185</v>
       </c>
-      <c r="O219" s="10" t="s">
+      <c r="O219" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P219" s="13">
@@ -19167,7 +19168,7 @@
       <c r="N220" s="10">
         <v>244</v>
       </c>
-      <c r="O220" s="10" t="s">
+      <c r="O220" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P220" s="13">
@@ -19217,7 +19218,7 @@
       <c r="N221" s="10">
         <v>323</v>
       </c>
-      <c r="O221" s="10" t="s">
+      <c r="O221" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P221" s="13">
@@ -19267,7 +19268,7 @@
       <c r="N222" s="10">
         <v>245</v>
       </c>
-      <c r="O222" s="10" t="s">
+      <c r="O222" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P222" s="13">
@@ -19317,7 +19318,7 @@
       <c r="N223" s="10">
         <v>181</v>
       </c>
-      <c r="O223" s="10" t="s">
+      <c r="O223" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P223" s="13">
@@ -19367,7 +19368,7 @@
       <c r="N224" s="10">
         <v>156</v>
       </c>
-      <c r="O224" s="10" t="s">
+      <c r="O224" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P224" s="13">
@@ -19417,7 +19418,7 @@
       <c r="N225" s="10">
         <v>232</v>
       </c>
-      <c r="O225" s="10" t="s">
+      <c r="O225" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P225" s="13">
@@ -19467,7 +19468,7 @@
       <c r="N226" s="10">
         <v>245</v>
       </c>
-      <c r="O226" s="10" t="s">
+      <c r="O226" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P226" s="13">
@@ -19517,7 +19518,7 @@
       <c r="N227" s="10">
         <v>182</v>
       </c>
-      <c r="O227" s="10" t="s">
+      <c r="O227" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P227" s="13">
@@ -19567,7 +19568,7 @@
       <c r="N228" s="10">
         <v>241</v>
       </c>
-      <c r="O228" s="10" t="s">
+      <c r="O228" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P228" s="13">
@@ -19617,7 +19618,7 @@
       <c r="N229" s="10">
         <v>-409</v>
       </c>
-      <c r="O229" s="10" t="s">
+      <c r="O229" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P229" s="13">
@@ -19667,7 +19668,7 @@
       <c r="N230" s="10">
         <v>249</v>
       </c>
-      <c r="O230" s="10" t="s">
+      <c r="O230" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P230" s="13">
@@ -19717,7 +19718,7 @@
       <c r="N231" s="10">
         <v>224</v>
       </c>
-      <c r="O231" s="10" t="s">
+      <c r="O231" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P231" s="13">
@@ -19767,7 +19768,7 @@
       <c r="N232" s="10">
         <v>247</v>
       </c>
-      <c r="O232" s="10" t="s">
+      <c r="O232" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P232" s="13">
@@ -19817,7 +19818,7 @@
       <c r="N233" s="10">
         <v>179</v>
       </c>
-      <c r="O233" s="10" t="s">
+      <c r="O233" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P233" s="13">
@@ -19867,7 +19868,7 @@
       <c r="N234" s="10">
         <v>218</v>
       </c>
-      <c r="O234" s="10" t="s">
+      <c r="O234" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P234" s="13">
@@ -19917,7 +19918,7 @@
       <c r="N235" s="10">
         <v>191</v>
       </c>
-      <c r="O235" s="10" t="s">
+      <c r="O235" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P235" s="13">
@@ -19967,7 +19968,7 @@
       <c r="N236" s="10">
         <v>178</v>
       </c>
-      <c r="O236" s="10" t="s">
+      <c r="O236" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P236" s="13">
@@ -20017,7 +20018,7 @@
       <c r="N237" s="10">
         <v>213</v>
       </c>
-      <c r="O237" s="10" t="s">
+      <c r="O237" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P237" s="13">
@@ -20067,7 +20068,7 @@
       <c r="N238" s="10">
         <v>231</v>
       </c>
-      <c r="O238" s="10" t="s">
+      <c r="O238" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P238" s="13">
@@ -20105,7 +20106,7 @@
       <c r="L239" s="10"/>
       <c r="M239" s="10"/>
       <c r="N239" s="10"/>
-      <c r="O239" s="10" t="s">
+      <c r="O239" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P239" s="10"/>
@@ -20151,7 +20152,7 @@
       <c r="N240" s="10">
         <v>19</v>
       </c>
-      <c r="O240" s="10" t="s">
+      <c r="O240" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P240" s="10"/>
@@ -20199,7 +20200,7 @@
       <c r="N241" s="10">
         <v>239</v>
       </c>
-      <c r="O241" s="10" t="s">
+      <c r="O241" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P241" s="13">
@@ -20249,7 +20250,7 @@
       <c r="N242" s="10">
         <v>175</v>
       </c>
-      <c r="O242" s="10" t="s">
+      <c r="O242" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P242" s="13">
@@ -20287,7 +20288,7 @@
       <c r="L243" s="10"/>
       <c r="M243" s="10"/>
       <c r="N243" s="10"/>
-      <c r="O243" s="10" t="s">
+      <c r="O243" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P243" s="10"/>
@@ -20335,7 +20336,7 @@
       <c r="N244" s="10">
         <v>271</v>
       </c>
-      <c r="O244" s="10" t="s">
+      <c r="O244" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P244" s="13">
@@ -20385,7 +20386,7 @@
       <c r="N245" s="10">
         <v>228</v>
       </c>
-      <c r="O245" s="10" t="s">
+      <c r="O245" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P245" s="13">
@@ -20435,7 +20436,7 @@
       <c r="N246" s="10">
         <v>215</v>
       </c>
-      <c r="O246" s="10" t="s">
+      <c r="O246" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P246" s="13">
@@ -20485,7 +20486,7 @@
       <c r="N247" s="10">
         <v>208</v>
       </c>
-      <c r="O247" s="10" t="s">
+      <c r="O247" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P247" s="13">
@@ -20535,7 +20536,7 @@
       <c r="N248" s="10">
         <v>167</v>
       </c>
-      <c r="O248" s="10" t="s">
+      <c r="O248" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P248" s="13">
@@ -20585,7 +20586,7 @@
       <c r="N249" s="10">
         <v>240</v>
       </c>
-      <c r="O249" s="10" t="s">
+      <c r="O249" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P249" s="13">
@@ -20635,7 +20636,7 @@
       <c r="N250" s="10">
         <v>194</v>
       </c>
-      <c r="O250" s="10" t="s">
+      <c r="O250" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P250" s="13">
@@ -20685,7 +20686,7 @@
       <c r="N251" s="10">
         <v>223</v>
       </c>
-      <c r="O251" s="10" t="s">
+      <c r="O251" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P251" s="13">
@@ -20735,7 +20736,7 @@
       <c r="N252" s="10">
         <v>234</v>
       </c>
-      <c r="O252" s="10" t="s">
+      <c r="O252" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P252" s="13">
@@ -20783,7 +20784,7 @@
       <c r="N253" s="10">
         <v>19</v>
       </c>
-      <c r="O253" s="10" t="s">
+      <c r="O253" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P253" s="10"/>
@@ -20831,7 +20832,7 @@
       <c r="N254" s="10">
         <v>323</v>
       </c>
-      <c r="O254" s="10" t="s">
+      <c r="O254" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P254" s="13">
@@ -20881,7 +20882,7 @@
       <c r="N255" s="10">
         <v>579</v>
       </c>
-      <c r="O255" s="10" t="s">
+      <c r="O255" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P255" s="13">
@@ -20931,7 +20932,7 @@
       <c r="N256" s="10">
         <v>341</v>
       </c>
-      <c r="O256" s="10" t="s">
+      <c r="O256" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P256" s="13">
@@ -20981,7 +20982,7 @@
       <c r="N257" s="10">
         <v>435</v>
       </c>
-      <c r="O257" s="10" t="s">
+      <c r="O257" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P257" s="13">
@@ -21031,7 +21032,7 @@
       <c r="N258" s="10">
         <v>229</v>
       </c>
-      <c r="O258" s="10" t="s">
+      <c r="O258" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P258" s="13">
@@ -21081,7 +21082,7 @@
       <c r="N259" s="10">
         <v>276</v>
       </c>
-      <c r="O259" s="10" t="s">
+      <c r="O259" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P259" s="13">
@@ -21131,7 +21132,7 @@
       <c r="N260" s="10">
         <v>292</v>
       </c>
-      <c r="O260" s="10" t="s">
+      <c r="O260" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P260" s="13">
@@ -21181,7 +21182,7 @@
       <c r="N261" s="10">
         <v>290</v>
       </c>
-      <c r="O261" s="10" t="s">
+      <c r="O261" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P261" s="13">
@@ -21231,7 +21232,7 @@
       <c r="N262" s="10">
         <v>423</v>
       </c>
-      <c r="O262" s="10" t="s">
+      <c r="O262" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P262" s="13">
@@ -21281,7 +21282,7 @@
       <c r="N263" s="10">
         <v>263</v>
       </c>
-      <c r="O263" s="10" t="s">
+      <c r="O263" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P263" s="13">
@@ -21331,7 +21332,7 @@
       <c r="N264" s="10">
         <v>260</v>
       </c>
-      <c r="O264" s="10" t="s">
+      <c r="O264" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P264" s="13">
@@ -21381,7 +21382,7 @@
       <c r="N265" s="10">
         <v>265</v>
       </c>
-      <c r="O265" s="10" t="s">
+      <c r="O265" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P265" s="13">
@@ -21431,7 +21432,7 @@
       <c r="N266" s="10">
         <v>266</v>
       </c>
-      <c r="O266" s="10" t="s">
+      <c r="O266" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P266" s="13">
@@ -21469,7 +21470,7 @@
       <c r="L267" s="10"/>
       <c r="M267" s="10"/>
       <c r="N267" s="10"/>
-      <c r="O267" s="10" t="s">
+      <c r="O267" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P267" s="10"/>
@@ -21517,7 +21518,7 @@
       <c r="N268" s="10">
         <v>298</v>
       </c>
-      <c r="O268" s="10" t="s">
+      <c r="O268" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P268" s="13">
@@ -21567,7 +21568,7 @@
       <c r="N269" s="10">
         <v>282</v>
       </c>
-      <c r="O269" s="10" t="s">
+      <c r="O269" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P269" s="13">
@@ -21617,7 +21618,7 @@
       <c r="N270" s="10">
         <v>318</v>
       </c>
-      <c r="O270" s="10" t="s">
+      <c r="O270" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P270" s="13">
@@ -21667,7 +21668,7 @@
       <c r="N271" s="10">
         <v>303</v>
       </c>
-      <c r="O271" s="10" t="s">
+      <c r="O271" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P271" s="13">
@@ -21717,7 +21718,7 @@
       <c r="N272" s="10">
         <v>303</v>
       </c>
-      <c r="O272" s="10" t="s">
+      <c r="O272" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P272" s="13">
@@ -21767,7 +21768,7 @@
       <c r="N273" s="10">
         <v>285</v>
       </c>
-      <c r="O273" s="10" t="s">
+      <c r="O273" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P273" s="13">
@@ -21817,7 +21818,7 @@
       <c r="N274" s="10">
         <v>291</v>
       </c>
-      <c r="O274" s="10" t="s">
+      <c r="O274" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P274" s="13">
@@ -21867,7 +21868,7 @@
       <c r="N275" s="10">
         <v>285</v>
       </c>
-      <c r="O275" s="10" t="s">
+      <c r="O275" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P275" s="13">
@@ -21917,7 +21918,7 @@
       <c r="N276" s="10">
         <v>256</v>
       </c>
-      <c r="O276" s="10" t="s">
+      <c r="O276" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P276" s="13">
@@ -21967,7 +21968,7 @@
       <c r="N277" s="10">
         <v>308</v>
       </c>
-      <c r="O277" s="10" t="s">
+      <c r="O277" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P277" s="13">
@@ -22017,7 +22018,7 @@
       <c r="N278" s="10">
         <v>270</v>
       </c>
-      <c r="O278" s="10" t="s">
+      <c r="O278" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P278" s="13">
@@ -22067,7 +22068,7 @@
       <c r="N279" s="10">
         <v>265</v>
       </c>
-      <c r="O279" s="10" t="s">
+      <c r="O279" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P279" s="13">
@@ -22117,7 +22118,7 @@
       <c r="N280" s="10">
         <v>266</v>
       </c>
-      <c r="O280" s="10" t="s">
+      <c r="O280" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P280" s="13">
@@ -22155,7 +22156,7 @@
       <c r="L281" s="10"/>
       <c r="M281" s="10"/>
       <c r="N281" s="10"/>
-      <c r="O281" s="10" t="s">
+      <c r="O281" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P281" s="10"/>
@@ -22203,7 +22204,7 @@
       <c r="N282" s="10">
         <v>261</v>
       </c>
-      <c r="O282" s="10" t="s">
+      <c r="O282" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P282" s="13">
@@ -22253,7 +22254,7 @@
       <c r="N283" s="10">
         <v>256</v>
       </c>
-      <c r="O283" s="10" t="s">
+      <c r="O283" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P283" s="13">
@@ -22303,7 +22304,7 @@
       <c r="N284" s="10">
         <v>307</v>
       </c>
-      <c r="O284" s="10" t="s">
+      <c r="O284" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P284" s="13">
@@ -22353,7 +22354,7 @@
       <c r="N285" s="10">
         <v>372</v>
       </c>
-      <c r="O285" s="10" t="s">
+      <c r="O285" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P285" s="13">
@@ -22403,7 +22404,7 @@
       <c r="N286" s="10">
         <v>257</v>
       </c>
-      <c r="O286" s="10" t="s">
+      <c r="O286" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P286" s="13">
@@ -22453,7 +22454,7 @@
       <c r="N287" s="10">
         <v>262</v>
       </c>
-      <c r="O287" s="10" t="s">
+      <c r="O287" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P287" s="13">
@@ -22503,7 +22504,7 @@
       <c r="N288" s="10">
         <v>270</v>
       </c>
-      <c r="O288" s="10" t="s">
+      <c r="O288" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P288" s="13">
@@ -22553,7 +22554,7 @@
       <c r="N289" s="10">
         <v>269</v>
       </c>
-      <c r="O289" s="10" t="s">
+      <c r="O289" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P289" s="13">
@@ -22603,7 +22604,7 @@
       <c r="N290" s="10">
         <v>267</v>
       </c>
-      <c r="O290" s="10" t="s">
+      <c r="O290" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P290" s="13">
@@ -22653,7 +22654,7 @@
       <c r="N291" s="10">
         <v>363</v>
       </c>
-      <c r="O291" s="10" t="s">
+      <c r="O291" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P291" s="13">
@@ -22703,7 +22704,7 @@
       <c r="N292" s="10">
         <v>264</v>
       </c>
-      <c r="O292" s="10" t="s">
+      <c r="O292" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P292" s="13">
@@ -22753,7 +22754,7 @@
       <c r="N293" s="10">
         <v>263</v>
       </c>
-      <c r="O293" s="10" t="s">
+      <c r="O293" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P293" s="13">
@@ -22803,7 +22804,7 @@
       <c r="N294" s="10">
         <v>258</v>
       </c>
-      <c r="O294" s="10" t="s">
+      <c r="O294" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P294" s="13">
@@ -22853,7 +22854,7 @@
       <c r="N295" s="10">
         <v>289</v>
       </c>
-      <c r="O295" s="10" t="s">
+      <c r="O295" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P295" s="13">
@@ -22903,7 +22904,7 @@
       <c r="N296" s="10">
         <v>265</v>
       </c>
-      <c r="O296" s="10" t="s">
+      <c r="O296" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P296" s="13">
@@ -22953,7 +22954,7 @@
       <c r="N297" s="10">
         <v>269</v>
       </c>
-      <c r="O297" s="10" t="s">
+      <c r="O297" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P297" s="13">
@@ -23003,7 +23004,7 @@
       <c r="N298" s="10">
         <v>406</v>
       </c>
-      <c r="O298" s="10" t="s">
+      <c r="O298" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P298" s="13">
@@ -23053,7 +23054,7 @@
       <c r="N299" s="10">
         <v>425</v>
       </c>
-      <c r="O299" s="10" t="s">
+      <c r="O299" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P299" s="13">
@@ -23103,7 +23104,7 @@
       <c r="N300" s="10">
         <v>427</v>
       </c>
-      <c r="O300" s="10" t="s">
+      <c r="O300" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P300" s="13">
@@ -23153,7 +23154,7 @@
       <c r="N301" s="10">
         <v>355</v>
       </c>
-      <c r="O301" s="10" t="s">
+      <c r="O301" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P301" s="13">
@@ -23203,7 +23204,7 @@
       <c r="N302" s="10">
         <v>387</v>
       </c>
-      <c r="O302" s="10" t="s">
+      <c r="O302" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P302" s="13">
@@ -23253,7 +23254,7 @@
       <c r="N303" s="10">
         <v>375</v>
       </c>
-      <c r="O303" s="10" t="s">
+      <c r="O303" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P303" s="13">
@@ -23303,7 +23304,7 @@
       <c r="N304" s="10">
         <v>508</v>
       </c>
-      <c r="O304" s="10" t="s">
+      <c r="O304" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P304" s="13">
@@ -23353,7 +23354,7 @@
       <c r="N305" s="10">
         <v>426</v>
       </c>
-      <c r="O305" s="10" t="s">
+      <c r="O305" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P305" s="13">
@@ -23403,7 +23404,7 @@
       <c r="N306" s="10">
         <v>376</v>
       </c>
-      <c r="O306" s="10" t="s">
+      <c r="O306" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P306" s="13">
@@ -23453,7 +23454,7 @@
       <c r="N307" s="10">
         <v>382</v>
       </c>
-      <c r="O307" s="10" t="s">
+      <c r="O307" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P307" s="13">
@@ -23503,7 +23504,7 @@
       <c r="N308" s="10">
         <v>264</v>
       </c>
-      <c r="O308" s="10" t="s">
+      <c r="O308" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P308" s="13">
@@ -23553,7 +23554,7 @@
       <c r="N309" s="10">
         <v>350</v>
       </c>
-      <c r="O309" s="10" t="s">
+      <c r="O309" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P309" s="13">
@@ -23603,7 +23604,7 @@
       <c r="N310" s="10">
         <v>433</v>
       </c>
-      <c r="O310" s="10" t="s">
+      <c r="O310" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P310" s="13">
@@ -23653,7 +23654,7 @@
       <c r="N311" s="10">
         <v>441</v>
       </c>
-      <c r="O311" s="10" t="s">
+      <c r="O311" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P311" s="13">
@@ -23703,7 +23704,7 @@
       <c r="N312" s="10">
         <v>377</v>
       </c>
-      <c r="O312" s="10" t="s">
+      <c r="O312" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P312" s="13">
@@ -23753,7 +23754,7 @@
       <c r="N313" s="10">
         <v>-133</v>
       </c>
-      <c r="O313" s="10" t="s">
+      <c r="O313" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P313" s="13">
@@ -23803,7 +23804,7 @@
       <c r="N314" s="10">
         <v>355</v>
       </c>
-      <c r="O314" s="10" t="s">
+      <c r="O314" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P314" s="13">
@@ -23853,7 +23854,7 @@
       <c r="N315" s="10">
         <v>380</v>
       </c>
-      <c r="O315" s="10" t="s">
+      <c r="O315" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P315" s="13">
@@ -23903,7 +23904,7 @@
       <c r="N316" s="10">
         <v>433</v>
       </c>
-      <c r="O316" s="10" t="s">
+      <c r="O316" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P316" s="13">
@@ -23953,7 +23954,7 @@
       <c r="N317" s="10">
         <v>458</v>
       </c>
-      <c r="O317" s="10" t="s">
+      <c r="O317" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P317" s="13">
@@ -24003,7 +24004,7 @@
       <c r="N318" s="10">
         <v>420</v>
       </c>
-      <c r="O318" s="10" t="s">
+      <c r="O318" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P318" s="13">
@@ -24053,7 +24054,7 @@
       <c r="N319" s="10">
         <v>408</v>
       </c>
-      <c r="O319" s="10" t="s">
+      <c r="O319" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P319" s="13">
@@ -24103,7 +24104,7 @@
       <c r="N320" s="10">
         <v>494</v>
       </c>
-      <c r="O320" s="10" t="s">
+      <c r="O320" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P320" s="13">
@@ -24153,7 +24154,7 @@
       <c r="N321" s="10">
         <v>405</v>
       </c>
-      <c r="O321" s="10" t="s">
+      <c r="O321" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P321" s="13">
@@ -24203,7 +24204,7 @@
       <c r="N322" s="10">
         <v>13</v>
       </c>
-      <c r="O322" s="10" t="s">
+      <c r="O322" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P322" s="13">
@@ -24253,7 +24254,7 @@
       <c r="N323" s="10">
         <v>-197</v>
       </c>
-      <c r="O323" s="10" t="s">
+      <c r="O323" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P323" s="13">
@@ -24303,7 +24304,7 @@
       <c r="N324" s="10">
         <v>22</v>
       </c>
-      <c r="O324" s="10" t="s">
+      <c r="O324" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P324" s="13">
@@ -24343,7 +24344,7 @@
       <c r="L325" s="10"/>
       <c r="M325" s="10"/>
       <c r="N325" s="10"/>
-      <c r="O325" s="10" t="s">
+      <c r="O325" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P325" s="13">
@@ -24393,7 +24394,7 @@
       <c r="N326" s="10">
         <v>754</v>
       </c>
-      <c r="O326" s="10" t="s">
+      <c r="O326" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P326" s="13">
@@ -24443,7 +24444,7 @@
       <c r="N327" s="10">
         <v>460</v>
       </c>
-      <c r="O327" s="10" t="s">
+      <c r="O327" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P327" s="13">
@@ -24493,7 +24494,7 @@
       <c r="N328" s="10">
         <v>0</v>
       </c>
-      <c r="O328" s="10" t="s">
+      <c r="O328" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P328" s="13">
@@ -24543,7 +24544,7 @@
       <c r="N329" s="10">
         <v>505</v>
       </c>
-      <c r="O329" s="10" t="s">
+      <c r="O329" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P329" s="13">
@@ -24583,7 +24584,7 @@
       <c r="L330" s="10"/>
       <c r="M330" s="10"/>
       <c r="N330" s="10"/>
-      <c r="O330" s="10" t="s">
+      <c r="O330" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P330" s="13">
@@ -24633,7 +24634,7 @@
       <c r="N331" s="10">
         <v>-30</v>
       </c>
-      <c r="O331" s="10" t="s">
+      <c r="O331" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P331" s="13">
@@ -24683,7 +24684,7 @@
       <c r="N332" s="10">
         <v>-177</v>
       </c>
-      <c r="O332" s="10" t="s">
+      <c r="O332" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P332" s="13">
@@ -24733,7 +24734,7 @@
       <c r="N333" s="10">
         <v>39</v>
       </c>
-      <c r="O333" s="10" t="s">
+      <c r="O333" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P333" s="13">
@@ -24783,7 +24784,7 @@
       <c r="N334" s="10">
         <v>85</v>
       </c>
-      <c r="O334" s="10" t="s">
+      <c r="O334" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P334" s="13">
@@ -24833,7 +24834,7 @@
       <c r="N335" s="10">
         <v>548</v>
       </c>
-      <c r="O335" s="10" t="s">
+      <c r="O335" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P335" s="13">
@@ -24883,7 +24884,7 @@
       <c r="N336" s="10">
         <v>579</v>
       </c>
-      <c r="O336" s="10" t="s">
+      <c r="O336" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P336" s="13">
@@ -24933,7 +24934,7 @@
       <c r="N337" s="10">
         <v>593</v>
       </c>
-      <c r="O337" s="10" t="s">
+      <c r="O337" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P337" s="13">
@@ -24983,7 +24984,7 @@
       <c r="N338" s="10">
         <v>476</v>
       </c>
-      <c r="O338" s="10" t="s">
+      <c r="O338" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P338" s="13">
@@ -25033,7 +25034,7 @@
       <c r="N339" s="10">
         <v>575</v>
       </c>
-      <c r="O339" s="10" t="s">
+      <c r="O339" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P339" s="13">
@@ -25083,7 +25084,7 @@
       <c r="N340" s="10">
         <v>562</v>
       </c>
-      <c r="O340" s="10" t="s">
+      <c r="O340" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P340" s="13">
@@ -25133,7 +25134,7 @@
       <c r="N341" s="10">
         <v>569</v>
       </c>
-      <c r="O341" s="10" t="s">
+      <c r="O341" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P341" s="13">
@@ -25183,7 +25184,7 @@
       <c r="N342" s="10">
         <v>740</v>
       </c>
-      <c r="O342" s="10" t="s">
+      <c r="O342" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P342" s="13">
@@ -25221,7 +25222,7 @@
       <c r="L343" s="10"/>
       <c r="M343" s="10"/>
       <c r="N343" s="10"/>
-      <c r="O343" s="10" t="s">
+      <c r="O343" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P343" s="10"/>
@@ -25269,7 +25270,7 @@
       <c r="N344" s="10">
         <v>11</v>
       </c>
-      <c r="O344" s="10" t="s">
+      <c r="O344" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P344" s="13">
@@ -25319,7 +25320,7 @@
       <c r="N345" s="10">
         <v>-47</v>
       </c>
-      <c r="O345" s="10" t="s">
+      <c r="O345" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P345" s="13">
@@ -25369,7 +25370,7 @@
       <c r="N346" s="10">
         <v>389</v>
       </c>
-      <c r="O346" s="10" t="s">
+      <c r="O346" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P346" s="13">
@@ -25419,7 +25420,7 @@
       <c r="N347" s="10">
         <v>365</v>
       </c>
-      <c r="O347" s="10" t="s">
+      <c r="O347" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P347" s="13">
@@ -25469,7 +25470,7 @@
       <c r="N348" s="10">
         <v>-110</v>
       </c>
-      <c r="O348" s="10" t="s">
+      <c r="O348" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P348" s="13">
@@ -25509,7 +25510,7 @@
       <c r="L349" s="10"/>
       <c r="M349" s="10"/>
       <c r="N349" s="10"/>
-      <c r="O349" s="10" t="s">
+      <c r="O349" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P349" s="13">
@@ -25559,7 +25560,7 @@
       <c r="N350" s="10">
         <v>-81</v>
       </c>
-      <c r="O350" s="10" t="s">
+      <c r="O350" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P350" s="13">
@@ -25609,7 +25610,7 @@
       <c r="N351" s="10">
         <v>43</v>
       </c>
-      <c r="O351" s="10" t="s">
+      <c r="O351" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P351" s="13">
@@ -25659,7 +25660,7 @@
       <c r="N352" s="10">
         <v>-49</v>
       </c>
-      <c r="O352" s="10" t="s">
+      <c r="O352" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P352" s="13">
@@ -25709,7 +25710,7 @@
       <c r="N353" s="10">
         <v>250</v>
       </c>
-      <c r="O353" s="10" t="s">
+      <c r="O353" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P353" s="13">
@@ -25759,7 +25760,7 @@
       <c r="N354" s="10">
         <v>352</v>
       </c>
-      <c r="O354" s="10" t="s">
+      <c r="O354" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P354" s="13">
@@ -25809,7 +25810,7 @@
       <c r="N355" s="10">
         <v>378</v>
       </c>
-      <c r="O355" s="10" t="s">
+      <c r="O355" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P355" s="13">
@@ -25849,7 +25850,7 @@
       <c r="L356" s="10"/>
       <c r="M356" s="10"/>
       <c r="N356" s="10"/>
-      <c r="O356" s="10" t="s">
+      <c r="O356" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P356" s="13">
@@ -25899,7 +25900,7 @@
       <c r="N357" s="10">
         <v>-43</v>
       </c>
-      <c r="O357" s="10" t="s">
+      <c r="O357" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P357" s="13">
@@ -25949,7 +25950,7 @@
       <c r="N358" s="10">
         <v>342</v>
       </c>
-      <c r="O358" s="10" t="s">
+      <c r="O358" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P358" s="13">
@@ -25999,7 +26000,7 @@
       <c r="N359" s="10">
         <v>233</v>
       </c>
-      <c r="O359" s="10" t="s">
+      <c r="O359" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P359" s="13">
@@ -26049,7 +26050,7 @@
       <c r="N360" s="10">
         <v>-15</v>
       </c>
-      <c r="O360" s="10" t="s">
+      <c r="O360" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P360" s="13">
@@ -26099,7 +26100,7 @@
       <c r="N361" s="10">
         <v>23</v>
       </c>
-      <c r="O361" s="10" t="s">
+      <c r="O361" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P361" s="13">
@@ -26149,7 +26150,7 @@
       <c r="N362" s="10">
         <v>230</v>
       </c>
-      <c r="O362" s="10" t="s">
+      <c r="O362" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P362" s="13">
@@ -26199,7 +26200,7 @@
       <c r="N363" s="10">
         <v>430</v>
       </c>
-      <c r="O363" s="10" t="s">
+      <c r="O363" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P363" s="13">
@@ -26249,7 +26250,7 @@
       <c r="N364" s="10">
         <v>377</v>
       </c>
-      <c r="O364" s="10" t="s">
+      <c r="O364" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P364" s="13">
@@ -26299,7 +26300,7 @@
       <c r="N365" s="10">
         <v>338</v>
       </c>
-      <c r="O365" s="10" t="s">
+      <c r="O365" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P365" s="13">
@@ -26349,7 +26350,7 @@
       <c r="N366" s="10">
         <v>634</v>
       </c>
-      <c r="O366" s="10" t="s">
+      <c r="O366" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P366" s="13">
@@ -26399,7 +26400,7 @@
       <c r="N367" s="10">
         <v>409</v>
       </c>
-      <c r="O367" s="10" t="s">
+      <c r="O367" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P367" s="13">
@@ -26449,7 +26450,7 @@
       <c r="N368" s="10">
         <v>488</v>
       </c>
-      <c r="O368" s="10" t="s">
+      <c r="O368" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P368" s="13">
@@ -26499,7 +26500,7 @@
       <c r="N369" s="10">
         <v>220</v>
       </c>
-      <c r="O369" s="10" t="s">
+      <c r="O369" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P369" s="13">
@@ -26549,7 +26550,7 @@
       <c r="N370" s="10">
         <v>218</v>
       </c>
-      <c r="O370" s="10" t="s">
+      <c r="O370" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P370" s="13">
@@ -26599,7 +26600,7 @@
       <c r="N371" s="10">
         <v>211</v>
       </c>
-      <c r="O371" s="10" t="s">
+      <c r="O371" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P371" s="13">
@@ -26649,7 +26650,7 @@
       <c r="N372" s="10">
         <v>217</v>
       </c>
-      <c r="O372" s="10" t="s">
+      <c r="O372" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P372" s="13">
@@ -26699,7 +26700,7 @@
       <c r="N373" s="10">
         <v>212</v>
       </c>
-      <c r="O373" s="10" t="s">
+      <c r="O373" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P373" s="13">
@@ -26749,7 +26750,7 @@
       <c r="N374" s="10">
         <v>210</v>
       </c>
-      <c r="O374" s="10" t="s">
+      <c r="O374" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P374" s="13">
@@ -26799,7 +26800,7 @@
       <c r="N375" s="10">
         <v>226</v>
       </c>
-      <c r="O375" s="10" t="s">
+      <c r="O375" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P375" s="13">
@@ -26849,7 +26850,7 @@
       <c r="N376" s="10">
         <v>240</v>
       </c>
-      <c r="O376" s="10" t="s">
+      <c r="O376" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P376" s="13">
@@ -26899,7 +26900,7 @@
       <c r="N377" s="10">
         <v>239</v>
       </c>
-      <c r="O377" s="10" t="s">
+      <c r="O377" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P377" s="13">
@@ -26949,7 +26950,7 @@
       <c r="N378" s="10">
         <v>8</v>
       </c>
-      <c r="O378" s="10" t="s">
+      <c r="O378" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P378" s="13">
@@ -26999,7 +27000,7 @@
       <c r="N379" s="10">
         <v>662</v>
       </c>
-      <c r="O379" s="10" t="s">
+      <c r="O379" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P379" s="13">
@@ -27049,7 +27050,7 @@
       <c r="N380" s="10">
         <v>225</v>
       </c>
-      <c r="O380" s="10" t="s">
+      <c r="O380" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P380" s="13">
@@ -27099,7 +27100,7 @@
       <c r="N381" s="10">
         <v>642</v>
       </c>
-      <c r="O381" s="10" t="s">
+      <c r="O381" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P381" s="13">
@@ -27149,7 +27150,7 @@
       <c r="N382" s="10">
         <v>660</v>
       </c>
-      <c r="O382" s="10" t="s">
+      <c r="O382" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P382" s="13">
@@ -27199,7 +27200,7 @@
       <c r="N383" s="10">
         <v>21</v>
       </c>
-      <c r="O383" s="10" t="s">
+      <c r="O383" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P383" s="13">
@@ -27249,7 +27250,7 @@
       <c r="N384" s="10">
         <v>647</v>
       </c>
-      <c r="O384" s="10" t="s">
+      <c r="O384" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P384" s="13">
@@ -27299,7 +27300,7 @@
       <c r="N385" s="10">
         <v>627</v>
       </c>
-      <c r="O385" s="10" t="s">
+      <c r="O385" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P385" s="13">
@@ -27349,7 +27350,7 @@
       <c r="N386" s="10">
         <v>25</v>
       </c>
-      <c r="O386" s="10" t="s">
+      <c r="O386" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P386" s="13">
@@ -27399,7 +27400,7 @@
       <c r="N387" s="10">
         <v>665</v>
       </c>
-      <c r="O387" s="10" t="s">
+      <c r="O387" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P387" s="13">
@@ -27449,7 +27450,7 @@
       <c r="N388" s="10">
         <v>729</v>
       </c>
-      <c r="O388" s="10" t="s">
+      <c r="O388" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P388" s="13">
@@ -27499,7 +27500,7 @@
       <c r="N389" s="10">
         <v>25</v>
       </c>
-      <c r="O389" s="10" t="s">
+      <c r="O389" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P389" s="13">
@@ -27549,7 +27550,7 @@
       <c r="N390" s="10">
         <v>12</v>
       </c>
-      <c r="O390" s="10" t="s">
+      <c r="O390" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P390" s="13">
@@ -27599,7 +27600,7 @@
       <c r="N391" s="10">
         <v>33</v>
       </c>
-      <c r="O391" s="10" t="s">
+      <c r="O391" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P391" s="13">
@@ -27649,7 +27650,7 @@
       <c r="N392" s="10">
         <v>47</v>
       </c>
-      <c r="O392" s="10" t="s">
+      <c r="O392" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P392" s="13">
@@ -27699,7 +27700,7 @@
       <c r="N393" s="10">
         <v>679</v>
       </c>
-      <c r="O393" s="10" t="s">
+      <c r="O393" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P393" s="13">
@@ -27749,7 +27750,7 @@
       <c r="N394" s="10">
         <v>686</v>
       </c>
-      <c r="O394" s="10" t="s">
+      <c r="O394" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P394" s="13">
@@ -27799,7 +27800,7 @@
       <c r="N395" s="10">
         <v>688</v>
       </c>
-      <c r="O395" s="10" t="s">
+      <c r="O395" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P395" s="13">
@@ -27849,7 +27850,7 @@
       <c r="N396" s="10">
         <v>672</v>
       </c>
-      <c r="O396" s="10" t="s">
+      <c r="O396" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P396" s="13">
@@ -27899,7 +27900,7 @@
       <c r="N397" s="10">
         <v>678</v>
       </c>
-      <c r="O397" s="10" t="s">
+      <c r="O397" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P397" s="13">
@@ -27949,7 +27950,7 @@
       <c r="N398" s="10">
         <v>36</v>
       </c>
-      <c r="O398" s="10" t="s">
+      <c r="O398" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P398" s="13">
@@ -27999,7 +28000,7 @@
       <c r="N399" s="10">
         <v>259</v>
       </c>
-      <c r="O399" s="10" t="s">
+      <c r="O399" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P399" s="13">
@@ -28049,7 +28050,7 @@
       <c r="N400" s="10">
         <v>399</v>
       </c>
-      <c r="O400" s="10" t="s">
+      <c r="O400" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P400" s="13">
@@ -28099,7 +28100,7 @@
       <c r="N401" s="10">
         <v>634</v>
       </c>
-      <c r="O401" s="10" t="s">
+      <c r="O401" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P401" s="13">
@@ -28149,7 +28150,7 @@
       <c r="N402" s="10">
         <v>662</v>
       </c>
-      <c r="O402" s="10" t="s">
+      <c r="O402" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P402" s="13">
@@ -28199,7 +28200,7 @@
       <c r="N403" s="10">
         <v>217</v>
       </c>
-      <c r="O403" s="10" t="s">
+      <c r="O403" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P403" s="13">
@@ -28249,7 +28250,7 @@
       <c r="N404" s="10">
         <v>217</v>
       </c>
-      <c r="O404" s="10" t="s">
+      <c r="O404" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P404" s="13">
@@ -28299,7 +28300,7 @@
       <c r="N405" s="10">
         <v>661</v>
       </c>
-      <c r="O405" s="10" t="s">
+      <c r="O405" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P405" s="13">
@@ -28349,7 +28350,7 @@
       <c r="N406" s="10">
         <v>389</v>
       </c>
-      <c r="O406" s="10" t="s">
+      <c r="O406" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P406" s="13">
@@ -28399,7 +28400,7 @@
       <c r="N407" s="10">
         <v>364</v>
       </c>
-      <c r="O407" s="10" t="s">
+      <c r="O407" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P407" s="13">
@@ -28449,7 +28450,7 @@
       <c r="N408" s="10">
         <v>338</v>
       </c>
-      <c r="O408" s="10" t="s">
+      <c r="O408" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P408" s="13">
@@ -28499,7 +28500,7 @@
       <c r="N409" s="10">
         <v>430</v>
       </c>
-      <c r="O409" s="10" t="s">
+      <c r="O409" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P409" s="13">
@@ -28549,7 +28550,7 @@
       <c r="N410" s="10">
         <v>9</v>
       </c>
-      <c r="O410" s="10" t="s">
+      <c r="O410" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P410" s="13">
@@ -28599,7 +28600,7 @@
       <c r="N411" s="10">
         <v>353</v>
       </c>
-      <c r="O411" s="10" t="s">
+      <c r="O411" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P411" s="13">
@@ -28649,7 +28650,7 @@
       <c r="N412" s="10">
         <v>350</v>
       </c>
-      <c r="O412" s="10" t="s">
+      <c r="O412" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P412" s="13">
@@ -28697,7 +28698,7 @@
       <c r="N413" s="10">
         <v>349</v>
       </c>
-      <c r="O413" s="10" t="s">
+      <c r="O413" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P413" s="10"/>
@@ -28745,7 +28746,7 @@
       <c r="N414" s="10">
         <v>-225</v>
       </c>
-      <c r="O414" s="10" t="s">
+      <c r="O414" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P414" s="13">
@@ -28795,7 +28796,7 @@
       <c r="N415" s="10">
         <v>-106</v>
       </c>
-      <c r="O415" s="10" t="s">
+      <c r="O415" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P415" s="13">
@@ -28845,7 +28846,7 @@
       <c r="N416" s="10">
         <v>36</v>
       </c>
-      <c r="O416" s="10" t="s">
+      <c r="O416" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P416" s="13">
@@ -28895,7 +28896,7 @@
       <c r="N417" s="10">
         <v>257</v>
       </c>
-      <c r="O417" s="10" t="s">
+      <c r="O417" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P417" s="13">
@@ -28945,7 +28946,7 @@
       <c r="N418" s="10">
         <v>-94</v>
       </c>
-      <c r="O418" s="10" t="s">
+      <c r="O418" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P418" s="13">
@@ -28995,7 +28996,7 @@
       <c r="N419" s="10">
         <v>24</v>
       </c>
-      <c r="O419" s="10" t="s">
+      <c r="O419" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P419" s="13">
@@ -29045,7 +29046,7 @@
       <c r="N420" s="10">
         <v>9</v>
       </c>
-      <c r="O420" s="10" t="s">
+      <c r="O420" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P420" s="13">
@@ -29085,7 +29086,7 @@
       <c r="L421" s="10"/>
       <c r="M421" s="10"/>
       <c r="N421" s="10"/>
-      <c r="O421" s="10" t="s">
+      <c r="O421" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P421" s="13">
@@ -29135,7 +29136,7 @@
       <c r="N422" s="10">
         <v>-93</v>
       </c>
-      <c r="O422" s="10" t="s">
+      <c r="O422" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P422" s="13">
@@ -29175,7 +29176,7 @@
       <c r="L423" s="10"/>
       <c r="M423" s="10"/>
       <c r="N423" s="10"/>
-      <c r="O423" s="10" t="s">
+      <c r="O423" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P423" s="13">
@@ -29225,7 +29226,7 @@
       <c r="N424" s="10">
         <v>15</v>
       </c>
-      <c r="O424" s="10" t="s">
+      <c r="O424" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P424" s="13">
@@ -29275,7 +29276,7 @@
       <c r="N425" s="10">
         <v>28</v>
       </c>
-      <c r="O425" s="10" t="s">
+      <c r="O425" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P425" s="13">
@@ -29315,7 +29316,7 @@
       <c r="L426" s="10"/>
       <c r="M426" s="10"/>
       <c r="N426" s="10"/>
-      <c r="O426" s="10" t="s">
+      <c r="O426" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P426" s="13">
@@ -29355,7 +29356,7 @@
       <c r="L427" s="10"/>
       <c r="M427" s="10"/>
       <c r="N427" s="10"/>
-      <c r="O427" s="10" t="s">
+      <c r="O427" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P427" s="13">
@@ -29405,7 +29406,7 @@
       <c r="N428" s="10">
         <v>1166</v>
       </c>
-      <c r="O428" s="10" t="s">
+      <c r="O428" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P428" s="13">
@@ -29455,7 +29456,7 @@
       <c r="N429" s="10">
         <v>-104</v>
       </c>
-      <c r="O429" s="10" t="s">
+      <c r="O429" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P429" s="13">
@@ -29495,7 +29496,7 @@
       <c r="L430" s="10"/>
       <c r="M430" s="10"/>
       <c r="N430" s="10"/>
-      <c r="O430" s="10" t="s">
+      <c r="O430" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P430" s="13">
@@ -29545,7 +29546,7 @@
       <c r="N431" s="10">
         <v>206</v>
       </c>
-      <c r="O431" s="10" t="s">
+      <c r="O431" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P431" s="13">
@@ -29585,7 +29586,7 @@
       <c r="L432" s="10"/>
       <c r="M432" s="10"/>
       <c r="N432" s="10"/>
-      <c r="O432" s="10" t="s">
+      <c r="O432" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P432" s="13">
@@ -29635,7 +29636,7 @@
       <c r="N433" s="10">
         <v>5</v>
       </c>
-      <c r="O433" s="10" t="s">
+      <c r="O433" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P433" s="13">
@@ -29675,7 +29676,7 @@
       <c r="L434" s="10"/>
       <c r="M434" s="10"/>
       <c r="N434" s="10"/>
-      <c r="O434" s="10" t="s">
+      <c r="O434" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P434" s="13">
@@ -29725,7 +29726,7 @@
       <c r="N435" s="10">
         <v>206</v>
       </c>
-      <c r="O435" s="10" t="s">
+      <c r="O435" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P435" s="13">
@@ -29765,7 +29766,7 @@
       <c r="L436" s="10"/>
       <c r="M436" s="10"/>
       <c r="N436" s="10"/>
-      <c r="O436" s="10" t="s">
+      <c r="O436" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P436" s="13">
@@ -29805,7 +29806,7 @@
       <c r="L437" s="10"/>
       <c r="M437" s="10"/>
       <c r="N437" s="10"/>
-      <c r="O437" s="10" t="s">
+      <c r="O437" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P437" s="13">
@@ -29845,7 +29846,7 @@
       <c r="L438" s="10"/>
       <c r="M438" s="10"/>
       <c r="N438" s="10"/>
-      <c r="O438" s="10" t="s">
+      <c r="O438" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P438" s="13">
@@ -29895,7 +29896,7 @@
       <c r="N439" s="10">
         <v>65</v>
       </c>
-      <c r="O439" s="10" t="s">
+      <c r="O439" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P439" s="13">
@@ -29945,7 +29946,7 @@
       <c r="N440" s="10">
         <v>121</v>
       </c>
-      <c r="O440" s="10" t="s">
+      <c r="O440" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P440" s="13">
@@ -29985,7 +29986,7 @@
       <c r="L441" s="10"/>
       <c r="M441" s="10"/>
       <c r="N441" s="10"/>
-      <c r="O441" s="10" t="s">
+      <c r="O441" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P441" s="13">
@@ -30025,7 +30026,7 @@
       <c r="L442" s="10"/>
       <c r="M442" s="10"/>
       <c r="N442" s="10"/>
-      <c r="O442" s="10" t="s">
+      <c r="O442" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P442" s="13">
@@ -30073,7 +30074,7 @@
       <c r="N443" s="10">
         <v>268</v>
       </c>
-      <c r="O443" s="10" t="s">
+      <c r="O443" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P443" s="10"/>
@@ -30111,7 +30112,7 @@
       <c r="L444" s="10"/>
       <c r="M444" s="10"/>
       <c r="N444" s="10"/>
-      <c r="O444" s="10" t="s">
+      <c r="O444" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P444" s="13">
@@ -30151,7 +30152,7 @@
       <c r="L445" s="10"/>
       <c r="M445" s="10"/>
       <c r="N445" s="10"/>
-      <c r="O445" s="10" t="s">
+      <c r="O445" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P445" s="13">
@@ -30201,7 +30202,7 @@
       <c r="N446" s="10">
         <v>132</v>
       </c>
-      <c r="O446" s="10" t="s">
+      <c r="O446" s="14" t="s">
         <v>1950</v>
       </c>
       <c r="P446" s="13">
@@ -30251,7 +30252,7 @@
       <c r="N447" s="10">
         <v>178</v>
       </c>
-      <c r="O447" s="10" t="s">
+      <c r="O447" s="14" t="s">
         <v>1949</v>
       </c>
       <c r="P447" s="13">

--- a/drone_data.xlsx
+++ b/drone_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ronak\Desktop\Drone Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://genaero-my.sharepoint.com/personal/ronak_devadiga_generalaeronautics_com/Documents/Product/Drone Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD25A37-3904-4A89-8AF0-CA75DF89740C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B9700DC7-7B13-4793-86FD-3755454981BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3EC885-3814-46C0-9E9C-6E6583F87067}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7428" uniqueCount="2530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7435" uniqueCount="2535">
   <si>
     <t>name</t>
   </si>
@@ -7673,22 +7673,37 @@
     <t>testdroneavb2</t>
   </si>
   <si>
-    <t>12/16/2023</t>
-  </si>
-  <si>
-    <t>2/23/2025</t>
-  </si>
-  <si>
     <t>5/15/2026</t>
   </si>
   <si>
-    <t>4/29/2025</t>
-  </si>
-  <si>
-    <t>1/25/2025</t>
-  </si>
-  <si>
-    <t>12/31/2024</t>
+    <t>7/30/2025</t>
+  </si>
+  <si>
+    <t>5/18/2026</t>
+  </si>
+  <si>
+    <t>3/18/2025</t>
+  </si>
+  <si>
+    <t>5/17/2026</t>
+  </si>
+  <si>
+    <t>5/27/2025</t>
+  </si>
+  <si>
+    <t>5/16/2026</t>
+  </si>
+  <si>
+    <t>6/18/2025</t>
+  </si>
+  <si>
+    <t>10/29/2025</t>
+  </si>
+  <si>
+    <t>7/23/2025</t>
+  </si>
+  <si>
+    <t>5/19/2025</t>
   </si>
 </sst>
 </file>
@@ -10037,6 +10052,7 @@
     <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10336,7 +10352,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J7" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" s="8">
         <v>0</v>
@@ -10344,9 +10360,15 @@
       <c r="L7" s="8">
         <v>0</v>
       </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
+      <c r="M7" s="11">
+        <v>45598</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>1961</v>
+      </c>
+      <c r="O7" s="8">
+        <v>614</v>
+      </c>
       <c r="P7" s="8" t="s">
         <v>1949</v>
       </c>
@@ -10924,7 +10946,7 @@
         <v>84.300335648148149</v>
       </c>
       <c r="J21" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" s="8">
         <v>1</v>
@@ -10975,10 +10997,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J22" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K22" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="8">
         <v>1</v>
@@ -11028,13 +11050,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J23" s="8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K23" s="8">
         <v>0</v>
       </c>
       <c r="L23" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M23" s="11">
         <v>45475</v>
@@ -11081,25 +11103,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J24" s="8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K24" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M24" s="8" t="s">
         <v>1982</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>1995</v>
+        <v>2525</v>
       </c>
       <c r="O24" s="8">
         <v>144</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q24" s="8" t="s">
         <v>1983</v>
@@ -11134,25 +11156,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J25" s="8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K25" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M25" s="11">
         <v>45570</v>
       </c>
       <c r="N25" s="11">
-        <v>45666</v>
+        <v>45697</v>
       </c>
       <c r="O25" s="8">
         <v>162</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q25" s="8" t="s">
         <v>1984</v>
@@ -11187,13 +11209,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J26" s="8">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>1982</v>
@@ -11205,7 +11227,7 @@
         <v>144</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q26" s="8" t="s">
         <v>1985</v>
@@ -11240,13 +11262,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J27" s="8">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K27" s="8">
         <v>0</v>
       </c>
       <c r="L27" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>1986</v>
@@ -11293,13 +11315,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J28" s="8">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K28" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28" s="8">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>1987</v>
@@ -11311,7 +11333,7 @@
         <v>151</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q28" s="8" t="s">
         <v>1988</v>
@@ -11346,13 +11368,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J29" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K29" s="8">
         <v>0</v>
       </c>
       <c r="L29" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M29" s="11">
         <v>45356</v>
@@ -11387,25 +11409,25 @@
         <v>9820914808</v>
       </c>
       <c r="F30" s="10">
-        <v>5.1064467592592591</v>
+        <v>5.1610185185185182</v>
       </c>
       <c r="G30" s="8">
-        <v>7353.2833330000003</v>
+        <v>7431.8666670000002</v>
       </c>
       <c r="H30" s="8">
-        <v>1013.81</v>
+        <v>1019.62</v>
       </c>
       <c r="I30" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J30" s="8">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K30" s="8">
         <v>0</v>
       </c>
       <c r="L30" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M30" s="11">
         <v>45448</v>
@@ -11419,8 +11441,8 @@
       <c r="P30" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="Q30" s="11">
-        <v>46361</v>
+      <c r="Q30" s="8" t="s">
+        <v>2526</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -11452,13 +11474,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J31" s="8">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K31" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M31" s="8" t="s">
         <v>1991</v>
@@ -11470,7 +11492,7 @@
         <v>165</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q31" s="11">
         <v>45728</v>
@@ -11505,13 +11527,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J32" s="8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K32" s="8">
         <v>1</v>
       </c>
       <c r="L32" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M32" s="8" t="s">
         <v>1993</v>
@@ -11558,13 +11580,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J33" s="8">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K33" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M33" s="8" t="s">
         <v>1994</v>
@@ -11576,7 +11598,7 @@
         <v>136</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q33" s="8" t="s">
         <v>1996</v>
@@ -11664,19 +11686,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J35" s="8">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K35" s="8">
         <v>0</v>
       </c>
       <c r="L35" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M35" s="11">
         <v>45569</v>
       </c>
-      <c r="N35" s="8" t="s">
-        <v>2072</v>
+      <c r="N35" s="11">
+        <v>45788</v>
       </c>
       <c r="O35" s="8">
         <v>132</v>
@@ -11717,13 +11739,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J36" s="8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K36" s="8">
         <v>0</v>
       </c>
       <c r="L36" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M36" s="11">
         <v>45476</v>
@@ -11770,13 +11792,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J37" s="8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K37" s="8">
         <v>0</v>
       </c>
       <c r="L37" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M37" s="11">
         <v>45356</v>
@@ -11823,13 +11845,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J38" s="8">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K38" s="8">
         <v>0</v>
       </c>
       <c r="L38" s="8">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M38" s="11">
         <v>45296</v>
@@ -11876,13 +11898,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J39" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K39" s="8">
         <v>0</v>
       </c>
       <c r="L39" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M39" s="11">
         <v>45600</v>
@@ -11929,22 +11951,22 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J40" s="8">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K40" s="8">
         <v>0</v>
       </c>
       <c r="L40" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>2524</v>
+        <v>2000</v>
       </c>
       <c r="N40" s="11">
         <v>46357</v>
       </c>
       <c r="O40" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P40" s="8" t="s">
         <v>1949</v>
@@ -11982,13 +12004,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J41" s="8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K41" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M41" s="8" t="s">
         <v>2001</v>
@@ -12035,7 +12057,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J42" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K42" s="8">
         <v>0</v>
@@ -12194,13 +12216,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J45" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K45" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M45" s="8" t="s">
         <v>2007</v>
@@ -12212,7 +12234,7 @@
         <v>176</v>
       </c>
       <c r="P45" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q45" s="11">
         <v>46000</v>
@@ -12247,13 +12269,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J46" s="8">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="K46" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L46" s="8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M46" s="11">
         <v>45566</v>
@@ -12265,7 +12287,7 @@
         <v>41</v>
       </c>
       <c r="P46" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q46" s="11">
         <v>46330</v>
@@ -12300,13 +12322,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J47" s="8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K47" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L47" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M47" s="11">
         <v>45566</v>
@@ -12318,7 +12340,7 @@
         <v>41</v>
       </c>
       <c r="P47" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q47" s="11">
         <v>46330</v>
@@ -12353,13 +12375,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J48" s="8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K48" s="8">
         <v>1</v>
       </c>
       <c r="L48" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M48" s="11">
         <v>45323</v>
@@ -12404,13 +12426,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J49" s="8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K49" s="8">
         <v>0</v>
       </c>
       <c r="L49" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M49" s="11">
         <v>45475</v>
@@ -12455,13 +12477,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J50" s="8">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K50" s="8">
         <v>0</v>
       </c>
       <c r="L50" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>2013</v>
@@ -12561,25 +12583,25 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J52" s="8">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K52" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M52" s="11">
         <v>45478</v>
       </c>
       <c r="N52" s="8" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="O52" s="8">
         <v>416</v>
       </c>
       <c r="P52" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q52" s="11">
         <v>45964</v>
@@ -12614,13 +12636,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J53" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K53" s="8">
         <v>1</v>
       </c>
       <c r="L53" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M53" s="11">
         <v>45544</v>
@@ -12667,13 +12689,13 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J54" s="8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K54" s="8">
         <v>0</v>
       </c>
       <c r="L54" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="8" t="s">
         <v>2014</v>
@@ -12720,7 +12742,7 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J55" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K55" s="8">
         <v>0</v>
@@ -12773,13 +12795,13 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J56" s="8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K56" s="8">
         <v>0</v>
       </c>
       <c r="L56" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" s="8" t="s">
         <v>2014</v>
@@ -12826,13 +12848,13 @@
         <v>84.338333333333338</v>
       </c>
       <c r="J57" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K57" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M57" s="8" t="s">
         <v>2014</v>
@@ -13091,13 +13113,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J62" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K62" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M62" s="8" t="s">
         <v>2007</v>
@@ -13109,7 +13131,7 @@
         <v>176</v>
       </c>
       <c r="P62" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q62" s="11">
         <v>45910</v>
@@ -13144,7 +13166,7 @@
         <v>84.338333333333338</v>
       </c>
       <c r="J63" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K63" s="8">
         <v>0</v>
@@ -13197,13 +13219,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J64" s="8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K64" s="8">
         <v>0</v>
       </c>
       <c r="L64" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M64" s="11">
         <v>45509</v>
@@ -13250,13 +13272,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J65" s="8">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="K65" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L65" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M65" s="11">
         <v>45417</v>
@@ -13268,7 +13290,7 @@
         <v>157</v>
       </c>
       <c r="P65" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q65" s="11">
         <v>46114</v>
@@ -13303,13 +13325,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J66" s="8">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K66" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M66" s="8" t="s">
         <v>2028</v>
@@ -13321,7 +13343,7 @@
         <v>168</v>
       </c>
       <c r="P66" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q66" s="8" t="s">
         <v>2029</v>
@@ -13409,13 +13431,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J68" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K68" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M68" s="8" t="s">
         <v>2033</v>
@@ -13427,7 +13449,7 @@
         <v>210</v>
       </c>
       <c r="P68" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q68" s="11">
         <v>46058</v>
@@ -13462,13 +13484,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J69" s="8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K69" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M69" s="8" t="s">
         <v>2034</v>
@@ -13480,7 +13502,7 @@
         <v>121</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q69" s="11">
         <v>45668</v>
@@ -13515,13 +13537,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J70" s="8">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K70" s="8">
         <v>0</v>
       </c>
       <c r="L70" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M70" s="11">
         <v>45600</v>
@@ -13568,13 +13590,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J71" s="8">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K71" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M71" s="11">
         <v>45631</v>
@@ -13621,13 +13643,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J72" s="8">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K72" s="8">
         <v>0</v>
       </c>
       <c r="L72" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M72" s="8" t="s">
         <v>1991</v>
@@ -13674,13 +13696,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J73" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K73" s="8">
         <v>0</v>
       </c>
       <c r="L73" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M73" s="8" t="s">
         <v>2038</v>
@@ -13727,13 +13749,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J74" s="8">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="K74" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="8">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M74" s="8" t="s">
         <v>1986</v>
@@ -13745,7 +13767,7 @@
         <v>148</v>
       </c>
       <c r="P74" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q74" s="11">
         <v>45878</v>
@@ -13780,13 +13802,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J75" s="8">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K75" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="8">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M75" s="11">
         <v>45508</v>
@@ -13798,7 +13820,7 @@
         <v>130</v>
       </c>
       <c r="P75" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q75" s="11">
         <v>46329</v>
@@ -13833,13 +13855,13 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J76" s="8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K76" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M76" s="8" t="s">
         <v>2014</v>
@@ -13851,7 +13873,7 @@
         <v>-98</v>
       </c>
       <c r="P76" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q76" s="8" t="s">
         <v>2041</v>
@@ -13884,19 +13906,19 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J77" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K77" s="8">
         <v>0</v>
       </c>
       <c r="L77" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M77" s="8" t="s">
         <v>2014</v>
       </c>
-      <c r="N77" s="8" t="s">
-        <v>2180</v>
+      <c r="N77" s="11">
+        <v>45451</v>
       </c>
       <c r="O77" s="8">
         <v>-98</v>
@@ -13935,13 +13957,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J78" s="8">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K78" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M78" s="11">
         <v>45511</v>
@@ -14094,13 +14116,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J81" s="8">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K81" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M81" s="11">
         <v>45388</v>
@@ -14112,7 +14134,7 @@
         <v>187</v>
       </c>
       <c r="P81" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q81" s="8" t="s">
         <v>2039</v>
@@ -14147,13 +14169,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J82" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K82" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M82" s="8" t="s">
         <v>2046</v>
@@ -14165,7 +14187,7 @@
         <v>178</v>
       </c>
       <c r="P82" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q82" s="8" t="s">
         <v>2048</v>
@@ -14200,13 +14222,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J83" s="8">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K83" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M83" s="11">
         <v>45385</v>
@@ -14218,7 +14240,7 @@
         <v>95</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q83" s="8" t="s">
         <v>2050</v>
@@ -14253,13 +14275,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J84" s="8">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K84" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L84" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M84" s="8" t="s">
         <v>2033</v>
@@ -14306,25 +14328,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J85" s="8">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K85" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L85" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M85" s="11">
         <v>45480</v>
       </c>
-      <c r="N85" s="11">
-        <v>45752</v>
+      <c r="N85" s="8" t="s">
+        <v>2032</v>
       </c>
       <c r="O85" s="8">
         <v>220</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q85" s="11">
         <v>45781</v>
@@ -14465,13 +14487,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J88" s="8">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K88" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M88" s="8" t="s">
         <v>2055</v>
@@ -14518,13 +14540,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J89" s="8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K89" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M89" s="8" t="s">
         <v>2056</v>
@@ -14571,13 +14593,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J90" s="8">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K90" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="8">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M90" s="8" t="s">
         <v>2057</v>
@@ -14589,7 +14611,7 @@
         <v>146</v>
       </c>
       <c r="P90" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q90" s="8" t="s">
         <v>2059</v>
@@ -14624,13 +14646,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J91" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K91" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M91" s="8" t="s">
         <v>2060</v>
@@ -14642,7 +14664,7 @@
         <v>170</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q91" s="11">
         <v>45876</v>
@@ -14677,13 +14699,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J92" s="8">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K92" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M92" s="8" t="s">
         <v>2061</v>
@@ -14695,7 +14717,7 @@
         <v>174</v>
       </c>
       <c r="P92" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q92" s="8" t="s">
         <v>2063</v>
@@ -14718,19 +14740,19 @@
         <v>9820914808</v>
       </c>
       <c r="F93" s="10">
-        <v>3.0335416666666668</v>
+        <v>3.0981944444444443</v>
       </c>
       <c r="G93" s="8">
-        <v>4368.3</v>
+        <v>4461.3999999999996</v>
       </c>
       <c r="H93" s="8">
-        <v>539.46</v>
+        <v>558.99</v>
       </c>
       <c r="I93" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J93" s="8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K93" s="8">
         <v>1</v>
@@ -14750,8 +14772,8 @@
       <c r="P93" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="Q93" s="11">
-        <v>46331</v>
+      <c r="Q93" s="8" t="s">
+        <v>2526</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -14783,13 +14805,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J94" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K94" s="8">
         <v>0</v>
       </c>
       <c r="L94" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M94" s="8" t="s">
         <v>1982</v>
@@ -14889,7 +14911,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J96" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K96" s="8">
         <v>0</v>
@@ -14995,13 +15017,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J98" s="8">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K98" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M98" s="8" t="s">
         <v>2067</v>
@@ -15013,7 +15035,7 @@
         <v>173</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q98" s="8" t="s">
         <v>2069</v>
@@ -15101,13 +15123,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J100" s="8">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K100" s="8">
         <v>0</v>
       </c>
       <c r="L100" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M100" s="8" t="s">
         <v>2030</v>
@@ -15154,13 +15176,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J101" s="8">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K101" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M101" s="8" t="s">
         <v>2071</v>
@@ -15172,7 +15194,7 @@
         <v>177</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q101" s="11">
         <v>45728</v>
@@ -15207,13 +15229,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J102" s="8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K102" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M102" s="8" t="s">
         <v>1961</v>
@@ -15225,7 +15247,7 @@
         <v>152</v>
       </c>
       <c r="P102" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q102" s="11">
         <v>45787</v>
@@ -15260,13 +15282,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J103" s="8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K103" s="8">
         <v>0</v>
       </c>
       <c r="L103" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M103" s="8" t="s">
         <v>2073</v>
@@ -15313,13 +15335,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J104" s="8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K104" s="8">
         <v>0</v>
       </c>
       <c r="L104" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M104" s="8" t="s">
         <v>2073</v>
@@ -15366,13 +15388,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J105" s="8">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K105" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M105" s="8" t="s">
         <v>2076</v>
@@ -15384,7 +15406,7 @@
         <v>172</v>
       </c>
       <c r="P105" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q105" s="11">
         <v>46358</v>
@@ -15419,13 +15441,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J106" s="8">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K106" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L106" s="8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M106" s="11">
         <v>45570</v>
@@ -15525,13 +15547,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J108" s="8">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K108" s="8">
         <v>0</v>
       </c>
       <c r="L108" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M108" s="8" t="s">
         <v>2078</v>
@@ -15578,13 +15600,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J109" s="8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K109" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M109" s="8" t="s">
         <v>2079</v>
@@ -15596,7 +15618,7 @@
         <v>197</v>
       </c>
       <c r="P109" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q109" s="11">
         <v>46144</v>
@@ -15684,13 +15706,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J111" s="8">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K111" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L111" s="8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M111" s="8" t="s">
         <v>2080</v>
@@ -15790,13 +15812,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J113" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K113" s="8">
         <v>0</v>
       </c>
       <c r="L113" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M113" s="8" t="s">
         <v>2083</v>
@@ -15843,13 +15865,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J114" s="8">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K114" s="8">
         <v>0</v>
       </c>
       <c r="L114" s="8">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M114" s="8" t="s">
         <v>2067</v>
@@ -15896,13 +15918,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J115" s="8">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K115" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M115" s="8" t="s">
         <v>2076</v>
@@ -15914,7 +15936,7 @@
         <v>172</v>
       </c>
       <c r="P115" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q115" s="8" t="s">
         <v>2086</v>
@@ -16002,13 +16024,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J117" s="8">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K117" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M117" s="8" t="s">
         <v>2028</v>
@@ -16020,7 +16042,7 @@
         <v>168</v>
       </c>
       <c r="P117" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q117" s="11">
         <v>45728</v>
@@ -16096,22 +16118,22 @@
         <v>9820914808</v>
       </c>
       <c r="F119" s="10">
-        <v>3.2098495370370372</v>
+        <v>3.3239004629629632</v>
       </c>
       <c r="G119" s="8">
-        <v>4622.1833329999999</v>
+        <v>4786.4166670000004</v>
       </c>
       <c r="H119" s="8">
-        <v>727.5</v>
+        <v>762.14</v>
       </c>
       <c r="I119" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J119" s="8">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K119" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="8">
         <v>0</v>
@@ -16161,7 +16183,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J120" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K120" s="8">
         <v>0</v>
@@ -16214,19 +16236,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J121" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K121" s="8">
         <v>0</v>
       </c>
       <c r="L121" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121" s="8" t="s">
         <v>2038</v>
       </c>
       <c r="N121" s="8" t="s">
-        <v>2272</v>
+        <v>2093</v>
       </c>
       <c r="O121" s="8">
         <v>206</v>
@@ -16267,13 +16289,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J122" s="8">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K122" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L122" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M122" s="8" t="s">
         <v>2056</v>
@@ -16426,13 +16448,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J125" s="8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K125" s="8">
         <v>0</v>
       </c>
       <c r="L125" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M125" s="11">
         <v>45358</v>
@@ -16479,13 +16501,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J126" s="8">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K126" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M126" s="8" t="s">
         <v>2088</v>
@@ -16497,7 +16519,7 @@
         <v>166</v>
       </c>
       <c r="P126" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q126" s="8" t="s">
         <v>2096</v>
@@ -16532,25 +16554,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J127" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K127" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L127" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M127" s="11">
         <v>45570</v>
       </c>
-      <c r="N127" s="11">
-        <v>45967</v>
+      <c r="N127" s="8" t="s">
+        <v>1996</v>
       </c>
       <c r="O127" s="8">
         <v>162</v>
       </c>
       <c r="P127" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q127" s="11">
         <v>45995</v>
@@ -16585,13 +16607,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J128" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K128" s="8">
         <v>0</v>
       </c>
       <c r="L128" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M128" s="11">
         <v>45478</v>
@@ -16638,13 +16660,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J129" s="8">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K129" s="8">
         <v>0</v>
       </c>
       <c r="L129" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M129" s="11">
         <v>45358</v>
@@ -16691,13 +16713,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J130" s="8">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K130" s="8">
         <v>0</v>
       </c>
       <c r="L130" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M130" s="11">
         <v>45419</v>
@@ -16744,13 +16766,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J131" s="8">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K131" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L131" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M131" s="8" t="s">
         <v>2038</v>
@@ -16762,7 +16784,7 @@
         <v>206</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q131" s="8" t="s">
         <v>2099</v>
@@ -16797,7 +16819,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J132" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K132" s="8">
         <v>0</v>
@@ -16903,13 +16925,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J134" s="8">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K134" s="8">
         <v>0</v>
       </c>
       <c r="L134" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M134" s="8" t="s">
         <v>2103</v>
@@ -17009,13 +17031,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J136" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K136" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M136" s="8" t="s">
         <v>2105</v>
@@ -17027,7 +17049,7 @@
         <v>205</v>
       </c>
       <c r="P136" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q136" s="8" t="s">
         <v>2085</v>
@@ -17168,13 +17190,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J139" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K139" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L139" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M139" s="8" t="s">
         <v>2106</v>
@@ -17209,13 +17231,13 @@
         <v>9820914808</v>
       </c>
       <c r="F140" s="10">
-        <v>2.7548842592592591</v>
+        <v>1.8803240740740741</v>
       </c>
       <c r="G140" s="8">
-        <v>3967.0333329999999</v>
+        <v>2707.666667</v>
       </c>
       <c r="H140" s="8">
-        <v>392.03</v>
+        <v>288.31</v>
       </c>
       <c r="I140" s="10">
         <v>84.29965277777778</v>
@@ -17241,8 +17263,8 @@
       <c r="P140" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="Q140" s="11">
-        <v>46331</v>
+      <c r="Q140" s="8" t="s">
+        <v>2528</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -17274,13 +17296,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J141" s="8">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K141" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L141" s="8">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M141" s="8" t="s">
         <v>2038</v>
@@ -17315,25 +17337,25 @@
         <v>9820914808</v>
       </c>
       <c r="F142" s="10">
-        <v>1.3481944444444445</v>
+        <v>1.3651273148148149</v>
       </c>
       <c r="G142" s="8">
-        <v>1941.4</v>
+        <v>1965.7833330000001</v>
       </c>
       <c r="H142" s="8">
-        <v>117.55</v>
+        <v>118.72</v>
       </c>
       <c r="I142" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J142" s="8">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K142" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L142" s="8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M142" s="8" t="s">
         <v>2051</v>
@@ -17345,10 +17367,10 @@
         <v>169</v>
       </c>
       <c r="P142" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q142" s="8" t="s">
-        <v>2109</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -17380,13 +17402,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J143" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K143" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M143" s="8" t="s">
         <v>2038</v>
@@ -17398,7 +17420,7 @@
         <v>206</v>
       </c>
       <c r="P143" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q143" s="11">
         <v>45940</v>
@@ -17421,25 +17443,25 @@
         <v>9820914808</v>
       </c>
       <c r="F144" s="10">
-        <v>4.0775694444444444</v>
+        <v>4.0811689814814818</v>
       </c>
       <c r="G144" s="8">
-        <v>5871.7</v>
+        <v>5876.8833329999998</v>
       </c>
       <c r="H144" s="8">
-        <v>484.32</v>
+        <v>484.68</v>
       </c>
       <c r="I144" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J144" s="8">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K144" s="8">
         <v>0</v>
       </c>
       <c r="L144" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M144" s="8" t="s">
         <v>2028</v>
@@ -17453,8 +17475,8 @@
       <c r="P144" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="Q144" s="8" t="s">
-        <v>2110</v>
+      <c r="Q144" s="11">
+        <v>45973</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -17486,13 +17508,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J145" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K145" s="8">
         <v>1</v>
       </c>
       <c r="L145" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M145" s="8" t="s">
         <v>2111</v>
@@ -17539,13 +17561,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J146" s="8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K146" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L146" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M146" s="8" t="s">
         <v>2111</v>
@@ -17557,7 +17579,7 @@
         <v>198</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q146" s="11">
         <v>45968</v>
@@ -17592,13 +17614,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J147" s="8">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K147" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L147" s="8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M147" s="8" t="s">
         <v>2067</v>
@@ -17610,7 +17632,7 @@
         <v>173</v>
       </c>
       <c r="P147" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q147" s="11">
         <v>45967</v>
@@ -17645,13 +17667,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J148" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K148" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L148" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M148" s="8" t="s">
         <v>2113</v>
@@ -17751,25 +17773,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J150" s="8">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K150" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L150" s="8">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M150" s="8" t="s">
         <v>2042</v>
       </c>
-      <c r="N150" s="8" t="s">
-        <v>2035</v>
+      <c r="N150" s="11">
+        <v>45816</v>
       </c>
       <c r="O150" s="8">
         <v>179</v>
       </c>
       <c r="P150" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q150" s="8" t="s">
         <v>2035</v>
@@ -17804,13 +17826,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J151" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K151" s="8">
         <v>0</v>
       </c>
       <c r="L151" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M151" s="8" t="s">
         <v>2114</v>
@@ -17857,13 +17879,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J152" s="8">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K152" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M152" s="11">
         <v>45632</v>
@@ -17875,7 +17897,7 @@
         <v>195</v>
       </c>
       <c r="P152" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q152" s="8" t="s">
         <v>2116</v>
@@ -17963,13 +17985,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J154" s="8">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K154" s="8">
         <v>0</v>
       </c>
       <c r="L154" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M154" s="8" t="s">
         <v>2046</v>
@@ -18016,10 +18038,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J155" s="8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K155" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" s="8">
         <v>1</v>
@@ -18069,13 +18091,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J156" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K156" s="8">
         <v>0</v>
       </c>
       <c r="L156" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M156" s="11">
         <v>45387</v>
@@ -18122,13 +18144,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J157" s="8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K157" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M157" s="8" t="s">
         <v>2007</v>
@@ -18140,7 +18162,7 @@
         <v>176</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q157" s="11">
         <v>46083</v>
@@ -18175,19 +18197,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J158" s="8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K158" s="8">
         <v>0</v>
       </c>
       <c r="L158" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M158" s="8" t="s">
         <v>2056</v>
       </c>
       <c r="N158" s="11">
-        <v>45362</v>
+        <v>45484</v>
       </c>
       <c r="O158" s="8">
         <v>204</v>
@@ -18228,13 +18250,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J159" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K159" s="8">
         <v>0</v>
       </c>
       <c r="L159" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M159" s="11">
         <v>45359</v>
@@ -18281,13 +18303,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J160" s="8">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="K160" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L160" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M160" s="8" t="s">
         <v>2042</v>
@@ -18299,7 +18321,7 @@
         <v>179</v>
       </c>
       <c r="P160" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q160" s="8" t="s">
         <v>2121</v>
@@ -18334,13 +18356,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J161" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K161" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L161" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M161" s="8" t="s">
         <v>2122</v>
@@ -18352,7 +18374,7 @@
         <v>258</v>
       </c>
       <c r="P161" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q161" s="11">
         <v>45785</v>
@@ -18387,13 +18409,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J162" s="8">
+        <v>36</v>
+      </c>
+      <c r="K162" s="8">
+        <v>1</v>
+      </c>
+      <c r="L162" s="8">
         <v>21</v>
-      </c>
-      <c r="K162" s="8">
-        <v>0</v>
-      </c>
-      <c r="L162" s="8">
-        <v>6</v>
       </c>
       <c r="M162" s="8" t="s">
         <v>2067</v>
@@ -18405,7 +18427,7 @@
         <v>173</v>
       </c>
       <c r="P162" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q162" s="8" t="s">
         <v>2123</v>
@@ -18440,13 +18462,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J163" s="8">
+        <v>7</v>
+      </c>
+      <c r="K163" s="8">
+        <v>2</v>
+      </c>
+      <c r="L163" s="8">
         <v>4</v>
-      </c>
-      <c r="K163" s="8">
-        <v>0</v>
-      </c>
-      <c r="L163" s="8">
-        <v>1</v>
       </c>
       <c r="M163" s="11">
         <v>45330</v>
@@ -18458,7 +18480,7 @@
         <v>246</v>
       </c>
       <c r="P163" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q163" s="8" t="s">
         <v>2124</v>
@@ -18493,13 +18515,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J164" s="8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K164" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M164" s="8" t="s">
         <v>2007</v>
@@ -18511,7 +18533,7 @@
         <v>176</v>
       </c>
       <c r="P164" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q164" s="8" t="s">
         <v>2125</v>
@@ -18546,19 +18568,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J165" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K165" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L165" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M165" s="11">
         <v>45297</v>
       </c>
       <c r="N165" s="8" t="s">
-        <v>2126</v>
+        <v>2058</v>
       </c>
       <c r="O165" s="8">
         <v>184</v>
@@ -18599,13 +18621,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J166" s="8">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K166" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M166" s="8" t="s">
         <v>2127</v>
@@ -18617,7 +18639,7 @@
         <v>242</v>
       </c>
       <c r="P166" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q166" s="11">
         <v>46296</v>
@@ -18705,10 +18727,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J168" s="8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K168" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L168" s="8">
         <v>0</v>
@@ -18758,13 +18780,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J169" s="8">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K169" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L169" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M169" s="11">
         <v>45481</v>
@@ -18811,25 +18833,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J170" s="8">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K170" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L170" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M170" s="11">
         <v>45359</v>
       </c>
-      <c r="N170" s="8" t="s">
-        <v>2086</v>
+      <c r="N170" s="11">
+        <v>46056</v>
       </c>
       <c r="O170" s="8">
         <v>247</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q170" s="11">
         <v>46270</v>
@@ -18864,7 +18886,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J171" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K171" s="8">
         <v>1</v>
@@ -18970,13 +18992,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J173" s="8">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K173" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L173" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M173" s="8" t="s">
         <v>2103</v>
@@ -18988,10 +19010,10 @@
         <v>181</v>
       </c>
       <c r="P173" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q173" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
@@ -19023,13 +19045,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J174" s="8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K174" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L174" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M174" s="11">
         <v>45632</v>
@@ -19178,13 +19200,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J177" s="8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K177" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L177" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M177" s="8" t="s">
         <v>2135</v>
@@ -19196,7 +19218,7 @@
         <v>226</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q177" s="8" t="s">
         <v>2136</v>
@@ -19231,10 +19253,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J178" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K178" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" s="8">
         <v>0</v>
@@ -19284,13 +19306,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J179" s="8">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K179" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L179" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M179" s="8" t="s">
         <v>2070</v>
@@ -19325,25 +19347,25 @@
         <v>9820914808</v>
       </c>
       <c r="F180" s="10">
-        <v>2.3748148148148149</v>
+        <v>2.4408564814814815</v>
       </c>
       <c r="G180" s="8">
-        <v>3419.7333330000001</v>
+        <v>3514.833333</v>
       </c>
       <c r="H180" s="8">
-        <v>475.18</v>
+        <v>489.08</v>
       </c>
       <c r="I180" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J180" s="8">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K180" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L180" s="8">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M180" s="8" t="s">
         <v>2030</v>
@@ -19357,8 +19379,8 @@
       <c r="P180" s="8" t="s">
         <v>1948</v>
       </c>
-      <c r="Q180" s="11">
-        <v>46361</v>
+      <c r="Q180" s="8" t="s">
+        <v>2528</v>
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
@@ -19390,13 +19412,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J181" s="8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K181" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L181" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M181" s="8" t="s">
         <v>2138</v>
@@ -19408,7 +19430,7 @@
         <v>275</v>
       </c>
       <c r="P181" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q181" s="8" t="s">
         <v>2131</v>
@@ -19443,13 +19465,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J182" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K182" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L182" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M182" s="8" t="s">
         <v>2130</v>
@@ -19461,7 +19483,7 @@
         <v>180</v>
       </c>
       <c r="P182" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q182" s="8" t="s">
         <v>2115</v>
@@ -19496,13 +19518,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J183" s="8">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K183" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L183" s="8">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M183" s="11">
         <v>45329</v>
@@ -19514,7 +19536,7 @@
         <v>215</v>
       </c>
       <c r="P183" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q183" s="8" t="s">
         <v>2097</v>
@@ -19549,19 +19571,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J184" s="8">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K184" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L184" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M184" s="8" t="s">
         <v>2139</v>
       </c>
       <c r="N184" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="O184" s="8">
         <v>271</v>
@@ -19602,13 +19624,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J185" s="8">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K185" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L185" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M185" s="8" t="s">
         <v>2021</v>
@@ -19655,25 +19677,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J186" s="8">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K186" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L186" s="8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M186" s="8" t="s">
         <v>2051</v>
       </c>
       <c r="N186" s="8" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="O186" s="8">
         <v>169</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q186" s="8" t="s">
         <v>2140</v>
@@ -19708,13 +19730,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J187" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K187" s="8">
         <v>0</v>
       </c>
       <c r="L187" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M187" s="8" t="s">
         <v>2021</v>
@@ -19761,13 +19783,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J188" s="8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K188" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M188" s="11">
         <v>45299</v>
@@ -19779,7 +19801,7 @@
         <v>245</v>
       </c>
       <c r="P188" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q188" s="8" t="s">
         <v>2108</v>
@@ -19814,13 +19836,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J189" s="8">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K189" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L189" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M189" s="8" t="s">
         <v>2105</v>
@@ -19867,13 +19889,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J190" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K190" s="8">
         <v>0</v>
       </c>
       <c r="L190" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M190" s="11">
         <v>45328</v>
@@ -19920,13 +19942,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J191" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K191" s="8">
         <v>0</v>
       </c>
       <c r="L191" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M191" s="8" t="s">
         <v>2143</v>
@@ -19973,13 +19995,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J192" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K192" s="8">
         <v>0</v>
       </c>
       <c r="L192" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M192" s="8" t="s">
         <v>2145</v>
@@ -20026,10 +20048,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J193" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K193" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L193" s="8">
         <v>0</v>
@@ -20079,25 +20101,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J194" s="8">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K194" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L194" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M194" s="8" t="s">
         <v>2046</v>
       </c>
       <c r="N194" s="8" t="s">
-        <v>2006</v>
+        <v>2096</v>
       </c>
       <c r="O194" s="8">
         <v>178</v>
       </c>
       <c r="P194" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q194" s="8" t="s">
         <v>2006</v>
@@ -20185,13 +20207,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J196" s="8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K196" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L196" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M196" s="11">
         <v>45450</v>
@@ -20238,13 +20260,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J197" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K197" s="8">
         <v>1</v>
       </c>
       <c r="L197" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M197" s="11">
         <v>45328</v>
@@ -20291,13 +20313,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J198" s="8">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K198" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L198" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M198" s="8" t="s">
         <v>2038</v>
@@ -20309,7 +20331,7 @@
         <v>206</v>
       </c>
       <c r="P198" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q198" s="11">
         <v>46300</v>
@@ -20434,25 +20456,25 @@
         <v>9820914808</v>
       </c>
       <c r="F201" s="10">
-        <v>5.6635300925925929</v>
+        <v>5.7191550925925929</v>
       </c>
       <c r="G201" s="8">
-        <v>8155.4833330000001</v>
+        <v>8235.5833330000005</v>
       </c>
       <c r="H201" s="8">
-        <v>4954748235</v>
+        <v>4954748242</v>
       </c>
       <c r="I201" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J201" s="8">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K201" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L201" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M201" s="8" t="s">
         <v>2030</v>
@@ -20467,7 +20489,7 @@
         <v>1949</v>
       </c>
       <c r="Q201" s="8" t="s">
-        <v>2109</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
@@ -20487,10 +20509,10 @@
         <v>9820914808</v>
       </c>
       <c r="F202" s="9">
-        <v>0.58333333333333337</v>
+        <v>0.59725694444444444</v>
       </c>
       <c r="G202" s="8">
-        <v>840</v>
+        <v>860.05</v>
       </c>
       <c r="H202" s="8">
         <v>0</v>
@@ -20605,13 +20627,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J204" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K204" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L204" s="8">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M204" s="8" t="s">
         <v>1961</v>
@@ -20623,7 +20645,7 @@
         <v>152</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q204" s="11">
         <v>46002</v>
@@ -20658,25 +20680,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J205" s="8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K205" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M205" s="8" t="s">
         <v>2076</v>
       </c>
-      <c r="N205" s="11">
-        <v>45725</v>
+      <c r="N205" s="8" t="s">
+        <v>2150</v>
       </c>
       <c r="O205" s="8">
         <v>172</v>
       </c>
       <c r="P205" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q205" s="11">
         <v>45666</v>
@@ -20711,13 +20733,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J206" s="8">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K206" s="8">
         <v>2</v>
       </c>
       <c r="L206" s="8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M206" s="8" t="s">
         <v>2042</v>
@@ -20764,25 +20786,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J207" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K207" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M207" s="8" t="s">
         <v>2056</v>
       </c>
-      <c r="N207" s="8" t="s">
-        <v>2302</v>
+      <c r="N207" s="11">
+        <v>45879</v>
       </c>
       <c r="O207" s="8">
         <v>204</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q207" s="11">
         <v>45694</v>
@@ -20817,13 +20839,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J208" s="8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K208" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L208" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M208" s="8" t="s">
         <v>2106</v>
@@ -20870,13 +20892,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J209" s="8">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K209" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L209" s="8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M209" s="11">
         <v>45543</v>
@@ -20923,13 +20945,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J210" s="8">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K210" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L210" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M210" s="8" t="s">
         <v>2082</v>
@@ -20976,13 +20998,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J211" s="8">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K211" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L211" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M211" s="11">
         <v>45450</v>
@@ -21029,13 +21051,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J212" s="8">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K212" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L212" s="8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M212" s="11">
         <v>45510</v>
@@ -21070,25 +21092,25 @@
         <v>9820914808</v>
       </c>
       <c r="F213" s="10">
-        <v>2.927997685185185</v>
+        <v>2.9310648148148148</v>
       </c>
       <c r="G213" s="8">
-        <v>4216.3166670000001</v>
+        <v>4220.7333330000001</v>
       </c>
       <c r="H213" s="8">
-        <v>373.16</v>
+        <v>373.2</v>
       </c>
       <c r="I213" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J213" s="8">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K213" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213" s="8">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M213" s="11">
         <v>45450</v>
@@ -21100,10 +21122,10 @@
         <v>219</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q213" s="8" t="s">
-        <v>2155</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
@@ -21135,25 +21157,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J214" s="8">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="K214" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L214" s="8">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M214" s="8" t="s">
         <v>2042</v>
       </c>
       <c r="N214" s="11">
-        <v>45933</v>
+        <v>45873</v>
       </c>
       <c r="O214" s="8">
         <v>179</v>
       </c>
       <c r="P214" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q214" s="11">
         <v>45841</v>
@@ -21175,26 +21197,26 @@
       <c r="E215" s="8">
         <v>9820914808</v>
       </c>
-      <c r="F215" s="9">
-        <v>0.99612268518518521</v>
+      <c r="F215" s="10">
+        <v>1.0184259259259258</v>
       </c>
       <c r="G215" s="8">
-        <v>1434.416667</v>
+        <v>1466.5333330000001</v>
       </c>
       <c r="H215" s="8">
-        <v>114.39</v>
+        <v>117.52</v>
       </c>
       <c r="I215" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J215" s="8">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K215" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L215" s="8">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="M215" s="11">
         <v>45419</v>
@@ -21206,10 +21228,10 @@
         <v>218</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q215" s="8" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
@@ -21241,19 +21263,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J216" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K216" s="8">
         <v>0</v>
       </c>
       <c r="L216" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M216" s="11">
         <v>45359</v>
       </c>
       <c r="N216" s="8" t="s">
-        <v>2275</v>
+        <v>2156</v>
       </c>
       <c r="O216" s="8">
         <v>247</v>
@@ -21400,19 +21422,19 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J219" s="8">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K219" s="8">
         <v>0</v>
       </c>
       <c r="L219" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M219" s="11">
         <v>45511</v>
       </c>
       <c r="N219" s="11">
-        <v>45724</v>
+        <v>45697</v>
       </c>
       <c r="O219" s="8">
         <v>-409</v>
@@ -21453,13 +21475,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J220" s="8">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K220" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L220" s="8">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M220" s="8" t="s">
         <v>2158</v>
@@ -21471,7 +21493,7 @@
         <v>234</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q220" s="8" t="s">
         <v>2159</v>
@@ -21506,13 +21528,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J221" s="8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K221" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L221" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M221" s="8" t="s">
         <v>2114</v>
@@ -21524,7 +21546,7 @@
         <v>182</v>
       </c>
       <c r="P221" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q221" s="8" t="s">
         <v>2005</v>
@@ -21559,7 +21581,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J222" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K222" s="8">
         <v>0</v>
@@ -21612,13 +21634,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J223" s="8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K223" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L223" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M223" s="8" t="s">
         <v>2162</v>
@@ -21630,7 +21652,7 @@
         <v>232</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q223" s="8" t="s">
         <v>2164</v>
@@ -21665,13 +21687,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J224" s="8">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K224" s="8">
         <v>0</v>
       </c>
       <c r="L224" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M224" s="11">
         <v>45387</v>
@@ -21718,13 +21740,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J225" s="8">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K225" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L225" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M225" s="8" t="s">
         <v>2103</v>
@@ -21736,7 +21758,7 @@
         <v>181</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q225" s="8" t="s">
         <v>2165</v>
@@ -21771,13 +21793,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J226" s="8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K226" s="8">
         <v>0</v>
       </c>
       <c r="L226" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M226" s="11">
         <v>45299</v>
@@ -21792,7 +21814,7 @@
         <v>1949</v>
       </c>
       <c r="Q226" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
@@ -21824,13 +21846,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J227" s="8">
+        <v>7</v>
+      </c>
+      <c r="K227" s="8">
+        <v>0</v>
+      </c>
+      <c r="L227" s="8">
         <v>4</v>
-      </c>
-      <c r="K227" s="8">
-        <v>0</v>
-      </c>
-      <c r="L227" s="8">
-        <v>1</v>
       </c>
       <c r="M227" s="8" t="s">
         <v>2129</v>
@@ -21877,7 +21899,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J228" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K228" s="8">
         <v>0</v>
@@ -21930,7 +21952,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J229" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K229" s="8">
         <v>0</v>
@@ -22132,13 +22154,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J233" s="8">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K233" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M233" s="8" t="s">
         <v>2170</v>
@@ -22185,13 +22207,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J234" s="8">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K234" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L234" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M234" s="8" t="s">
         <v>2173</v>
@@ -22238,10 +22260,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J235" s="8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K235" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L235" s="8">
         <v>0</v>
@@ -22291,25 +22313,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J236" s="8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K236" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L236" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M236" s="11">
         <v>45572</v>
       </c>
       <c r="N236" s="8" t="s">
-        <v>1981</v>
+        <v>2172</v>
       </c>
       <c r="O236" s="8">
         <v>223</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q236" s="8" t="s">
         <v>2174</v>
@@ -22344,13 +22366,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J237" s="8">
+        <v>16</v>
+      </c>
+      <c r="K237" s="8">
+        <v>3</v>
+      </c>
+      <c r="L237" s="8">
         <v>10</v>
-      </c>
-      <c r="K237" s="8">
-        <v>2</v>
-      </c>
-      <c r="L237" s="8">
-        <v>4</v>
       </c>
       <c r="M237" s="11">
         <v>45602</v>
@@ -22450,13 +22472,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J239" s="8">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K239" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L239" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M239" s="8" t="s">
         <v>2177</v>
@@ -22468,7 +22490,7 @@
         <v>167</v>
       </c>
       <c r="P239" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q239" s="8" t="s">
         <v>1997</v>
@@ -22503,13 +22525,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J240" s="8">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K240" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L240" s="8">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M240" s="8" t="s">
         <v>2004</v>
@@ -22521,7 +22543,7 @@
         <v>208</v>
       </c>
       <c r="P240" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q240" s="11">
         <v>45696</v>
@@ -22556,13 +22578,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J241" s="8">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K241" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L241" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M241" s="11">
         <v>45329</v>
@@ -22574,7 +22596,7 @@
         <v>215</v>
       </c>
       <c r="P241" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q241" s="8" t="s">
         <v>1998</v>
@@ -22609,13 +22631,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J242" s="8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K242" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L242" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M242" s="8" t="s">
         <v>2178</v>
@@ -22662,13 +22684,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J243" s="8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K243" s="8">
         <v>0</v>
       </c>
       <c r="L243" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M243" s="8" t="s">
         <v>2139</v>
@@ -22811,7 +22833,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J246" s="8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K246" s="8">
         <v>0</v>
@@ -22993,22 +23015,22 @@
         <v>9820914808</v>
       </c>
       <c r="F250" s="9">
-        <v>0.35905092592592591</v>
+        <v>0.57984953703703701</v>
       </c>
       <c r="G250" s="8">
-        <v>517.03333329999998</v>
+        <v>834.98333330000003</v>
       </c>
       <c r="H250" s="8">
-        <v>51.8</v>
+        <v>96.26</v>
       </c>
       <c r="I250" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J250" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K250" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L250" s="8">
         <v>0</v>
@@ -23026,7 +23048,7 @@
         <v>1949</v>
       </c>
       <c r="Q250" s="8" t="s">
-        <v>2155</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="251" spans="1:17" x14ac:dyDescent="0.25">
@@ -23058,13 +23080,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J251" s="8">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K251" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L251" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M251" s="11">
         <v>45840</v>
@@ -23076,7 +23098,7 @@
         <v>435</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q251" s="11">
         <v>45695</v>
@@ -23111,13 +23133,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J252" s="8">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K252" s="8">
         <v>1</v>
       </c>
       <c r="L252" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M252" s="11">
         <v>45423</v>
@@ -23217,19 +23239,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J254" s="8">
+        <v>29</v>
+      </c>
+      <c r="K254" s="8">
+        <v>6</v>
+      </c>
+      <c r="L254" s="8">
         <v>16</v>
-      </c>
-      <c r="K254" s="8">
-        <v>1</v>
-      </c>
-      <c r="L254" s="8">
-        <v>4</v>
       </c>
       <c r="M254" s="8" t="s">
         <v>2129</v>
       </c>
       <c r="N254" s="8" t="s">
-        <v>2184</v>
+        <v>2172</v>
       </c>
       <c r="O254" s="8">
         <v>323</v>
@@ -23323,13 +23345,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J256" s="8">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K256" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L256" s="8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M256" s="8" t="s">
         <v>2187</v>
@@ -23376,13 +23398,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J257" s="8">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K257" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L257" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M257" s="11">
         <v>45300</v>
@@ -23429,13 +23451,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J258" s="8">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K258" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L258" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M258" s="8" t="s">
         <v>2189</v>
@@ -23447,7 +23469,7 @@
         <v>260</v>
       </c>
       <c r="P258" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q258" s="11">
         <v>46270</v>
@@ -23482,13 +23504,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J259" s="8">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K259" s="8">
         <v>0</v>
       </c>
       <c r="L259" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M259" s="8" t="s">
         <v>2190</v>
@@ -23535,19 +23557,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J260" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K260" s="8">
         <v>0</v>
       </c>
       <c r="L260" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M260" s="8" t="s">
         <v>2035</v>
       </c>
-      <c r="N260" s="11">
-        <v>45875</v>
+      <c r="N260" s="8" t="s">
+        <v>2192</v>
       </c>
       <c r="O260" s="8">
         <v>423</v>
@@ -23576,25 +23598,25 @@
         <v>9820914808</v>
       </c>
       <c r="F261" s="10">
-        <v>1.2101504629629629</v>
+        <v>1.201712962962963</v>
       </c>
       <c r="G261" s="8">
-        <v>1742.616667</v>
+        <v>1730.4666669999999</v>
       </c>
       <c r="H261" s="8">
-        <v>222.23</v>
+        <v>221.28</v>
       </c>
       <c r="I261" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J261" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K261" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L261" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M261" s="8" t="s">
         <v>2193</v>
@@ -23606,10 +23628,10 @@
         <v>298</v>
       </c>
       <c r="P261" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q261" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="262" spans="1:17" x14ac:dyDescent="0.25">
@@ -23790,13 +23812,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J265" s="8">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K265" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L265" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M265" s="8" t="s">
         <v>2196</v>
@@ -23808,7 +23830,7 @@
         <v>303</v>
       </c>
       <c r="P265" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q265" s="8" t="s">
         <v>1990</v>
@@ -23843,10 +23865,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J266" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K266" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L266" s="8">
         <v>0</v>
@@ -23854,8 +23876,8 @@
       <c r="M266" s="8" t="s">
         <v>2196</v>
       </c>
-      <c r="N266" s="11">
-        <v>45962</v>
+      <c r="N266" s="8" t="s">
+        <v>2531</v>
       </c>
       <c r="O266" s="8">
         <v>303</v>
@@ -23896,7 +23918,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J267" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K267" s="8">
         <v>0</v>
@@ -23949,13 +23971,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J268" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K268" s="8">
         <v>0</v>
       </c>
       <c r="L268" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M268" s="11">
         <v>45482</v>
@@ -24002,13 +24024,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J269" s="8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K269" s="8">
         <v>0</v>
       </c>
       <c r="L269" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M269" s="8" t="s">
         <v>2198</v>
@@ -24098,13 +24120,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J271" s="8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K271" s="8">
         <v>0</v>
       </c>
       <c r="L271" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M271" s="8" t="s">
         <v>2194</v>
@@ -24151,13 +24173,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J272" s="8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K272" s="8">
         <v>0</v>
       </c>
       <c r="L272" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M272" s="8" t="s">
         <v>2195</v>
@@ -24363,19 +24385,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J276" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K276" s="8">
         <v>0</v>
       </c>
       <c r="L276" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M276" s="11">
         <v>45574</v>
       </c>
       <c r="N276" s="8" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="O276" s="8">
         <v>285</v>
@@ -24469,13 +24491,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J278" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K278" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M278" s="11">
         <v>45574</v>
@@ -24628,25 +24650,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J281" s="8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K281" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L281" s="8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M281" s="8" t="s">
         <v>2024</v>
       </c>
       <c r="N281" s="8" t="s">
-        <v>2528</v>
+        <v>2207</v>
       </c>
       <c r="O281" s="8">
         <v>267</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q281" s="8" t="s">
         <v>2208</v>
@@ -24681,13 +24703,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J282" s="8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K282" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L282" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M282" s="8" t="s">
         <v>2199</v>
@@ -24734,13 +24756,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J283" s="8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K283" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L283" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M283" s="8" t="s">
         <v>2209</v>
@@ -24787,13 +24809,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J284" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K284" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L284" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M284" s="8" t="s">
         <v>2210</v>
@@ -24840,13 +24862,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J285" s="8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K285" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L285" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M285" s="11">
         <v>45455</v>
@@ -24858,7 +24880,7 @@
         <v>372</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q285" s="8" t="s">
         <v>2211</v>
@@ -24893,25 +24915,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J286" s="8">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K286" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L286" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M286" s="11">
         <v>45332</v>
       </c>
       <c r="N286" s="8" t="s">
-        <v>2211</v>
+        <v>2532</v>
       </c>
       <c r="O286" s="8">
         <v>307</v>
       </c>
       <c r="P286" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q286" s="8" t="s">
         <v>2212</v>
@@ -24946,13 +24968,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J287" s="8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K287" s="8">
         <v>0</v>
       </c>
       <c r="L287" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M287" s="11">
         <v>45634</v>
@@ -24987,25 +25009,25 @@
         <v>9820914808</v>
       </c>
       <c r="F288" s="10">
-        <v>3.9235185185185184</v>
+        <v>3.9453356481481481</v>
       </c>
       <c r="G288" s="8">
-        <v>5649.8666670000002</v>
+        <v>5681.2833330000003</v>
       </c>
       <c r="H288" s="8">
-        <v>1305.69</v>
+        <v>1326.35</v>
       </c>
       <c r="I288" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J288" s="8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K288" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L288" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M288" s="8" t="s">
         <v>2190</v>
@@ -25020,7 +25042,7 @@
         <v>1948</v>
       </c>
       <c r="Q288" s="8" t="s">
-        <v>2214</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="289" spans="1:17" x14ac:dyDescent="0.25">
@@ -25105,13 +25127,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J290" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K290" s="8">
         <v>0</v>
       </c>
       <c r="L290" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M290" s="8" t="s">
         <v>2122</v>
@@ -25158,13 +25180,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J291" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K291" s="8">
         <v>0</v>
       </c>
       <c r="L291" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M291" s="8" t="s">
         <v>2018</v>
@@ -25211,13 +25233,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J292" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K292" s="8">
         <v>0</v>
       </c>
       <c r="L292" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M292" s="8" t="s">
         <v>2195</v>
@@ -25317,13 +25339,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J294" s="8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K294" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L294" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M294" s="8" t="s">
         <v>2216</v>
@@ -25335,7 +25357,7 @@
         <v>425</v>
       </c>
       <c r="P294" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q294" s="11">
         <v>45971</v>
@@ -25370,13 +25392,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J295" s="8">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K295" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L295" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M295" s="8" t="s">
         <v>2217</v>
@@ -25388,7 +25410,7 @@
         <v>427</v>
       </c>
       <c r="P295" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q295" s="8" t="s">
         <v>2188</v>
@@ -25476,13 +25498,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J297" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K297" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L297" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M297" s="8" t="s">
         <v>2200</v>
@@ -25494,7 +25516,7 @@
         <v>387</v>
       </c>
       <c r="P297" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q297" s="11">
         <v>45972</v>
@@ -25529,13 +25551,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J298" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K298" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L298" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M298" s="11">
         <v>45901</v>
@@ -25547,7 +25569,7 @@
         <v>406</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q298" s="8" t="s">
         <v>2002</v>
@@ -25570,25 +25592,25 @@
         <v>9820914808</v>
       </c>
       <c r="F299" s="10">
-        <v>3.6607407407407409</v>
+        <v>3.6937615740740739</v>
       </c>
       <c r="G299" s="8">
-        <v>5271.4666669999997</v>
+        <v>5319.0166669999999</v>
       </c>
       <c r="H299" s="8">
-        <v>401.09</v>
+        <v>403.66</v>
       </c>
       <c r="I299" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J299" s="8">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K299" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L299" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M299" s="8" t="s">
         <v>2221</v>
@@ -25600,10 +25622,10 @@
         <v>382</v>
       </c>
       <c r="P299" s="8" t="s">
-        <v>1949</v>
-      </c>
-      <c r="Q299" s="11">
-        <v>46361</v>
+        <v>1948</v>
+      </c>
+      <c r="Q299" s="8" t="s">
+        <v>2109</v>
       </c>
     </row>
     <row r="300" spans="1:17" x14ac:dyDescent="0.25">
@@ -25635,13 +25657,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J300" s="8">
+        <v>15</v>
+      </c>
+      <c r="K300" s="8">
+        <v>1</v>
+      </c>
+      <c r="L300" s="8">
         <v>9</v>
-      </c>
-      <c r="K300" s="8">
-        <v>0</v>
-      </c>
-      <c r="L300" s="8">
-        <v>3</v>
       </c>
       <c r="M300" s="8" t="s">
         <v>1960</v>
@@ -25653,7 +25675,7 @@
         <v>264</v>
       </c>
       <c r="P300" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q300" s="11">
         <v>45699</v>
@@ -25688,13 +25710,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J301" s="8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K301" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L301" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M301" s="8" t="s">
         <v>2222</v>
@@ -25741,13 +25763,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J302" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K302" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L302" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M302" s="11">
         <v>45577</v>
@@ -25759,7 +25781,7 @@
         <v>376</v>
       </c>
       <c r="P302" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q302" s="11">
         <v>46266</v>
@@ -25847,25 +25869,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J304" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K304" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L304" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M304" s="8" t="s">
         <v>2223</v>
       </c>
-      <c r="N304" s="8" t="s">
-        <v>2353</v>
+      <c r="N304" s="11">
+        <v>45817</v>
       </c>
       <c r="O304" s="8">
         <v>426</v>
       </c>
       <c r="P304" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q304" s="8" t="s">
         <v>2098</v>
@@ -25953,10 +25975,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J306" s="8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K306" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L306" s="8">
         <v>0</v>
@@ -26059,13 +26081,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J308" s="8">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K308" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L308" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M308" s="11">
         <v>45608</v>
@@ -26077,10 +26099,10 @@
         <v>377</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q308" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="309" spans="1:17" x14ac:dyDescent="0.25">
@@ -26112,13 +26134,13 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J309" s="8">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K309" s="8">
         <v>0</v>
       </c>
       <c r="L309" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M309" s="8" t="s">
         <v>2198</v>
@@ -26218,13 +26240,13 @@
         <v>84.341712962962958</v>
       </c>
       <c r="J311" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K311" s="8">
         <v>0</v>
       </c>
       <c r="L311" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M311" s="8" t="s">
         <v>2229</v>
@@ -26271,13 +26293,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J312" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K312" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L312" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M312" s="8" t="s">
         <v>2231</v>
@@ -26377,13 +26399,13 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J314" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K314" s="8">
         <v>0</v>
       </c>
       <c r="L314" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M314" s="8" t="s">
         <v>2170</v>
@@ -26418,25 +26440,25 @@
         <v>9820914808</v>
       </c>
       <c r="F315" s="10">
-        <v>5.3626620370370368</v>
+        <v>5.3968749999999996</v>
       </c>
       <c r="G315" s="8">
-        <v>7722.2333330000001</v>
+        <v>7771.5</v>
       </c>
       <c r="H315" s="8">
-        <v>1140.68</v>
+        <v>1147.73</v>
       </c>
       <c r="I315" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J315" s="8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K315" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L315" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M315" s="8" t="s">
         <v>2219</v>
@@ -26448,7 +26470,7 @@
         <v>355</v>
       </c>
       <c r="P315" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q315" s="8" t="s">
         <v>2002</v>
@@ -26642,13 +26664,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J319" s="8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K319" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L319" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M319" s="11">
         <v>45842</v>
@@ -26660,7 +26682,7 @@
         <v>494</v>
       </c>
       <c r="P319" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q319" s="11">
         <v>46204</v>
@@ -26683,25 +26705,25 @@
         <v>9820914808</v>
       </c>
       <c r="F320" s="10">
-        <v>1.9575</v>
+        <v>2.0839351851851853</v>
       </c>
       <c r="G320" s="8">
-        <v>2818.8</v>
+        <v>3000.8666669999998</v>
       </c>
       <c r="H320" s="8">
-        <v>452.63</v>
+        <v>487.67</v>
       </c>
       <c r="I320" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J320" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K320" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L320" s="8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M320" s="8" t="s">
         <v>2090</v>
@@ -26713,10 +26735,10 @@
         <v>420</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q320" s="8" t="s">
-        <v>2120</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="321" spans="1:17" x14ac:dyDescent="0.25">
@@ -26801,13 +26823,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J322" s="8">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K322" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L322" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M322" s="11">
         <v>45691</v>
@@ -26819,7 +26841,7 @@
         <v>458</v>
       </c>
       <c r="P322" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q322" s="11">
         <v>46331</v>
@@ -26854,25 +26876,25 @@
         <v>84.375891203703702</v>
       </c>
       <c r="J323" s="8">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K323" s="8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L323" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M323" s="8" t="s">
         <v>2217</v>
       </c>
       <c r="N323" s="8" t="s">
-        <v>1973</v>
+        <v>2524</v>
       </c>
       <c r="O323" s="8">
         <v>13</v>
       </c>
       <c r="P323" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q323" s="11">
         <v>46083</v>
@@ -26895,22 +26917,22 @@
         <v>9820914808</v>
       </c>
       <c r="F324" s="10">
-        <v>1.1920833333333334</v>
+        <v>1.19625</v>
       </c>
       <c r="G324" s="8">
-        <v>1716.6</v>
+        <v>1722.6</v>
       </c>
       <c r="H324" s="8">
-        <v>272.74</v>
+        <v>273.47000000000003</v>
       </c>
       <c r="I324" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J324" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K324" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L324" s="8">
         <v>0</v>
@@ -26918,8 +26940,8 @@
       <c r="M324" s="8" t="s">
         <v>2146</v>
       </c>
-      <c r="N324" s="11">
-        <v>46143</v>
+      <c r="N324" s="8" t="s">
+        <v>2530</v>
       </c>
       <c r="O324" s="8">
         <v>754</v>
@@ -26928,7 +26950,7 @@
         <v>1949</v>
       </c>
       <c r="Q324" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="325" spans="1:17" x14ac:dyDescent="0.25">
@@ -26960,13 +26982,13 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J325" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K325" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L325" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M325" s="11">
         <v>45779</v>
@@ -26978,10 +27000,10 @@
         <v>-197</v>
       </c>
       <c r="P325" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q325" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="326" spans="1:17" x14ac:dyDescent="0.25">
@@ -27113,13 +27135,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J328" s="8">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K328" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L328" s="8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M328" s="11">
         <v>45750</v>
@@ -27166,19 +27188,19 @@
         <v>84.376539351851847</v>
       </c>
       <c r="J329" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K329" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L329" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M329" s="8" t="s">
         <v>2225</v>
       </c>
-      <c r="N329" s="8" t="s">
-        <v>2031</v>
+      <c r="N329" s="11">
+        <v>45666</v>
       </c>
       <c r="O329" s="8">
         <v>0</v>
@@ -27207,10 +27229,10 @@
         <v>9820914808</v>
       </c>
       <c r="F330" s="10">
-        <v>6.0994097222222221</v>
+        <v>6.1484490740740743</v>
       </c>
       <c r="G330" s="8">
-        <v>8783.15</v>
+        <v>8853.7666669999999</v>
       </c>
       <c r="H330" s="8">
         <v>1431.41</v>
@@ -27219,13 +27241,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J330" s="8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K330" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L330" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M330" s="8" t="s">
         <v>2237</v>
@@ -27237,7 +27259,7 @@
         <v>505</v>
       </c>
       <c r="P330" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q330" s="8" t="s">
         <v>2526</v>
@@ -27478,10 +27500,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J335" s="8">
+        <v>3</v>
+      </c>
+      <c r="K335" s="8">
         <v>2</v>
-      </c>
-      <c r="K335" s="8">
-        <v>1</v>
       </c>
       <c r="L335" s="8">
         <v>1</v>
@@ -27572,10 +27594,10 @@
         <v>9820914808</v>
       </c>
       <c r="F337" s="9">
-        <v>0.63599537037037035</v>
+        <v>0.78729166666666661</v>
       </c>
       <c r="G337" s="8">
-        <v>915.83333330000005</v>
+        <v>1133.7</v>
       </c>
       <c r="H337" s="8">
         <v>4.2699999999999996</v>
@@ -27739,10 +27761,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J340" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K340" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L340" s="8">
         <v>1</v>
@@ -27833,25 +27855,25 @@
         <v>9820914808</v>
       </c>
       <c r="F342" s="10">
-        <v>3.2662384259259261</v>
+        <v>3.2682754629629631</v>
       </c>
       <c r="G342" s="8">
-        <v>4703.3833329999998</v>
+        <v>4706.3166670000001</v>
       </c>
       <c r="H342" s="8">
-        <v>328.23</v>
+        <v>327.06</v>
       </c>
       <c r="I342" s="10">
         <v>84.29965277777778</v>
       </c>
       <c r="J342" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K342" s="8">
         <v>0</v>
       </c>
       <c r="L342" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M342" s="8" t="s">
         <v>2244</v>
@@ -27865,8 +27887,8 @@
       <c r="P342" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="Q342" s="11">
-        <v>46361</v>
+      <c r="Q342" s="8" t="s">
+        <v>2530</v>
       </c>
     </row>
     <row r="343" spans="1:17" x14ac:dyDescent="0.25">
@@ -28051,10 +28073,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J346" s="8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K346" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L346" s="8">
         <v>3</v>
@@ -28104,13 +28126,13 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J347" s="8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K347" s="8">
         <v>1</v>
       </c>
       <c r="L347" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M347" s="11">
         <v>45784</v>
@@ -28765,19 +28787,19 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J362" s="8">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K362" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L362" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M362" s="8" t="s">
         <v>2258</v>
       </c>
-      <c r="N362" s="11">
-        <v>46208</v>
+      <c r="N362" s="8" t="s">
+        <v>2528</v>
       </c>
       <c r="O362" s="8">
         <v>268</v>
@@ -28869,13 +28891,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J364" s="8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K364" s="8">
         <v>0</v>
       </c>
       <c r="L364" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M364" s="8" t="s">
         <v>2189</v>
@@ -29016,13 +29038,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J367" s="8">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K367" s="8">
         <v>3</v>
       </c>
       <c r="L367" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M367" s="8" t="s">
         <v>2210</v>
@@ -29116,13 +29138,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J369" s="8">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="K369" s="8">
         <v>3</v>
       </c>
       <c r="L369" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M369" s="11">
         <v>45359</v>
@@ -29169,13 +29191,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J370" s="8">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K370" s="8">
         <v>0</v>
       </c>
       <c r="L370" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M370" s="11">
         <v>45390</v>
@@ -29222,13 +29244,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J371" s="8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K371" s="8">
         <v>2</v>
       </c>
       <c r="L371" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M371" s="11">
         <v>45604</v>
@@ -29275,7 +29297,7 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J372" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K372" s="8">
         <v>1</v>
@@ -29296,7 +29318,7 @@
         <v>1949</v>
       </c>
       <c r="Q372" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="373" spans="1:17" x14ac:dyDescent="0.25">
@@ -29328,13 +29350,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J373" s="8">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K373" s="8">
         <v>2</v>
       </c>
       <c r="L373" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M373" s="11">
         <v>45420</v>
@@ -29381,13 +29403,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J374" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K374" s="8">
         <v>0</v>
       </c>
       <c r="L374" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M374" s="11">
         <v>45573</v>
@@ -29422,25 +29444,25 @@
         <v>8448820535</v>
       </c>
       <c r="F375" s="10">
-        <v>1.4233217592592593</v>
+        <v>1.5583680555555555</v>
       </c>
       <c r="G375" s="8">
-        <v>2049.583333</v>
+        <v>2244.0500000000002</v>
       </c>
       <c r="H375" s="8">
-        <v>319.02999999999997</v>
+        <v>351.74</v>
       </c>
       <c r="I375" s="10">
         <v>84.334097222222226</v>
       </c>
       <c r="J375" s="8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K375" s="8">
         <v>0</v>
       </c>
       <c r="L375" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M375" s="11">
         <v>45300</v>
@@ -29455,7 +29477,7 @@
         <v>1949</v>
       </c>
       <c r="Q375" s="8" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="376" spans="1:17" x14ac:dyDescent="0.25">
@@ -29475,25 +29497,25 @@
         <v>8448820535</v>
       </c>
       <c r="F376" s="10">
-        <v>2.8598032407407405</v>
+        <v>2.8719675925925925</v>
       </c>
       <c r="G376" s="8">
-        <v>4118.1166670000002</v>
+        <v>4135.6333329999998</v>
       </c>
       <c r="H376" s="8">
-        <v>31514.89</v>
+        <v>31517.15</v>
       </c>
       <c r="I376" s="10">
         <v>84.334097222222226</v>
       </c>
       <c r="J376" s="8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K376" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L376" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M376" s="8" t="s">
         <v>2190</v>
@@ -29505,10 +29527,10 @@
         <v>226</v>
       </c>
       <c r="P376" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q376" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="377" spans="1:17" x14ac:dyDescent="0.25">
@@ -29540,13 +29562,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J377" s="8">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K377" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L377" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M377" s="11">
         <v>45331</v>
@@ -29593,13 +29615,13 @@
         <v>84.339050925925932</v>
       </c>
       <c r="J378" s="8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K378" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L378" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M378" s="8" t="s">
         <v>2194</v>
@@ -29646,19 +29668,19 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J379" s="8">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K379" s="8">
         <v>1</v>
       </c>
       <c r="L379" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M379" s="11">
         <v>45573</v>
       </c>
-      <c r="N379" s="11">
-        <v>45723</v>
+      <c r="N379" s="8" t="s">
+        <v>2533</v>
       </c>
       <c r="O379" s="8">
         <v>217</v>
@@ -29699,13 +29721,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J380" s="8">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K380" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L380" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M380" s="11">
         <v>45605</v>
@@ -29740,25 +29762,25 @@
         <v>8448820535</v>
       </c>
       <c r="F381" s="10">
-        <v>5.3599305555555556</v>
+        <v>5.3629513888888889</v>
       </c>
       <c r="G381" s="8">
-        <v>7718.3</v>
+        <v>7722.65</v>
       </c>
       <c r="H381" s="8">
-        <v>10122.620000000001</v>
+        <v>10122.64</v>
       </c>
       <c r="I381" s="10">
         <v>84.334097222222226</v>
       </c>
       <c r="J381" s="8">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K381" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L381" s="8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M381" s="8" t="s">
         <v>2209</v>
@@ -29770,10 +29792,10 @@
         <v>225</v>
       </c>
       <c r="P381" s="8" t="s">
-        <v>1949</v>
-      </c>
-      <c r="Q381" s="11">
-        <v>46300</v>
+        <v>1948</v>
+      </c>
+      <c r="Q381" s="8" t="s">
+        <v>2528</v>
       </c>
     </row>
     <row r="382" spans="1:17" x14ac:dyDescent="0.25">
@@ -29805,19 +29827,19 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J382" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K382" s="8">
         <v>0</v>
       </c>
       <c r="L382" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M382" s="8" t="s">
         <v>2070</v>
       </c>
       <c r="N382" s="11">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="O382" s="8">
         <v>33</v>
@@ -29858,13 +29880,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J383" s="8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K383" s="8">
         <v>0</v>
       </c>
       <c r="L383" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M383" s="8" t="s">
         <v>2266</v>
@@ -29911,13 +29933,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J384" s="8">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K384" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L384" s="8">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M384" s="11">
         <v>45543</v>
@@ -29929,7 +29951,7 @@
         <v>18</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q384" s="11">
         <v>46236</v>
@@ -29964,13 +29986,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J385" s="8">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K385" s="8">
         <v>1</v>
       </c>
       <c r="L385" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M385" s="8" t="s">
         <v>2113</v>
@@ -30017,13 +30039,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J386" s="8">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K386" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L386" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M386" s="11">
         <v>45452</v>
@@ -30070,13 +30092,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J387" s="8">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K387" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L387" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M387" s="11">
         <v>45574</v>
@@ -30088,7 +30110,7 @@
         <v>25</v>
       </c>
       <c r="P387" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q387" s="8" t="s">
         <v>2268</v>
@@ -30176,19 +30198,19 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J389" s="8">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K389" s="8">
         <v>0</v>
       </c>
       <c r="L389" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M389" s="8" t="s">
         <v>1960</v>
       </c>
       <c r="N389" s="11">
-        <v>45545</v>
+        <v>45394</v>
       </c>
       <c r="O389" s="8">
         <v>805</v>
@@ -30217,25 +30239,25 @@
         <v>8095220410</v>
       </c>
       <c r="F390" s="10">
-        <v>4.3993055555555554</v>
+        <v>4.4427546296296292</v>
       </c>
       <c r="G390" s="8">
-        <v>6335</v>
+        <v>6397.5666670000001</v>
       </c>
       <c r="H390" s="8">
-        <v>1119.1600000000001</v>
+        <v>1130.05</v>
       </c>
       <c r="I390" s="10">
         <v>84.338449074074077</v>
       </c>
       <c r="J390" s="8">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K390" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L390" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M390" s="8" t="s">
         <v>2202</v>
@@ -30247,10 +30269,10 @@
         <v>56</v>
       </c>
       <c r="P390" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q390" s="8" t="s">
-        <v>2109</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="391" spans="1:17" x14ac:dyDescent="0.25">
@@ -30282,13 +30304,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J391" s="8">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K391" s="8">
         <v>0</v>
       </c>
       <c r="L391" s="8">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M391" s="8" t="s">
         <v>2270</v>
@@ -30335,13 +30357,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J392" s="8">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K392" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L392" s="8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M392" s="11">
         <v>45574</v>
@@ -30353,7 +30375,7 @@
         <v>25</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q392" s="8" t="s">
         <v>2268</v>
@@ -30388,19 +30410,19 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J393" s="8">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K393" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L393" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M393" s="8" t="s">
         <v>2271</v>
       </c>
       <c r="N393" s="8" t="s">
-        <v>1983</v>
+        <v>2525</v>
       </c>
       <c r="O393" s="8">
         <v>33</v>
@@ -30441,13 +30463,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J394" s="8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K394" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L394" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M394" s="11">
         <v>45332</v>
@@ -30459,7 +30481,7 @@
         <v>47</v>
       </c>
       <c r="P394" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q394" s="8" t="s">
         <v>2268</v>
@@ -30494,13 +30516,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J395" s="8">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K395" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L395" s="8">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M395" s="8" t="s">
         <v>2219</v>
@@ -30547,13 +30569,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J396" s="8">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K396" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L396" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M396" s="8" t="s">
         <v>2258</v>
@@ -30565,7 +30587,7 @@
         <v>70</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q396" s="8" t="s">
         <v>2273</v>
@@ -30600,13 +30622,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J397" s="8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K397" s="8">
         <v>0</v>
       </c>
       <c r="L397" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M397" s="11">
         <v>45483</v>
@@ -30653,13 +30675,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J398" s="8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K398" s="8">
         <v>0</v>
       </c>
       <c r="L398" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M398" s="11">
         <v>45635</v>
@@ -30706,13 +30728,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J399" s="8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K399" s="8">
         <v>0</v>
       </c>
       <c r="L399" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M399" s="11">
         <v>45545</v>
@@ -30812,13 +30834,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J401" s="8">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K401" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L401" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M401" s="8" t="s">
         <v>2275</v>
@@ -30830,7 +30852,7 @@
         <v>69</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q401" s="8" t="s">
         <v>2276</v>
@@ -31455,13 +31477,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J416" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K416" s="8">
         <v>0</v>
       </c>
       <c r="L416" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M416" s="8" t="s">
         <v>2227</v>
@@ -32000,13 +32022,13 @@
         <v>84.381435185185182</v>
       </c>
       <c r="J429" s="8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K429" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L429" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M429" s="8" t="s">
         <v>2297</v>
@@ -32209,7 +32231,7 @@
         <v>9</v>
       </c>
       <c r="K433" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L433" s="8">
         <v>2</v>
@@ -32224,7 +32246,7 @@
         <v>-49</v>
       </c>
       <c r="P433" s="8" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="Q433" s="11">
         <v>46331</v>
@@ -32312,10 +32334,10 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J435" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K435" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L435" s="8">
         <v>0</v>
@@ -32365,13 +32387,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J436" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K436" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L436" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M436" s="11">
         <v>45724</v>
@@ -32383,7 +32405,7 @@
         <v>352</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q436" s="11">
         <v>45757</v>
@@ -32557,13 +32579,13 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J440" s="8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K440" s="8">
         <v>1</v>
       </c>
       <c r="L440" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M440" s="11">
         <v>45907</v>
@@ -32610,13 +32632,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J441" s="8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K441" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L441" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M441" s="11">
         <v>45720</v>
@@ -32769,10 +32791,10 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J444" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K444" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L444" s="8">
         <v>2</v>
@@ -32822,13 +32844,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J445" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K445" s="8">
         <v>0</v>
       </c>
       <c r="L445" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M445" s="8" t="s">
         <v>2302</v>
@@ -32924,13 +32946,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J447" s="8">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K447" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L447" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M447" s="8" t="s">
         <v>1957</v>
@@ -32942,7 +32964,7 @@
         <v>342</v>
       </c>
       <c r="P447" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q447" s="8" t="s">
         <v>2181</v>
@@ -32998,7 +33020,7 @@
         <v>1949</v>
       </c>
       <c r="Q448" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="449" spans="1:17" x14ac:dyDescent="0.25">
@@ -33083,13 +33105,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J450" s="8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K450" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L450" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M450" s="11">
         <v>45812</v>
@@ -33101,7 +33123,7 @@
         <v>233</v>
       </c>
       <c r="P450" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q450" s="8" t="s">
         <v>2146</v>
@@ -33136,7 +33158,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J451" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K451" s="8">
         <v>0</v>
@@ -33189,13 +33211,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J452" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K452" s="8">
         <v>1</v>
       </c>
       <c r="L452" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M452" s="8" t="s">
         <v>2305</v>
@@ -33242,10 +33264,10 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J453" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K453" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L453" s="8">
         <v>1</v>
@@ -33254,7 +33276,7 @@
         <v>45909</v>
       </c>
       <c r="N453" s="8" t="s">
-        <v>2047</v>
+        <v>2008</v>
       </c>
       <c r="O453" s="8">
         <v>389</v>
@@ -33348,13 +33370,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J455" s="8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K455" s="8">
         <v>2</v>
       </c>
       <c r="L455" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M455" s="8" t="s">
         <v>2303</v>
@@ -33507,13 +33529,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J458" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K458" s="8">
         <v>1</v>
       </c>
       <c r="L458" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M458" s="11">
         <v>45755</v>
@@ -33640,25 +33662,25 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J461" s="8">
+        <v>3</v>
+      </c>
+      <c r="K461" s="8">
         <v>1</v>
       </c>
-      <c r="K461" s="8">
-        <v>0</v>
-      </c>
       <c r="L461" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M461" s="8" t="s">
         <v>2311</v>
       </c>
-      <c r="N461" s="8" t="s">
-        <v>2311</v>
+      <c r="N461" s="11">
+        <v>45696</v>
       </c>
       <c r="O461" s="8">
         <v>349</v>
       </c>
       <c r="P461" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q461" s="8"/>
     </row>
@@ -34336,25 +34358,25 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J475" s="8">
+        <v>3</v>
+      </c>
+      <c r="K475" s="8">
         <v>1</v>
       </c>
-      <c r="K475" s="8">
-        <v>0</v>
-      </c>
       <c r="L475" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M475" s="8" t="s">
-        <v>2064</v>
+        <v>2534</v>
       </c>
       <c r="N475" s="8" t="s">
         <v>2064</v>
       </c>
       <c r="O475" s="8">
-        <v>246</v>
+        <v>-94</v>
       </c>
       <c r="P475" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q475" s="11">
         <v>45726</v>
@@ -34377,13 +34399,13 @@
         <v>2563254163</v>
       </c>
       <c r="F476" s="9">
-        <v>6.7129629629629636E-2</v>
+        <v>0.11282407407407408</v>
       </c>
       <c r="G476" s="8">
-        <v>96.666666669999998</v>
+        <v>162.46666669999999</v>
       </c>
       <c r="H476" s="8">
-        <v>4.66</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I476" s="10">
         <v>84.254247685185192</v>
@@ -34410,7 +34432,7 @@
         <v>1948</v>
       </c>
       <c r="Q476" s="8" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="477" spans="1:17" x14ac:dyDescent="0.25">
@@ -34442,10 +34464,10 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J477" s="8">
+        <v>5</v>
+      </c>
+      <c r="K477" s="8">
         <v>4</v>
-      </c>
-      <c r="K477" s="8">
-        <v>3</v>
       </c>
       <c r="L477" s="8">
         <v>1</v>
@@ -34506,7 +34528,7 @@
         <v>1949</v>
       </c>
       <c r="Q478" s="8" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="479" spans="1:17" x14ac:dyDescent="0.25">
@@ -34718,22 +34740,22 @@
         <v>7042118352</v>
       </c>
       <c r="F483" s="9">
-        <v>0.31284722222222222</v>
+        <v>0.32047453703703704</v>
       </c>
       <c r="G483" s="8">
-        <v>450.5</v>
+        <v>461.48333330000003</v>
       </c>
       <c r="H483" s="8">
-        <v>24.73</v>
+        <v>26.76</v>
       </c>
       <c r="I483" s="10">
         <v>84.418796296296293</v>
       </c>
       <c r="J483" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K483" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L483" s="8">
         <v>1</v>
@@ -34742,7 +34764,7 @@
         <v>2066</v>
       </c>
       <c r="N483" s="11">
-        <v>46058</v>
+        <v>46300</v>
       </c>
       <c r="O483" s="8">
         <v>15</v>
@@ -34751,7 +34773,7 @@
         <v>1948</v>
       </c>
       <c r="Q483" s="8" t="s">
-        <v>2159</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="484" spans="1:17" x14ac:dyDescent="0.25">
@@ -35456,10 +35478,10 @@
         <v>84.382268518518515</v>
       </c>
       <c r="J499" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K499" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L499" s="8">
         <v>3</v>
@@ -36673,10 +36695,10 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J526" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K526" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L526" s="8">
         <v>1</v>
@@ -36685,7 +36707,7 @@
         <v>2050</v>
       </c>
       <c r="N526" s="8" t="s">
-        <v>2050</v>
+        <v>2530</v>
       </c>
       <c r="O526" s="8">
         <v>121</v>
@@ -37835,7 +37857,7 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J552" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K552" s="8">
         <v>0</v>
@@ -37847,7 +37869,7 @@
         <v>2381</v>
       </c>
       <c r="N552" s="11">
-        <v>45454</v>
+        <v>45547</v>
       </c>
       <c r="O552" s="8">
         <v>129</v>
@@ -41982,10 +42004,10 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J637" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K637" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L637" s="8">
         <v>2</v>
@@ -42135,7 +42157,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J640" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K640" s="8">
         <v>0</v>
@@ -42474,10 +42496,10 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J647" s="8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K647" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L647" s="8">
         <v>0</v>
@@ -42492,7 +42514,7 @@
         <v>119</v>
       </c>
       <c r="P647" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q647" s="11">
         <v>46178</v>
@@ -42576,25 +42598,25 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J649" s="8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K649" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L649" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M649" s="11">
         <v>44933</v>
       </c>
       <c r="N649" s="11">
-        <v>45755</v>
+        <v>45999</v>
       </c>
       <c r="O649" s="8">
         <v>105</v>
       </c>
       <c r="P649" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q649" s="8" t="s">
         <v>1985</v>
@@ -43048,7 +43070,7 @@
       </c>
       <c r="I659" s="8"/>
       <c r="J659" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K659" s="8">
         <v>0</v>
@@ -43056,8 +43078,12 @@
       <c r="L659" s="8">
         <v>0</v>
       </c>
-      <c r="M659" s="8"/>
-      <c r="N659" s="8"/>
+      <c r="M659" s="11">
+        <v>45598</v>
+      </c>
+      <c r="N659" s="11">
+        <v>45598</v>
+      </c>
       <c r="O659" s="8"/>
       <c r="P659" s="8" t="s">
         <v>1949</v>
@@ -43314,13 +43340,13 @@
         <v>84.334780092592595</v>
       </c>
       <c r="J665" s="8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K665" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L665" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M665" s="8" t="s">
         <v>2455</v>
@@ -43332,7 +43358,7 @@
         <v>142</v>
       </c>
       <c r="P665" s="8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="Q665" s="8" t="s">
         <v>2164</v>
@@ -43756,13 +43782,13 @@
         <v>1</v>
       </c>
       <c r="M674" s="11">
-        <v>45476</v>
+        <v>45446</v>
       </c>
       <c r="N674" s="11">
-        <v>45476</v>
+        <v>45446</v>
       </c>
       <c r="O674" s="8">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P674" s="8" t="s">
         <v>1949</v>
@@ -45124,13 +45150,13 @@
         <v>8448820535</v>
       </c>
       <c r="F705" s="10">
-        <v>2.2825694444444444</v>
+        <v>2.3423148148148147</v>
       </c>
       <c r="G705" s="8">
-        <v>3286.9</v>
+        <v>3372.9333329999999</v>
       </c>
       <c r="H705" s="8">
-        <v>538.11</v>
+        <v>553.75</v>
       </c>
       <c r="I705" s="10">
         <v>84.334097222222226</v>
@@ -45157,7 +45183,7 @@
         <v>1949</v>
       </c>
       <c r="Q705" s="8" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="706" spans="1:17" x14ac:dyDescent="0.25">
@@ -46025,7 +46051,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J726" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K726" s="8">
         <v>0</v>
@@ -46034,13 +46060,13 @@
         <v>0</v>
       </c>
       <c r="M726" s="8" t="s">
-        <v>2529</v>
+        <v>2410</v>
       </c>
       <c r="N726" s="11">
         <v>45748</v>
       </c>
       <c r="O726" s="8">
-        <v>938</v>
+        <v>559</v>
       </c>
       <c r="P726" s="8" t="s">
         <v>1949</v>
@@ -47177,7 +47203,7 @@
       </c>
       <c r="J6" s="4" cm="1">
         <f t="array" ref="J6">ROWS(_xlfn._xlws.FILTER('Drone details'!A2:A447,VALUE('Drone details'!K2:K447&amp;"0")&gt;0))</f>
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="K6" s="4" cm="1">
         <f t="array" ref="K6">SUMPRODUCT((ISNUMBER('Drone details'!N2:N447)*('Drone details'!N2:N447&lt;=30))*1)</f>
@@ -47194,7 +47220,7 @@
       </c>
       <c r="J7" s="4" cm="1">
         <f t="array" ref="J7">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Drone details'!C2:C447,VALUE('Drone details'!K2:K447&amp;"0")&gt;0)))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K7" s="4" t="e" cm="1" vm="1">
         <f t="array" ref="K7">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Drone details'!C2:C447,(ISNUMBER('Drone details'!N2:N447))*('Drone details'!N2:N447&lt;=30))))</f>

--- a/drone_data.xlsx
+++ b/drone_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://genaero-my.sharepoint.com/personal/ronak_devadiga_generalaeronautics_com/Documents/Product/Drone Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F59D71E7-BC2D-4B27-A834-02E1344DD2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2736DB6D-9AD5-4BF8-AE07-9628D213553C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9120,22 +9120,13 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
         <v>0</v>
-      </c>
-      <c r="M7" s="11">
-        <v>45333</v>
-      </c>
-      <c r="N7" s="11">
-        <v>45412</v>
-      </c>
-      <c r="O7">
-        <v>614</v>
       </c>
       <c r="P7" t="s">
         <v>309</v>
@@ -9640,7 +9631,7 @@
         <v>84.300335648148149</v>
       </c>
       <c r="J21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -9690,10 +9681,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -9743,13 +9734,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M23" s="11">
         <v>45329</v>
@@ -9796,25 +9787,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J24">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M24" s="11">
         <v>45404</v>
       </c>
       <c r="N24" s="11">
-        <v>45868</v>
+        <v>45866</v>
       </c>
       <c r="O24">
         <v>144</v>
       </c>
       <c r="P24" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q24" s="11">
         <v>45857</v>
@@ -9849,25 +9840,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J25">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M25" s="11">
         <v>45422</v>
       </c>
       <c r="N25" s="11">
-        <v>45902</v>
+        <v>45901</v>
       </c>
       <c r="O25">
         <v>162</v>
       </c>
       <c r="P25" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q25" s="11">
         <v>45900</v>
@@ -9902,13 +9893,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J26">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M26" s="11">
         <v>45404</v>
@@ -9920,7 +9911,7 @@
         <v>144</v>
       </c>
       <c r="P26" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q26" s="11">
         <v>46105</v>
@@ -9955,13 +9946,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J27">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M27" s="11">
         <v>45408</v>
@@ -10008,13 +9999,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J28">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M28" s="11">
         <v>45411</v>
@@ -10026,7 +10017,7 @@
         <v>151</v>
       </c>
       <c r="P28" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q28" s="11">
         <v>46066</v>
@@ -10061,13 +10052,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J29">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M29" s="11">
         <v>45415</v>
@@ -10114,13 +10105,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M30" s="11">
         <v>45418</v>
@@ -10167,13 +10158,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J31">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M31" s="11">
         <v>45425</v>
@@ -10185,7 +10176,7 @@
         <v>165</v>
       </c>
       <c r="P31" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q31" s="11">
         <v>45994</v>
@@ -10220,13 +10211,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J32">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M32" s="11">
         <v>45407</v>
@@ -10273,13 +10264,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J33">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M33" s="11">
         <v>45396</v>
@@ -10291,7 +10282,7 @@
         <v>136</v>
       </c>
       <c r="P33" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q33" s="11">
         <v>45883</v>
@@ -10379,19 +10370,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J35">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M35" s="11">
         <v>45392</v>
       </c>
       <c r="N35" s="11">
-        <v>45966</v>
+        <v>45960</v>
       </c>
       <c r="O35">
         <v>132</v>
@@ -10432,13 +10423,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J36">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M36" s="11">
         <v>45358</v>
@@ -10485,13 +10476,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J37">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M37" s="11">
         <v>45415</v>
@@ -10538,13 +10529,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J38">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M38" s="11">
         <v>45413</v>
@@ -10591,13 +10582,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J39">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M39" s="11">
         <v>45393</v>
@@ -10644,13 +10635,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J40">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M40" s="11">
         <v>45275</v>
@@ -10697,13 +10688,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J41">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
         <v>2</v>
-      </c>
-      <c r="L41">
-        <v>7</v>
       </c>
       <c r="M41" s="11">
         <v>45489</v>
@@ -10750,7 +10741,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -10909,13 +10900,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J45">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M45" s="11">
         <v>45436</v>
@@ -10927,7 +10918,7 @@
         <v>176</v>
       </c>
       <c r="P45" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q45" s="11">
         <v>45912</v>
@@ -10962,13 +10953,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J46">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="K46">
+        <v>2</v>
+      </c>
+      <c r="L46">
         <v>5</v>
-      </c>
-      <c r="L46">
-        <v>16</v>
       </c>
       <c r="M46" s="11">
         <v>45301</v>
@@ -10980,7 +10971,7 @@
         <v>41</v>
       </c>
       <c r="P46" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q46" s="11">
         <v>46123</v>
@@ -11015,13 +11006,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J47">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M47" s="11">
         <v>45301</v>
@@ -11033,7 +11024,7 @@
         <v>41</v>
       </c>
       <c r="P47" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q47" s="11">
         <v>46123</v>
@@ -11068,13 +11059,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J48">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K48">
         <v>1</v>
       </c>
       <c r="L48">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M48" s="11">
         <v>45293</v>
@@ -11118,13 +11109,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J49">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M49" s="11">
         <v>45329</v>
@@ -11168,13 +11159,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J50">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M50" s="11">
         <v>45310</v>
@@ -11274,25 +11265,25 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J52">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M52" s="11">
         <v>45419</v>
       </c>
       <c r="N52" s="11">
-        <v>45734</v>
+        <v>45711</v>
       </c>
       <c r="O52">
         <v>416</v>
       </c>
       <c r="P52" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q52" s="11">
         <v>45727</v>
@@ -11327,13 +11318,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J53">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M53" s="11">
         <v>45544</v>
@@ -11380,13 +11371,13 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J54">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M54" s="11">
         <v>45400</v>
@@ -11421,13 +11412,13 @@
         <v>9610765474</v>
       </c>
       <c r="F55" s="10">
-        <v>0.61784722222222221</v>
+        <v>0.70035879629629627</v>
       </c>
       <c r="G55">
-        <v>889.7</v>
+        <v>1008.5166666666599</v>
       </c>
       <c r="H55">
-        <v>86.25</v>
+        <v>105.83</v>
       </c>
       <c r="I55" s="9">
         <v>84.338483796296302</v>
@@ -11436,7 +11427,7 @@
         <v>8</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
         <v>1</v>
@@ -11445,7 +11436,7 @@
         <v>45400</v>
       </c>
       <c r="N55" s="11">
-        <v>45643</v>
+        <v>46161</v>
       </c>
       <c r="O55">
         <v>-98</v>
@@ -11486,13 +11477,13 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J56">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" s="11">
         <v>45400</v>
@@ -11539,13 +11530,13 @@
         <v>84.338333333333338</v>
       </c>
       <c r="J57">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
         <v>1</v>
-      </c>
-      <c r="L57">
-        <v>4</v>
       </c>
       <c r="M57" s="11">
         <v>45400</v>
@@ -11804,13 +11795,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J62">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M62" s="11">
         <v>45436</v>
@@ -11822,7 +11813,7 @@
         <v>176</v>
       </c>
       <c r="P62" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q62" s="11">
         <v>45939</v>
@@ -11857,7 +11848,7 @@
         <v>84.338333333333338</v>
       </c>
       <c r="J63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -11910,13 +11901,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J64">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M64" s="11">
         <v>45420</v>
@@ -11963,13 +11954,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J65">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K65">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M65" s="11">
         <v>45417</v>
@@ -11981,7 +11972,7 @@
         <v>157</v>
       </c>
       <c r="P65" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q65" s="11">
         <v>46057</v>
@@ -12016,13 +12007,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J66">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M66" s="11">
         <v>45428</v>
@@ -12034,7 +12025,7 @@
         <v>168</v>
       </c>
       <c r="P66" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q66" s="11">
         <v>46106</v>
@@ -12122,13 +12113,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J68">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M68" s="11">
         <v>45470</v>
@@ -12140,7 +12131,7 @@
         <v>210</v>
       </c>
       <c r="P68" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q68" s="11">
         <v>46144</v>
@@ -12175,13 +12166,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J69">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M69" s="11">
         <v>45381</v>
@@ -12193,7 +12184,7 @@
         <v>121</v>
       </c>
       <c r="P69" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q69" s="11">
         <v>45962</v>
@@ -12228,13 +12219,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J70">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M70" s="11">
         <v>45393</v>
@@ -12281,13 +12272,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J71">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M71" s="11">
         <v>45424</v>
@@ -12334,13 +12325,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J72">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="K72">
         <v>0</v>
       </c>
       <c r="L72">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M72" s="11">
         <v>45425</v>
@@ -12387,13 +12378,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J73">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M73" s="11">
         <v>45466</v>
@@ -12440,13 +12431,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J74">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M74" s="11">
         <v>45408</v>
@@ -12458,7 +12449,7 @@
         <v>148</v>
       </c>
       <c r="P74" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q74" s="11">
         <v>45908</v>
@@ -12493,13 +12484,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J75">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M75" s="11">
         <v>45390</v>
@@ -12511,7 +12502,7 @@
         <v>130</v>
       </c>
       <c r="P75" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q75" s="11">
         <v>46092</v>
@@ -12546,13 +12537,13 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J76">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
         <v>1</v>
-      </c>
-      <c r="L76">
-        <v>4</v>
       </c>
       <c r="M76" s="11">
         <v>45400</v>
@@ -12564,7 +12555,7 @@
         <v>-98</v>
       </c>
       <c r="P76" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q76" s="11">
         <v>45791</v>
@@ -12596,19 +12587,19 @@
         <v>84.338483796296302</v>
       </c>
       <c r="J77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M77" s="11">
         <v>45400</v>
       </c>
       <c r="N77" s="11">
-        <v>45510</v>
+        <v>45499</v>
       </c>
       <c r="O77">
         <v>-98</v>
@@ -12646,13 +12637,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J78">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
         <v>1</v>
-      </c>
-      <c r="L78">
-        <v>4</v>
       </c>
       <c r="M78" s="11">
         <v>45481</v>
@@ -12793,25 +12784,25 @@
         <v>9820914808</v>
       </c>
       <c r="F81" s="9">
-        <v>1.7109953703703704</v>
+        <v>1.7230324074074075</v>
       </c>
       <c r="G81">
-        <v>2463.8333333333298</v>
+        <v>2481.1666666666601</v>
       </c>
       <c r="H81">
-        <v>171.12</v>
+        <v>172.28</v>
       </c>
       <c r="I81" s="9">
         <v>84.29965277777778</v>
       </c>
       <c r="J81">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M81" s="11">
         <v>45447</v>
@@ -12823,7 +12814,7 @@
         <v>187</v>
       </c>
       <c r="P81" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q81" s="11">
         <v>46049</v>
@@ -12858,13 +12849,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J82">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M82" s="11">
         <v>45438</v>
@@ -12876,7 +12867,7 @@
         <v>178</v>
       </c>
       <c r="P82" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q82" s="11">
         <v>46037</v>
@@ -12911,13 +12902,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J83">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M83" s="11">
         <v>45355</v>
@@ -12929,7 +12920,7 @@
         <v>95</v>
       </c>
       <c r="P83" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q83" s="11">
         <v>46011</v>
@@ -12964,13 +12955,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J84">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
         <v>3</v>
-      </c>
-      <c r="L84">
-        <v>9</v>
       </c>
       <c r="M84" s="11">
         <v>45470</v>
@@ -13017,25 +13008,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J85">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K85">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M85" s="11">
         <v>45480</v>
       </c>
       <c r="N85" s="11">
-        <v>45807</v>
+        <v>45780</v>
       </c>
       <c r="O85">
         <v>220</v>
       </c>
       <c r="P85" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q85" s="11">
         <v>45752</v>
@@ -13176,13 +13167,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J88">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
         <v>2</v>
-      </c>
-      <c r="L88">
-        <v>7</v>
       </c>
       <c r="M88" s="11">
         <v>45410</v>
@@ -13229,13 +13220,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J89">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M89" s="11">
         <v>45464</v>
@@ -13282,13 +13273,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J90">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M90" s="11">
         <v>45406</v>
@@ -13300,7 +13291,7 @@
         <v>146</v>
       </c>
       <c r="P90" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q90" s="11">
         <v>45956</v>
@@ -13335,13 +13326,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J91">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
         <v>1</v>
-      </c>
-      <c r="L91">
-        <v>4</v>
       </c>
       <c r="M91" s="11">
         <v>45430</v>
@@ -13353,7 +13344,7 @@
         <v>170</v>
       </c>
       <c r="P91" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q91" s="11">
         <v>45846</v>
@@ -13388,13 +13379,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J92">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M92" s="11">
         <v>45434</v>
@@ -13406,7 +13397,7 @@
         <v>174</v>
       </c>
       <c r="P92" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q92" s="11">
         <v>45943</v>
@@ -13441,7 +13432,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J93">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K93">
         <v>1</v>
@@ -13494,13 +13485,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J94">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M94" s="11">
         <v>45404</v>
@@ -13600,7 +13591,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J96">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -13706,13 +13697,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J98">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M98" s="11">
         <v>45433</v>
@@ -13724,7 +13715,7 @@
         <v>173</v>
       </c>
       <c r="P98" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q98" s="11">
         <v>45949</v>
@@ -13812,13 +13803,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J100">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K100">
         <v>0</v>
       </c>
       <c r="L100">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M100" s="11">
         <v>45435</v>
@@ -13865,13 +13856,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J101">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M101" s="11">
         <v>45437</v>
@@ -13883,7 +13874,7 @@
         <v>177</v>
       </c>
       <c r="P101" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q101" s="11">
         <v>45994</v>
@@ -13918,13 +13909,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J102">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
         <v>2</v>
-      </c>
-      <c r="L102">
-        <v>3</v>
       </c>
       <c r="M102" s="11">
         <v>45412</v>
@@ -13936,7 +13927,7 @@
         <v>152</v>
       </c>
       <c r="P102" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q102" s="11">
         <v>45935</v>
@@ -13971,13 +13962,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J103">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K103">
         <v>0</v>
       </c>
       <c r="L103">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M103" s="11">
         <v>45409</v>
@@ -14024,13 +14015,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J104">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K104">
         <v>0</v>
       </c>
       <c r="L104">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M104" s="11">
         <v>45409</v>
@@ -14077,13 +14068,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J105">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M105" s="11">
         <v>45432</v>
@@ -14095,7 +14086,7 @@
         <v>172</v>
       </c>
       <c r="P105" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="11">
         <v>46065</v>
@@ -14130,13 +14121,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J106">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M106" s="11">
         <v>45422</v>
@@ -14236,13 +14227,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J108">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K108">
         <v>0</v>
       </c>
       <c r="L108">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M108" s="11">
         <v>45493</v>
@@ -14289,13 +14280,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J109">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M109" s="11">
         <v>45457</v>
@@ -14307,7 +14298,7 @@
         <v>197</v>
       </c>
       <c r="P109" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q109" s="11">
         <v>46058</v>
@@ -14395,13 +14386,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J111">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L111">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M111" s="11">
         <v>45398</v>
@@ -14501,13 +14492,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J113">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K113">
         <v>0</v>
       </c>
       <c r="L113">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M113" s="11">
         <v>45467</v>
@@ -14554,13 +14545,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J114">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K114">
         <v>0</v>
       </c>
       <c r="L114">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M114" s="11">
         <v>45433</v>
@@ -14607,13 +14598,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J115">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M115" s="11">
         <v>45432</v>
@@ -14625,7 +14616,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q115" s="11">
         <v>46006</v>
@@ -14713,13 +14704,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J117">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M117" s="11">
         <v>45428</v>
@@ -14731,7 +14722,7 @@
         <v>168</v>
       </c>
       <c r="P117" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q117" s="11">
         <v>45994</v>
@@ -14819,10 +14810,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J119">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -14872,7 +14863,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J120">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K120">
         <v>0</v>
@@ -14925,19 +14916,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J121">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K121">
         <v>0</v>
       </c>
       <c r="L121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M121" s="11">
         <v>45466</v>
       </c>
       <c r="N121" s="11">
-        <v>45896</v>
+        <v>45856</v>
       </c>
       <c r="O121">
         <v>206</v>
@@ -14978,13 +14969,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J122">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L122">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M122" s="11">
         <v>45464</v>
@@ -15137,13 +15128,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J125">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K125">
         <v>0</v>
       </c>
       <c r="L125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M125" s="11">
         <v>45476</v>
@@ -15190,13 +15181,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J126">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M126" s="11">
         <v>45426</v>
@@ -15208,7 +15199,7 @@
         <v>166</v>
       </c>
       <c r="P126" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q126" s="11">
         <v>46017</v>
@@ -15243,25 +15234,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J127">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K127">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L127">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M127" s="11">
         <v>45422</v>
       </c>
       <c r="N127" s="11">
-        <v>45883</v>
+        <v>45819</v>
       </c>
       <c r="O127">
         <v>162</v>
       </c>
       <c r="P127" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q127" s="11">
         <v>45759</v>
@@ -15296,13 +15287,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J128">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K128">
         <v>0</v>
       </c>
       <c r="L128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M128" s="11">
         <v>45419</v>
@@ -15349,13 +15340,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J129">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K129">
         <v>0</v>
       </c>
       <c r="L129">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M129" s="11">
         <v>45476</v>
@@ -15402,13 +15393,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J130">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K130">
         <v>0</v>
       </c>
       <c r="L130">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M130" s="11">
         <v>45478</v>
@@ -15455,13 +15446,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J131">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K131">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L131">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M131" s="11">
         <v>45466</v>
@@ -15473,7 +15464,7 @@
         <v>206</v>
       </c>
       <c r="P131" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q131" s="11">
         <v>46079</v>
@@ -15508,7 +15499,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J132">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -15614,13 +15605,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J134">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K134">
         <v>0</v>
       </c>
       <c r="L134">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M134" s="11">
         <v>45441</v>
@@ -15720,13 +15711,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J136">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
         <v>1</v>
-      </c>
-      <c r="L136">
-        <v>2</v>
       </c>
       <c r="M136" s="11">
         <v>45465</v>
@@ -15738,7 +15729,7 @@
         <v>205</v>
       </c>
       <c r="P136" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q136" s="11">
         <v>46111</v>
@@ -15879,13 +15870,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J139">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L139">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M139" s="11">
         <v>45405</v>
@@ -15985,13 +15976,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J141">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="K141">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L141">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M141" s="11">
         <v>45466</v>
@@ -16038,13 +16029,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J142">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L142">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M142" s="11">
         <v>45429</v>
@@ -16056,7 +16047,7 @@
         <v>169</v>
       </c>
       <c r="P142" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q142" s="11">
         <v>46156</v>
@@ -16091,13 +16082,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J143">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
         <v>1</v>
-      </c>
-      <c r="L143">
-        <v>4</v>
       </c>
       <c r="M143" s="11">
         <v>45466</v>
@@ -16109,7 +16100,7 @@
         <v>206</v>
       </c>
       <c r="P143" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q143" s="11">
         <v>45940</v>
@@ -16144,13 +16135,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J144">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K144">
         <v>0</v>
       </c>
       <c r="L144">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M144" s="11">
         <v>45428</v>
@@ -16197,13 +16188,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J145">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K145">
         <v>1</v>
       </c>
       <c r="L145">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M145" s="11">
         <v>45458</v>
@@ -16250,13 +16241,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J146">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L146">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M146" s="11">
         <v>45458</v>
@@ -16268,7 +16259,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q146" s="11">
         <v>45849</v>
@@ -16303,13 +16294,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J147">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
         <v>3</v>
-      </c>
-      <c r="L147">
-        <v>13</v>
       </c>
       <c r="M147" s="11">
         <v>45433</v>
@@ -16321,7 +16312,7 @@
         <v>173</v>
       </c>
       <c r="P147" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q147" s="11">
         <v>45819</v>
@@ -16356,13 +16347,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J148">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
         <v>2</v>
-      </c>
-      <c r="L148">
-        <v>5</v>
       </c>
       <c r="M148" s="11">
         <v>45533</v>
@@ -16462,25 +16453,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J150">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L150">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M150" s="11">
         <v>45439</v>
       </c>
       <c r="N150" s="11">
-        <v>45875</v>
+        <v>45683</v>
       </c>
       <c r="O150">
         <v>179</v>
       </c>
       <c r="P150" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q150" s="11">
         <v>45683</v>
@@ -16515,13 +16506,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J151">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K151">
         <v>0</v>
       </c>
       <c r="L151">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M151" s="11">
         <v>45442</v>
@@ -16568,13 +16559,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J152">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M152" s="11">
         <v>45455</v>
@@ -16586,7 +16577,7 @@
         <v>195</v>
       </c>
       <c r="P152" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q152" s="11">
         <v>46051</v>
@@ -16674,13 +16665,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J154">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K154">
         <v>0</v>
       </c>
       <c r="L154">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M154" s="11">
         <v>45438</v>
@@ -16727,10 +16718,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J155">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155">
         <v>1</v>
@@ -16780,13 +16771,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J156">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K156">
         <v>0</v>
       </c>
       <c r="L156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M156" s="11">
         <v>45416</v>
@@ -16833,13 +16824,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J157">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
         <v>2</v>
-      </c>
-      <c r="L157">
-        <v>8</v>
       </c>
       <c r="M157" s="11">
         <v>45436</v>
@@ -16851,7 +16842,7 @@
         <v>176</v>
       </c>
       <c r="P157" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q157" s="11">
         <v>46056</v>
@@ -16886,19 +16877,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J158">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K158">
         <v>0</v>
       </c>
       <c r="L158">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M158" s="11">
         <v>45464</v>
       </c>
       <c r="N158" s="11">
-        <v>45603</v>
+        <v>45599</v>
       </c>
       <c r="O158">
         <v>204</v>
@@ -16939,13 +16930,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J159">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K159">
         <v>0</v>
       </c>
       <c r="L159">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M159" s="11">
         <v>45507</v>
@@ -16992,13 +16983,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J160">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
         <v>5</v>
-      </c>
-      <c r="L160">
-        <v>15</v>
       </c>
       <c r="M160" s="11">
         <v>45439</v>
@@ -17010,7 +17001,7 @@
         <v>179</v>
       </c>
       <c r="P160" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q160" s="11">
         <v>46078</v>
@@ -17045,13 +17036,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J161">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M161" s="11">
         <v>45518</v>
@@ -17063,7 +17054,7 @@
         <v>258</v>
       </c>
       <c r="P161" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q161" s="11">
         <v>45874</v>
@@ -17098,13 +17089,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J162">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M162" s="11">
         <v>45433</v>
@@ -17116,7 +17107,7 @@
         <v>173</v>
       </c>
       <c r="P162" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q162" s="11">
         <v>46112</v>
@@ -17151,13 +17142,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J163">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L163">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M163" s="11">
         <v>45506</v>
@@ -17169,7 +17160,7 @@
         <v>246</v>
       </c>
       <c r="P163" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q163" s="11">
         <v>46021</v>
@@ -17204,13 +17195,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J164">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L164">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M164" s="11">
         <v>45436</v>
@@ -17222,7 +17213,7 @@
         <v>176</v>
       </c>
       <c r="P164" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q164" s="11">
         <v>46040</v>
@@ -17257,19 +17248,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J165">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165">
         <v>2</v>
-      </c>
-      <c r="L165">
-        <v>3</v>
       </c>
       <c r="M165" s="11">
         <v>45444</v>
       </c>
       <c r="N165" s="11">
-        <v>46036</v>
+        <v>45946</v>
       </c>
       <c r="O165">
         <v>184</v>
@@ -17310,13 +17301,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J166">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M166" s="11">
         <v>45502</v>
@@ -17328,7 +17319,7 @@
         <v>242</v>
       </c>
       <c r="P166" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q166" s="11">
         <v>46032</v>
@@ -17416,10 +17407,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J168">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -17469,13 +17460,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J169">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M169" s="11">
         <v>45511</v>
@@ -17522,25 +17513,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J170">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K170">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L170">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M170" s="11">
         <v>45507</v>
       </c>
       <c r="N170" s="11">
-        <v>46083</v>
+        <v>46006</v>
       </c>
       <c r="O170">
         <v>247</v>
       </c>
       <c r="P170" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q170" s="11">
         <v>46151</v>
@@ -17575,7 +17566,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J171">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K171">
         <v>1</v>
@@ -17681,13 +17672,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J173">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
         <v>2</v>
-      </c>
-      <c r="L173">
-        <v>8</v>
       </c>
       <c r="M173" s="11">
         <v>45441</v>
@@ -17699,7 +17690,7 @@
         <v>181</v>
       </c>
       <c r="P173" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q173" s="11">
         <v>46157</v>
@@ -17734,13 +17725,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J174">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L174">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M174" s="11">
         <v>45455</v>
@@ -17887,13 +17878,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J177">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
         <v>2</v>
-      </c>
-      <c r="L177">
-        <v>7</v>
       </c>
       <c r="M177" s="11">
         <v>45486</v>
@@ -17905,7 +17896,7 @@
         <v>226</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q177" s="11">
         <v>45899</v>
@@ -17940,10 +17931,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J178">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L178">
         <v>0</v>
@@ -17993,13 +17984,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J179">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L179">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M179" s="11">
         <v>45528</v>
@@ -18046,13 +18037,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J180">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="K180">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L180">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M180" s="11">
         <v>45435</v>
@@ -18099,13 +18090,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J181">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
         <v>2</v>
-      </c>
-      <c r="L181">
-        <v>4</v>
       </c>
       <c r="M181" s="11">
         <v>45535</v>
@@ -18117,7 +18108,7 @@
         <v>275</v>
       </c>
       <c r="P181" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q181" s="11">
         <v>46047</v>
@@ -18152,13 +18143,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J182">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
         <v>2</v>
-      </c>
-      <c r="L182">
-        <v>5</v>
       </c>
       <c r="M182" s="11">
         <v>45440</v>
@@ -18170,7 +18161,7 @@
         <v>180</v>
       </c>
       <c r="P182" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q182" s="11">
         <v>46041</v>
@@ -18205,13 +18196,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J183">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K183">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L183">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M183" s="11">
         <v>45475</v>
@@ -18223,7 +18214,7 @@
         <v>215</v>
       </c>
       <c r="P183" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q183" s="11">
         <v>46099</v>
@@ -18258,13 +18249,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J184">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L184">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M184" s="11">
         <v>45531</v>
@@ -18311,13 +18302,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J185">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L185">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M185" s="11">
         <v>45490</v>
@@ -18364,25 +18355,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J186">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L186">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M186" s="11">
         <v>45429</v>
       </c>
       <c r="N186" s="11">
-        <v>45804</v>
+        <v>45776</v>
       </c>
       <c r="O186">
         <v>169</v>
       </c>
       <c r="P186" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q186" s="11">
         <v>45775</v>
@@ -18417,13 +18408,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J187">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K187">
         <v>0</v>
       </c>
       <c r="L187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M187" s="11">
         <v>45490</v>
@@ -18470,13 +18461,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J188">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
         <v>1</v>
-      </c>
-      <c r="L188">
-        <v>5</v>
       </c>
       <c r="M188" s="11">
         <v>45505</v>
@@ -18488,7 +18479,7 @@
         <v>245</v>
       </c>
       <c r="P188" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q188" s="11">
         <v>46075</v>
@@ -18523,13 +18514,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J189">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L189">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M189" s="11">
         <v>45465</v>
@@ -18576,13 +18567,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J190">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K190">
         <v>0</v>
       </c>
       <c r="L190">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M190" s="11">
         <v>45445</v>
@@ -18629,13 +18620,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J191">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K191">
         <v>0</v>
       </c>
       <c r="L191">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M191" s="11">
         <v>45496</v>
@@ -18682,13 +18673,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J192">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K192">
         <v>0</v>
       </c>
       <c r="L192">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M192" s="11">
         <v>45456</v>
@@ -18735,10 +18726,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J193">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L193">
         <v>0</v>
@@ -18788,25 +18779,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J194">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K194">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L194">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M194" s="11">
         <v>45438</v>
       </c>
       <c r="N194" s="11">
-        <v>46017</v>
+        <v>46009</v>
       </c>
       <c r="O194">
         <v>178</v>
       </c>
       <c r="P194" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q194" s="11">
         <v>46009</v>
@@ -18894,13 +18885,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J196">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K196">
+        <v>2</v>
+      </c>
+      <c r="L196">
         <v>4</v>
-      </c>
-      <c r="L196">
-        <v>12</v>
       </c>
       <c r="M196" s="11">
         <v>45479</v>
@@ -18947,13 +18938,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J197">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K197">
         <v>1</v>
       </c>
       <c r="L197">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M197" s="11">
         <v>45445</v>
@@ -19000,13 +18991,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J198">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K198">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L198">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M198" s="11">
         <v>45466</v>
@@ -19018,7 +19009,7 @@
         <v>206</v>
       </c>
       <c r="P198" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q198" s="11">
         <v>46152</v>
@@ -19153,13 +19144,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J201">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M201" s="11">
         <v>45435</v>
@@ -19312,13 +19303,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J204">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L204">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M204" s="11">
         <v>45412</v>
@@ -19330,7 +19321,7 @@
         <v>152</v>
       </c>
       <c r="P204" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q204" s="11">
         <v>45973</v>
@@ -19365,25 +19356,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J205">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L205">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M205" s="11">
         <v>45432</v>
       </c>
       <c r="N205" s="11">
-        <v>45950</v>
+        <v>45903</v>
       </c>
       <c r="O205">
         <v>172</v>
       </c>
       <c r="P205" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q205" s="11">
         <v>45901</v>
@@ -19418,13 +19409,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J206">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="K206">
         <v>2</v>
       </c>
       <c r="L206">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M206" s="11">
         <v>45439</v>
@@ -19471,25 +19462,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J207">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M207" s="11">
         <v>45464</v>
       </c>
       <c r="N207" s="11">
-        <v>45938</v>
+        <v>45897</v>
       </c>
       <c r="O207">
         <v>204</v>
       </c>
       <c r="P207" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q207" s="11">
         <v>45810</v>
@@ -19524,13 +19515,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J208">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K208">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L208">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M208" s="11">
         <v>45405</v>
@@ -19577,13 +19568,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J209">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K209">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L209">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M209" s="11">
         <v>45513</v>
@@ -19630,13 +19621,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J210">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L210">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M210" s="11">
         <v>45431</v>
@@ -19683,13 +19674,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J211">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K211">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L211">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M211" s="11">
         <v>45479</v>
@@ -19736,13 +19727,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J212">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
         <v>5</v>
-      </c>
-      <c r="L212">
-        <v>16</v>
       </c>
       <c r="M212" s="11">
         <v>45451</v>
@@ -19789,13 +19780,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J213">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="K213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L213">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M213" s="11">
         <v>45479</v>
@@ -19807,7 +19798,7 @@
         <v>219</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q213" s="11">
         <v>46158</v>
@@ -19842,25 +19833,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J214">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K214">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L214">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="M214" s="11">
         <v>45439</v>
       </c>
       <c r="N214" s="11">
-        <v>45755</v>
+        <v>45726</v>
       </c>
       <c r="O214">
         <v>179</v>
       </c>
       <c r="P214" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q214" s="11">
         <v>45723</v>
@@ -19895,13 +19886,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J215">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="K215">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L215">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="M215" s="11">
         <v>45478</v>
@@ -19913,7 +19904,7 @@
         <v>218</v>
       </c>
       <c r="P215" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q215" s="11">
         <v>46159</v>
@@ -19948,19 +19939,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J216">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K216">
         <v>0</v>
       </c>
       <c r="L216">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M216" s="11">
         <v>45507</v>
       </c>
       <c r="N216" s="11">
-        <v>45586</v>
+        <v>45564</v>
       </c>
       <c r="O216">
         <v>247</v>
@@ -20107,19 +20098,19 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J219">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K219">
         <v>0</v>
       </c>
       <c r="L219">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M219" s="11">
         <v>45481</v>
       </c>
       <c r="N219" s="11">
-        <v>45902</v>
+        <v>45872</v>
       </c>
       <c r="O219">
         <v>-409</v>
@@ -20160,13 +20151,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J220">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K220">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L220">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M220" s="11">
         <v>45494</v>
@@ -20178,7 +20169,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q220" s="11">
         <v>46156</v>
@@ -20213,13 +20204,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J221">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K221">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L221">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M221" s="11">
         <v>45442</v>
@@ -20231,7 +20222,7 @@
         <v>182</v>
       </c>
       <c r="P221" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q221" s="11">
         <v>46072</v>
@@ -20266,7 +20257,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J222">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K222">
         <v>0</v>
@@ -20319,13 +20310,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J223">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M223" s="11">
         <v>45492</v>
@@ -20337,7 +20328,7 @@
         <v>232</v>
       </c>
       <c r="P223" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q223" s="11">
         <v>45716</v>
@@ -20372,13 +20363,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J224">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K224">
         <v>0</v>
       </c>
       <c r="L224">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M224" s="11">
         <v>45416</v>
@@ -20425,13 +20416,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J225">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L225">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M225" s="11">
         <v>45441</v>
@@ -20443,7 +20434,7 @@
         <v>181</v>
       </c>
       <c r="P225" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q225" s="11">
         <v>46103</v>
@@ -20478,13 +20469,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J226">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K226">
         <v>0</v>
       </c>
       <c r="L226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M226" s="11">
         <v>45505</v>
@@ -20531,13 +20522,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J227">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K227">
         <v>0</v>
       </c>
       <c r="L227">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M227" s="11">
         <v>45583</v>
@@ -20584,7 +20575,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J228">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K228">
         <v>0</v>
@@ -20637,7 +20628,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J229">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K229">
         <v>0</v>
@@ -20834,13 +20825,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J233">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M233" s="11">
         <v>45491</v>
@@ -20887,13 +20878,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J234">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L234">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M234" s="11">
         <v>45473</v>
@@ -20940,10 +20931,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J235">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L235">
         <v>0</v>
@@ -20993,25 +20984,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J236">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K236">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L236">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M236" s="11">
         <v>45483</v>
       </c>
       <c r="N236" s="11">
-        <v>45923</v>
+        <v>45827</v>
       </c>
       <c r="O236">
         <v>223</v>
       </c>
       <c r="P236" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q236" s="11">
         <v>45882</v>
@@ -21046,13 +21037,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J237">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L237">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M237" s="11">
         <v>45454</v>
@@ -21152,13 +21143,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J239">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L239">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M239" s="11">
         <v>45427</v>
@@ -21170,7 +21161,7 @@
         <v>167</v>
       </c>
       <c r="P239" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q239" s="11">
         <v>46042</v>
@@ -21205,13 +21196,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J240">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K240">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L240">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="M240" s="11">
         <v>45468</v>
@@ -21223,7 +21214,7 @@
         <v>208</v>
       </c>
       <c r="P240" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q240" s="11">
         <v>45871</v>
@@ -21258,13 +21249,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J241">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K241">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L241">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M241" s="11">
         <v>45475</v>
@@ -21276,7 +21267,7 @@
         <v>215</v>
       </c>
       <c r="P241" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q241" s="11">
         <v>46039</v>
@@ -21311,13 +21302,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J242">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K242">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L242">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M242" s="11">
         <v>45488</v>
@@ -21364,13 +21355,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J243">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K243">
         <v>0</v>
       </c>
       <c r="L243">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M243" s="11">
         <v>45531</v>
@@ -21508,7 +21499,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J246">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -21693,10 +21684,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J250">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -21746,13 +21737,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J251">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K251">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L251">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M251" s="11">
         <v>45695</v>
@@ -21764,7 +21755,7 @@
         <v>435</v>
       </c>
       <c r="P251" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q251" s="11">
         <v>45840</v>
@@ -21799,13 +21790,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J252">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K252">
         <v>1</v>
       </c>
       <c r="L252">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M252" s="11">
         <v>45601</v>
@@ -21905,19 +21896,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J254">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K254">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L254">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M254" s="11">
         <v>45583</v>
       </c>
       <c r="N254" s="11">
-        <v>45923</v>
+        <v>45918</v>
       </c>
       <c r="O254">
         <v>323</v>
@@ -22011,13 +22002,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J256">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K256">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L256">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M256" s="11">
         <v>45552</v>
@@ -22064,13 +22055,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J257">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="K257">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L257">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M257" s="11">
         <v>45536</v>
@@ -22117,13 +22108,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J258">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L258">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M258" s="11">
         <v>45520</v>
@@ -22135,7 +22126,7 @@
         <v>260</v>
       </c>
       <c r="P258" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q258" s="11">
         <v>46151</v>
@@ -22170,13 +22161,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J259">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K259">
         <v>0</v>
       </c>
       <c r="L259">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M259" s="11">
         <v>45523</v>
@@ -22223,19 +22214,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J260">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K260">
         <v>0</v>
       </c>
       <c r="L260">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M260" s="11">
         <v>45683</v>
       </c>
       <c r="N260" s="11">
-        <v>45835</v>
+        <v>45816</v>
       </c>
       <c r="O260">
         <v>423</v>
@@ -22276,25 +22267,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J261">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K261">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L261">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M261" s="11">
         <v>45558</v>
       </c>
       <c r="N261" s="11">
-        <v>46014</v>
+        <v>46161</v>
       </c>
       <c r="O261">
         <v>298</v>
       </c>
       <c r="P261" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q261" s="11">
         <v>46157</v>
@@ -22473,13 +22464,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J265">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K265">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L265">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M265" s="11">
         <v>45563</v>
@@ -22491,7 +22482,7 @@
         <v>303</v>
       </c>
       <c r="P265" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q265" s="11">
         <v>46101</v>
@@ -22526,10 +22517,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J266">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -22538,7 +22529,7 @@
         <v>45563</v>
       </c>
       <c r="N266" s="11">
-        <v>45826</v>
+        <v>45668</v>
       </c>
       <c r="O266">
         <v>303</v>
@@ -22579,7 +22570,7 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J267">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -22632,13 +22623,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J268">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K268">
         <v>0</v>
       </c>
       <c r="L268">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M268" s="11">
         <v>45542</v>
@@ -22685,13 +22676,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J269">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K269">
         <v>0</v>
       </c>
       <c r="L269">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M269" s="11">
         <v>45521</v>
@@ -22776,13 +22767,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J271">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K271">
         <v>0</v>
       </c>
       <c r="L271">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M271" s="11">
         <v>45526</v>
@@ -22829,13 +22820,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J272">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K272">
         <v>0</v>
       </c>
       <c r="L272">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M272" s="11">
         <v>45525</v>
@@ -23041,19 +23032,19 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J276">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K276">
         <v>0</v>
       </c>
       <c r="L276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M276" s="11">
         <v>45545</v>
       </c>
       <c r="N276" s="11">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="O276">
         <v>285</v>
@@ -23147,13 +23138,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J278">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K278">
+        <v>0</v>
+      </c>
+      <c r="L278">
         <v>1</v>
-      </c>
-      <c r="L278">
-        <v>4</v>
       </c>
       <c r="M278" s="11">
         <v>45545</v>
@@ -23306,25 +23297,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J281">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L281">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M281" s="11">
         <v>45527</v>
       </c>
       <c r="N281" s="11">
-        <v>45741</v>
+        <v>45682</v>
       </c>
       <c r="O281">
         <v>267</v>
       </c>
       <c r="P281" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q281" s="11">
         <v>45681</v>
@@ -23359,13 +23350,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J282">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K282">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L282">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M282" s="11">
         <v>45530</v>
@@ -23412,13 +23403,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J283">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
         <v>1</v>
-      </c>
-      <c r="L283">
-        <v>4</v>
       </c>
       <c r="M283" s="11">
         <v>45522</v>
@@ -23465,13 +23456,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J284">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L284">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M284" s="11">
         <v>45517</v>
@@ -23518,13 +23509,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J285">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K285">
+        <v>0</v>
+      </c>
+      <c r="L285">
         <v>1</v>
-      </c>
-      <c r="L285">
-        <v>4</v>
       </c>
       <c r="M285" s="11">
         <v>45632</v>
@@ -23536,7 +23527,7 @@
         <v>372</v>
       </c>
       <c r="P285" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q285" s="11">
         <v>45893</v>
@@ -23571,25 +23562,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J286">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K286">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L286">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M286" s="11">
         <v>45567</v>
       </c>
       <c r="N286" s="11">
-        <v>45959</v>
+        <v>45893</v>
       </c>
       <c r="O286">
         <v>307</v>
       </c>
       <c r="P286" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q286" s="11">
         <v>45892</v>
@@ -23624,13 +23615,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J287">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K287">
         <v>0</v>
       </c>
       <c r="L287">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M287" s="11">
         <v>45516</v>
@@ -23677,13 +23668,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J288">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L288">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M288" s="11">
         <v>45523</v>
@@ -23783,13 +23774,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J290">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K290">
         <v>0</v>
       </c>
       <c r="L290">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M290" s="11">
         <v>45518</v>
@@ -23836,13 +23827,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J291">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K291">
         <v>0</v>
       </c>
       <c r="L291">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M291" s="11">
         <v>45549</v>
@@ -23889,13 +23880,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J292">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K292">
         <v>0</v>
       </c>
       <c r="L292">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M292" s="11">
         <v>45525</v>
@@ -23995,13 +23986,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J294">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K294">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L294">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M294" s="11">
         <v>45685</v>
@@ -24013,7 +24004,7 @@
         <v>425</v>
       </c>
       <c r="P294" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q294" s="11">
         <v>45941</v>
@@ -24048,13 +24039,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J295">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K295">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L295">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M295" s="11">
         <v>45687</v>
@@ -24066,7 +24057,7 @@
         <v>427</v>
       </c>
       <c r="P295" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q295" s="11">
         <v>46136</v>
@@ -24154,13 +24145,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J297">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
         <v>1</v>
-      </c>
-      <c r="L297">
-        <v>5</v>
       </c>
       <c r="M297" s="11">
         <v>45647</v>
@@ -24172,7 +24163,7 @@
         <v>387</v>
       </c>
       <c r="P297" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q297" s="11">
         <v>45972</v>
@@ -24207,13 +24198,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J298">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K298">
+        <v>0</v>
+      </c>
+      <c r="L298">
         <v>1</v>
-      </c>
-      <c r="L298">
-        <v>5</v>
       </c>
       <c r="M298" s="11">
         <v>45666</v>
@@ -24225,7 +24216,7 @@
         <v>406</v>
       </c>
       <c r="P298" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q298" s="11">
         <v>46048</v>
@@ -24260,13 +24251,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J299">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L299">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M299" s="11">
         <v>45642</v>
@@ -24278,7 +24269,7 @@
         <v>382</v>
       </c>
       <c r="P299" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q299" s="11">
         <v>46155</v>
@@ -24313,13 +24304,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J300">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K300">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L300">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M300" s="11">
         <v>45524</v>
@@ -24331,7 +24322,7 @@
         <v>264</v>
       </c>
       <c r="P300" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q300" s="11">
         <v>45963</v>
@@ -24366,13 +24357,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J301">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K301">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L301">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M301" s="11">
         <v>45610</v>
@@ -24419,13 +24410,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J302">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
         <v>1</v>
-      </c>
-      <c r="L302">
-        <v>2</v>
       </c>
       <c r="M302" s="11">
         <v>45636</v>
@@ -24437,7 +24428,7 @@
         <v>376</v>
       </c>
       <c r="P302" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q302" s="11">
         <v>46031</v>
@@ -24525,25 +24516,25 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J304">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
         <v>2</v>
-      </c>
-      <c r="L304">
-        <v>6</v>
       </c>
       <c r="M304" s="11">
         <v>45686</v>
       </c>
       <c r="N304" s="11">
-        <v>45906</v>
+        <v>45890</v>
       </c>
       <c r="O304">
         <v>426</v>
       </c>
       <c r="P304" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q304" s="11">
         <v>46125</v>
@@ -24631,10 +24622,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J306">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L306">
         <v>0</v>
@@ -24737,13 +24728,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J308">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K308">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L308">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M308" s="11">
         <v>45637</v>
@@ -24755,7 +24746,7 @@
         <v>377</v>
       </c>
       <c r="P308" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q308" s="11">
         <v>46157</v>
@@ -24790,13 +24781,13 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J309">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K309">
         <v>0</v>
       </c>
       <c r="L309">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M309" s="11">
         <v>45521</v>
@@ -24896,13 +24887,13 @@
         <v>84.341712962962958</v>
       </c>
       <c r="J311">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K311">
         <v>0</v>
       </c>
       <c r="L311">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M311" s="11">
         <v>45497</v>
@@ -24949,13 +24940,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J312">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L312">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M312" s="11">
         <v>45640</v>
@@ -25055,13 +25046,13 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J314">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K314">
         <v>0</v>
       </c>
       <c r="L314">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M314" s="11">
         <v>45491</v>
@@ -25108,13 +25099,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J315">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K315">
+        <v>1</v>
+      </c>
+      <c r="L315">
         <v>4</v>
-      </c>
-      <c r="L315">
-        <v>13</v>
       </c>
       <c r="M315" s="11">
         <v>45615</v>
@@ -25320,13 +25311,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J319">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K319">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L319">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M319" s="11">
         <v>45754</v>
@@ -25338,7 +25329,7 @@
         <v>494</v>
       </c>
       <c r="P319" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q319" s="11">
         <v>46029</v>
@@ -25373,13 +25364,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J320">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L320">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M320" s="11">
         <v>45680</v>
@@ -25391,7 +25382,7 @@
         <v>420</v>
       </c>
       <c r="P320" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q320" s="11">
         <v>46138</v>
@@ -25479,13 +25470,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J322">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K322">
+        <v>0</v>
+      </c>
+      <c r="L322">
         <v>2</v>
-      </c>
-      <c r="L322">
-        <v>4</v>
       </c>
       <c r="M322" s="11">
         <v>45718</v>
@@ -25497,7 +25488,7 @@
         <v>458</v>
       </c>
       <c r="P322" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q322" s="11">
         <v>46153</v>
@@ -25532,13 +25523,13 @@
         <v>84.375891203703702</v>
       </c>
       <c r="J323">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K323">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L323">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M323" s="11">
         <v>45687</v>
@@ -25550,7 +25541,7 @@
         <v>13</v>
       </c>
       <c r="P323" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q323" s="11">
         <v>46056</v>
@@ -25638,13 +25629,13 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J325">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
         <v>1</v>
-      </c>
-      <c r="L325">
-        <v>4</v>
       </c>
       <c r="M325" s="11">
         <v>45693</v>
@@ -25656,7 +25647,7 @@
         <v>-197</v>
       </c>
       <c r="P325" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q325" s="11">
         <v>46157</v>
@@ -25788,13 +25779,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J328">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K328">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L328">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M328" s="11">
         <v>45720</v>
@@ -25841,19 +25832,19 @@
         <v>84.376539351851847</v>
       </c>
       <c r="J329">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K329">
+        <v>0</v>
+      </c>
+      <c r="L329">
         <v>1</v>
-      </c>
-      <c r="L329">
-        <v>2</v>
       </c>
       <c r="M329" s="11">
         <v>45701</v>
       </c>
       <c r="N329" s="11">
-        <v>45901</v>
+        <v>45898</v>
       </c>
       <c r="O329">
         <v>0</v>
@@ -25894,13 +25885,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J330">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K330">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L330">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M330" s="11">
         <v>45765</v>
@@ -25912,7 +25903,7 @@
         <v>505</v>
       </c>
       <c r="P330" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q330" s="11">
         <v>46161</v>
@@ -26150,10 +26141,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J335">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L335">
         <v>1</v>
@@ -26409,10 +26400,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J340">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K340">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L340">
         <v>1</v>
@@ -26515,13 +26506,13 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K342">
         <v>0</v>
       </c>
       <c r="L342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M342" s="11">
         <v>45736</v>
@@ -26718,10 +26709,10 @@
         <v>84.29965277777778</v>
       </c>
       <c r="J346">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K346">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L346">
         <v>3</v>
@@ -26771,13 +26762,13 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J347">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K347">
         <v>1</v>
       </c>
       <c r="L347">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M347" s="11">
         <v>45843</v>
@@ -27365,13 +27356,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J362">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K362">
         <v>2</v>
       </c>
       <c r="L362">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M362" s="11">
         <v>45565</v>
@@ -27468,13 +27459,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J364">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K364">
         <v>0</v>
       </c>
       <c r="L364">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M364" s="11">
         <v>45520</v>
@@ -27609,13 +27600,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J367">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K367">
         <v>3</v>
       </c>
       <c r="L367">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M367" s="11">
         <v>45517</v>
@@ -27706,13 +27697,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J369">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K369">
         <v>3</v>
       </c>
       <c r="L369">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M369" s="11">
         <v>45507</v>
@@ -27759,13 +27750,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J370">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K370">
         <v>0</v>
       </c>
       <c r="L370">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M370" s="11">
         <v>45508</v>
@@ -27812,13 +27803,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J371">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K371">
         <v>2</v>
       </c>
       <c r="L371">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M371" s="11">
         <v>45515</v>
@@ -27865,7 +27856,7 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J372">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K372">
         <v>1</v>
@@ -27918,13 +27909,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J373">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K373">
         <v>2</v>
       </c>
       <c r="L373">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M373" s="11">
         <v>45509</v>
@@ -27971,13 +27962,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J374">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K374">
         <v>0</v>
       </c>
       <c r="L374">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M374" s="11">
         <v>45514</v>
@@ -28024,13 +28015,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J375">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K375">
         <v>0</v>
       </c>
       <c r="L375">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M375" s="11">
         <v>45536</v>
@@ -28077,13 +28068,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J376">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K376">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L376">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M376" s="11">
         <v>45523</v>
@@ -28095,7 +28086,7 @@
         <v>226</v>
       </c>
       <c r="P376" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q376" s="11">
         <v>46161</v>
@@ -28130,13 +28121,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J377">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K377">
+        <v>1</v>
+      </c>
+      <c r="L377">
         <v>2</v>
-      </c>
-      <c r="L377">
-        <v>3</v>
       </c>
       <c r="M377" s="11">
         <v>45537</v>
@@ -28183,13 +28174,13 @@
         <v>84.339050925925932</v>
       </c>
       <c r="J378">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K378">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L378">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M378" s="11">
         <v>45526</v>
@@ -28236,19 +28227,19 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J379">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K379">
         <v>1</v>
       </c>
       <c r="L379">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M379" s="11">
         <v>45514</v>
       </c>
       <c r="N379" s="11">
-        <v>45861</v>
+        <v>45841</v>
       </c>
       <c r="O379">
         <v>217</v>
@@ -28289,13 +28280,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J380">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L380">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M380" s="11">
         <v>45546</v>
@@ -28342,13 +28333,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J381">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K381">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L381">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M381" s="11">
         <v>45522</v>
@@ -28360,7 +28351,7 @@
         <v>225</v>
       </c>
       <c r="P381" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q381" s="11">
         <v>46160</v>
@@ -28395,19 +28386,19 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J382">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K382">
         <v>0</v>
       </c>
       <c r="L382">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M382" s="11">
         <v>45528</v>
       </c>
       <c r="N382" s="11">
-        <v>45603</v>
+        <v>45572</v>
       </c>
       <c r="O382">
         <v>33</v>
@@ -28448,13 +28439,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J383">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K383">
         <v>0</v>
       </c>
       <c r="L383">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M383" s="11">
         <v>45548</v>
@@ -28501,13 +28492,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J384">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K384">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L384">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M384" s="11">
         <v>45513</v>
@@ -28519,7 +28510,7 @@
         <v>18</v>
       </c>
       <c r="P384" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q384" s="11">
         <v>46061</v>
@@ -28554,13 +28545,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J385">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K385">
         <v>1</v>
       </c>
       <c r="L385">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M385" s="11">
         <v>45533</v>
@@ -28607,13 +28598,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J386">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K386">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L386">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M386" s="11">
         <v>45541</v>
@@ -28660,13 +28651,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J387">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K387">
+        <v>1</v>
+      </c>
+      <c r="L387">
         <v>3</v>
-      </c>
-      <c r="L387">
-        <v>12</v>
       </c>
       <c r="M387" s="11">
         <v>45545</v>
@@ -28678,7 +28669,7 @@
         <v>25</v>
       </c>
       <c r="P387" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q387" s="11">
         <v>46131</v>
@@ -28766,19 +28757,19 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J389">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K389">
         <v>0</v>
       </c>
       <c r="L389">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M389" s="11">
         <v>45524</v>
       </c>
       <c r="N389" s="11">
-        <v>45630</v>
+        <v>45574</v>
       </c>
       <c r="O389">
         <v>805</v>
@@ -28819,13 +28810,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J390">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K390">
+        <v>0</v>
+      </c>
+      <c r="L390">
         <v>4</v>
-      </c>
-      <c r="L390">
-        <v>13</v>
       </c>
       <c r="M390" s="11">
         <v>45551</v>
@@ -28837,7 +28828,7 @@
         <v>56</v>
       </c>
       <c r="P390" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q390" s="11">
         <v>46158</v>
@@ -28872,13 +28863,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J391">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K391">
         <v>0</v>
       </c>
       <c r="L391">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M391" s="11">
         <v>45532</v>
@@ -28925,13 +28916,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J392">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K392">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L392">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M392" s="11">
         <v>45545</v>
@@ -28943,7 +28934,7 @@
         <v>25</v>
       </c>
       <c r="P392" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q392" s="11">
         <v>46131</v>
@@ -28978,19 +28969,19 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J393">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K393">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L393">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M393" s="11">
         <v>45553</v>
       </c>
       <c r="N393" s="11">
-        <v>45868</v>
+        <v>45857</v>
       </c>
       <c r="O393">
         <v>33</v>
@@ -29031,13 +29022,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J394">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K394">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L394">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M394" s="11">
         <v>45567</v>
@@ -29049,7 +29040,7 @@
         <v>47</v>
       </c>
       <c r="P394" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q394" s="11">
         <v>46131</v>
@@ -29084,13 +29075,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J395">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="K395">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L395">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M395" s="11">
         <v>45615</v>
@@ -29137,13 +29128,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J396">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K396">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L396">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M396" s="11">
         <v>45565</v>
@@ -29155,7 +29146,7 @@
         <v>70</v>
       </c>
       <c r="P396" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q396" s="11">
         <v>46069</v>
@@ -29190,13 +29181,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J397">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K397">
         <v>0</v>
       </c>
       <c r="L397">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M397" s="11">
         <v>45572</v>
@@ -29243,13 +29234,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J398">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K398">
         <v>0</v>
       </c>
       <c r="L398">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M398" s="11">
         <v>45547</v>
@@ -29296,13 +29287,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J399">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K399">
         <v>0</v>
       </c>
       <c r="L399">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M399" s="11">
         <v>45574</v>
@@ -29402,13 +29393,13 @@
         <v>84.338449074074077</v>
       </c>
       <c r="J401">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K401">
+        <v>0</v>
+      </c>
+      <c r="L401">
         <v>2</v>
-      </c>
-      <c r="L401">
-        <v>6</v>
       </c>
       <c r="M401" s="11">
         <v>45564</v>
@@ -29420,7 +29411,7 @@
         <v>69</v>
       </c>
       <c r="P401" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q401" s="11">
         <v>46134</v>
@@ -29969,13 +29960,13 @@
         <v>84.334097222222226</v>
       </c>
       <c r="J416">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K416">
         <v>0</v>
       </c>
       <c r="L416">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M416" s="11">
         <v>45556</v>
@@ -30442,13 +30433,13 @@
         <v>84.381435185185182</v>
       </c>
       <c r="J429">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K429">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L429">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M429" s="11">
         <v>45806</v>
@@ -30527,13 +30518,13 @@
         <v>7017231604</v>
       </c>
       <c r="F431" s="10">
-        <v>0.85951388888888891</v>
+        <v>0.87815972222222227</v>
       </c>
       <c r="G431">
-        <v>1237.7</v>
+        <v>1264.55</v>
       </c>
       <c r="H431">
-        <v>214.57</v>
+        <v>220.59</v>
       </c>
       <c r="I431" s="9">
         <v>84.380775462962958</v>
@@ -30751,10 +30742,10 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J435">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K435">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L435">
         <v>0</v>
@@ -30804,13 +30795,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J436">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K436">
+        <v>0</v>
+      </c>
+      <c r="L436">
         <v>1</v>
-      </c>
-      <c r="L436">
-        <v>2</v>
       </c>
       <c r="M436" s="11">
         <v>45872</v>
@@ -30822,7 +30813,7 @@
         <v>352</v>
       </c>
       <c r="P436" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q436" s="11">
         <v>45934</v>
@@ -30986,13 +30977,13 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J440">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K440">
         <v>1</v>
       </c>
       <c r="L440">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M440" s="11">
         <v>45847</v>
@@ -31039,13 +31030,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J441">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K441">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L441">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M441" s="11">
         <v>45750</v>
@@ -31198,10 +31189,10 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J444">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K444">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L444">
         <v>2</v>
@@ -31251,13 +31242,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J445">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K445">
         <v>0</v>
       </c>
       <c r="L445">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M445" s="11">
         <v>45897</v>
@@ -31351,13 +31342,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J447">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K447">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L447">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M447" s="11">
         <v>45862</v>
@@ -31369,7 +31360,7 @@
         <v>342</v>
       </c>
       <c r="P447" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q447" s="11">
         <v>46097</v>
@@ -31510,13 +31501,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J450">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K450">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L450">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M450" s="11">
         <v>45753</v>
@@ -31528,7 +31519,7 @@
         <v>233</v>
       </c>
       <c r="P450" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q450" s="11">
         <v>46014</v>
@@ -31563,7 +31554,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J451">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K451">
         <v>0</v>
@@ -31616,13 +31607,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J452">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K452">
         <v>1</v>
       </c>
       <c r="L452">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M452" s="11">
         <v>45884</v>
@@ -31669,10 +31660,10 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J453">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K453">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L453">
         <v>1</v>
@@ -31681,7 +31672,7 @@
         <v>45909</v>
       </c>
       <c r="N453" s="11">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="O453">
         <v>389</v>
@@ -31775,13 +31766,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J455">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K455">
         <v>2</v>
       </c>
       <c r="L455">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M455" s="11">
         <v>45858</v>
@@ -31934,13 +31925,13 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J458">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K458">
         <v>1</v>
       </c>
       <c r="L458">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M458" s="11">
         <v>45873</v>
@@ -32054,25 +32045,25 @@
         <v>84.339074074074077</v>
       </c>
       <c r="J461">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K461">
+        <v>0</v>
+      </c>
+      <c r="L461">
         <v>1</v>
-      </c>
-      <c r="L461">
-        <v>3</v>
       </c>
       <c r="M461" s="11">
         <v>45869</v>
       </c>
       <c r="N461" s="11">
-        <v>45871</v>
+        <v>45869</v>
       </c>
       <c r="O461">
         <v>349</v>
       </c>
       <c r="P461" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
     </row>
     <row r="462" spans="1:17">
@@ -32727,25 +32718,25 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J475">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K475">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L475">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M475" s="11">
-        <v>45796</v>
+        <v>46136</v>
       </c>
       <c r="N475" s="11">
         <v>46136</v>
       </c>
       <c r="O475">
-        <v>-94</v>
+        <v>246</v>
       </c>
       <c r="P475" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q475" s="11">
         <v>45933</v>
@@ -32833,10 +32824,10 @@
         <v>84.380798611111118</v>
       </c>
       <c r="J477">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K477">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L477">
         <v>1</v>
@@ -33771,10 +33762,10 @@
         <v>84.382268518518515</v>
       </c>
       <c r="J499">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K499">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L499">
         <v>3</v>
@@ -34884,7 +34875,7 @@
         <v>4</v>
       </c>
       <c r="K526">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L526">
         <v>1</v>
@@ -35935,7 +35926,7 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J552">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K552">
         <v>0</v>
@@ -35947,7 +35938,7 @@
         <v>45132</v>
       </c>
       <c r="N552" s="11">
-        <v>45635</v>
+        <v>45602</v>
       </c>
       <c r="O552">
         <v>129</v>
@@ -39903,10 +39894,10 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J637">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K637">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L637">
         <v>2</v>
@@ -40053,7 +40044,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J640">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K640">
         <v>0</v>
@@ -40376,10 +40367,10 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J647">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K647">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L647">
         <v>0</v>
@@ -40394,7 +40385,7 @@
         <v>119</v>
       </c>
       <c r="P647" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q647" s="11">
         <v>46148</v>
@@ -40476,25 +40467,25 @@
         <v>84.293958333333336</v>
       </c>
       <c r="J649">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K649">
+        <v>0</v>
+      </c>
+      <c r="L649">
         <v>2</v>
-      </c>
-      <c r="L649">
-        <v>3</v>
       </c>
       <c r="M649" s="11">
         <v>45108</v>
       </c>
       <c r="N649" s="11">
-        <v>45881</v>
+        <v>45873</v>
       </c>
       <c r="O649">
         <v>105</v>
       </c>
       <c r="P649" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q649" s="11">
         <v>46105</v>
@@ -40919,19 +40910,13 @@
         <v>0</v>
       </c>
       <c r="J659">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K659">
         <v>0</v>
       </c>
       <c r="L659">
         <v>0</v>
-      </c>
-      <c r="M659" s="11">
-        <v>45333</v>
-      </c>
-      <c r="N659" s="11">
-        <v>45333</v>
       </c>
       <c r="P659" t="s">
         <v>309</v>
@@ -41165,13 +41150,13 @@
         <v>84.334780092592595</v>
       </c>
       <c r="J665">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K665">
+        <v>0</v>
+      </c>
+      <c r="L665">
         <v>1</v>
-      </c>
-      <c r="L665">
-        <v>4</v>
       </c>
       <c r="M665" s="11">
         <v>45469</v>
@@ -41183,7 +41168,7 @@
         <v>142</v>
       </c>
       <c r="P665" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="Q665" s="11">
         <v>45716</v>
@@ -43615,7 +43600,7 @@
         <v>84.254247685185192</v>
       </c>
       <c r="J726">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K726">
         <v>0</v>
@@ -43624,13 +43609,13 @@
         <v>0</v>
       </c>
       <c r="M726" s="11">
-        <v>45278</v>
+        <v>45657</v>
       </c>
       <c r="N726" s="11">
         <v>45661</v>
       </c>
       <c r="O726">
-        <v>559</v>
+        <v>938</v>
       </c>
       <c r="P726" t="s">
         <v>309</v>
@@ -44681,7 +44666,7 @@
       </c>
       <c r="J6" s="4" cm="1">
         <f t="array" ref="J6">ROWS(_xlfn._xlws.FILTER('Drone details'!A2:A447,VALUE('Drone details'!K2:K447&amp;"0")&gt;0))</f>
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="K6" s="4" cm="1">
         <f t="array" ref="K6">SUMPRODUCT((ISNUMBER('Drone details'!N2:N447)*('Drone details'!N2:N447&lt;=30))*1)</f>
@@ -44698,7 +44683,7 @@
       </c>
       <c r="J7" s="4" cm="1">
         <f t="array" ref="J7">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Drone details'!C2:C447,VALUE('Drone details'!K2:K447&amp;"0")&gt;0)))</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K7" s="4" t="e" cm="1" vm="1">
         <f t="array" ref="K7">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Drone details'!C2:C447,(ISNUMBER('Drone details'!N2:N447))*('Drone details'!N2:N447&lt;=30))))</f>
